--- a/resources/templates/Template Laporan RTM FST.xlsx
+++ b/resources/templates/Template Laporan RTM FST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SiGKM\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24FAA21-F638-4838-AB92-5BEC4FE98456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A89CF72-115A-4735-B064-BA12F55AC553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="839" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TM Standar Mutu Prog.Studi" sheetId="36" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="382">
   <si>
     <t>NO.</t>
   </si>
@@ -124,13 +124,1230 @@
   </si>
   <si>
     <t>SEMESTER GANJIL 2025/2026</t>
+  </si>
+  <si>
+    <t>Standar Visi Misi</t>
+  </si>
+  <si>
+    <t>Fakultas  memiliki dokumen rencana pengembangan yang mencakup: rencana jangka panjang, jangka menengah, dan jangka pendek, indikator kinerja, target yang berorientasi pada daya saing internasional</t>
+  </si>
+  <si>
+    <t>Fakultas  memiliki bukti sahih pelaksanaan rencana pengembangan institusi secara konsisten</t>
+  </si>
+  <si>
+    <t>Setiap UPPS  memiliki dokumen rencana jangka menengah (Renstra
+dan RSB), dan jangka pendek (Renop) yang memuat indikator kinerja dan target yang mendukung realisasi pencapaian Renstra dan RSB berikut indikator kinerja dan target Perguruan Tinggi</t>
+  </si>
+  <si>
+    <t>UPPS memiliki VMTS yang mencerminkan Visi Fakultas  dan memayungi visi keilmuan program studi yang dikelolanya setiap waktu perubahan VMTS</t>
+  </si>
+  <si>
+    <t>Fakultas dan UPPS memiliki dokumen formal kebijakan yang mencakup: penyusunan, sosialisasi, implementasi dan evaluasi VMTS masing-masing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakultas dan UPPS memiliki mekanisme yang terdokumentasi dan bukti sahih keterlibatan pemangku kepentingan dalam penyusunan VMTS Fakultas /UPPS setiap periode penyusunan </t>
+  </si>
+  <si>
+    <t>Seluruh unsur yang ada di Undana paham dengan VMTS Fakultas dan menggunakan Visi, Misi Undana sebagai acuan dalam melaksanakan kegiatan</t>
+  </si>
+  <si>
+    <t>Fakultas dan UPPS memiliki dokumen bukti alokasi sumber daya manusia, sarana prasarana, sistem tata Kelola/tata pamong dan anggaran dan bukti sahih pelaksanaan mekanisme control untuk pencapaian VMTS setiap tahun</t>
+  </si>
+  <si>
+    <t>Terbentuk tim kerja yang disahkan dengan SK Dekan untuk mengukur memonitor, mengkaji dan menganalisis indikator VMTS dan Target Fakultas/UPPS/PS dan tersedia dokumen bukti hasil pengukuran, monitoring dan hasil analisis ketercapaian indikator dan target  T/UPPS/PS serta bukti sahih penggunaan hasil analisis tersebut untuk perbaikan institusi secara berkelanjutan setiap tahun</t>
+  </si>
+  <si>
+    <t>Standar Tata Pamong dan Tata Kelola</t>
+  </si>
+  <si>
+    <t>Undana memiliki dokumen formal sistem tata pamong yang dijabarkan ke dalam berbagai kebijakan dan peraturan yang digunakan secara: konsisten, efektif, dan efisien sesuai konteks institusi serta menjamin akuntabilitas, keberlanjutan, transparansi, dan mitigasi potensi risiko</t>
+  </si>
+  <si>
+    <t>Undana memiliki bukti sahih dalam bentuk dokumen formal kebijakan dan peraturan guna menjamin integritas dan kualitas institusi yang dilaksanakan secara konsisten, efektif dan efisien</t>
+  </si>
+  <si>
+    <t>Undana memiliki dokumen formal struktur organisasi termasuk tata kerja institusi yang dilengkapi tugas dan fungsi guna menjamin terlaksananya fungsi perguruan tinggi secara konsisten, efektif dan efisien</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Undana memiliki bukti yang sahih terkait praktik baik perwujudan </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Good University Governnce</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mencakup aspek: kredibilitas, transparansi, akuntabilitas, tanggung jawab, keadilan, dan manajemen risiko secara konsisten, efektif, dan efisien, mengumumkan ringkasan laporan tahunan kepada masyarakat</t>
+    </r>
+  </si>
+  <si>
+    <t>Undana memiliki dokumen sahih yang memuat informasi tentang: struktur organisasi serta deskripsi yang jelas dan lengkap tentang tugas, fungsi, wewenang, dan tanggung jawab untuk setiap organ dalam struktur organisasi Undana</t>
+  </si>
+  <si>
+    <t>Undana memiliki dokumen sahih yang memuat informasi tentang: lembaga kode etik dalam OTK institusi yang sah; disertai deskripsi tugas, fungsi, wewenang dan
+tanggungjawab, dokumen kode etik bidang akademik dan nonakademik; SOP pelaksanaan kode etik yang sangat lengkap dan jelas (termasuk prosedur penyelesaian pelanggaran kode etik); laporan monitoring evaluasi pelaksanaan kode etik yang terdokumentasikan dengan baik sehingga dapat menjamin tata nilai dan integritas secara konsisten, efektif dan efisien serta dapat diakses oleh masyarakat pengguna</t>
+  </si>
+  <si>
+    <t>Standar Pengelolaan Sistim Penjaminan Mutu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakultas memiliki dokumen formal pengembangan sistem penjaminan mutu yang fungsional
+</t>
+  </si>
+  <si>
+    <t>Fakultas memiliki dokumen formal SPMI yang meliputi 5 aspek sebagai berikut: organ/fungsi SPMI, dokumen SPMI, auditor internal, hasil audit, dan bukti tindak lanjut</t>
+  </si>
+  <si>
+    <t>Fakultas memiliki (1) standar mutu yang melampaui SN- DIKTI, (2) bukti sahih efektivitas pelaksanaan siklus PPEPP dan (3) bukti penerapan inovasi SPMI yakni Audit Berbasis Risiko dan (4) bukti rujukan eksetenal benchmarking untuk
+peningkatan mutu</t>
+  </si>
+  <si>
+    <t>Fakultas/UPPS/Program studi memiliki bukti yang sahih pelaksanaan rapat tinjauan manajemen yang dihadiri oleh seluruh pimpinan Perguruan tinggi/UPPS/dosen dan bukti pembahasan evaluasi kinerja tahun sebelumnya dan rencana kinerja tahun berikutnya hasil audit internal, tindak lanjut atas hasil temuan dan rekomendasi
+peningkatan mutu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakultas  memiliki peringkat akreditasi institusi perguruan tinggi Unggul dan 10% program studi memiliki peringkat unggul tahun 2025 </t>
+  </si>
+  <si>
+    <t>Tersedia borang AIPT 3.0 (LKPTdan LEDPT)/borang AIPS 4.0 (LKPS dan LED) setiap akhir TS dan telah direview/audit oleh auditor internal Perguruan tinggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakultas memiliki minimal 5% program studi terakreditasi internasional oleh Lembaga internasional yang diakui pemerintah tahun 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimal setiap program studi memiliki  1 auditor  mutu internal bersertifikat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perguruan Tinggi memiliki hasil Audit eksternal dengan Opini Wajar Tanpa Pengecualian (Unqualified Opinion) </t>
+  </si>
+  <si>
+    <t>Standar Kerjasama Bidang Pendidikan, Penelitian dan PKM</t>
+  </si>
+  <si>
+    <t>Undana memiliki dokumen formal kebijakan dan prosedur,yang komprehensif, rinci, terkini, dan mudah diakses oleh pemangku kepentingan, tentang pengembangan jejaring dan kemitraan (dalam dan luar negeri) dan panduan dan laporan monitoring dan evaluasi kepuasan mitra kerjasama</t>
+  </si>
+  <si>
+    <t>Undana memiliki dokumen perencanaan pengembangan jejaring dan kemitraan yang sahih dan terarah guna mencapai visi, misi, dan tujuan strategis institusi</t>
+  </si>
+  <si>
+    <t>Undana memiliki system informasi tentang data jumlah, lingkup, relevansi, dan kebermanfaatan kerjasama secara berkala dan dapat diakses oleh pemangku kepentingan</t>
+  </si>
+  <si>
+    <t>Undana memiliki bukti sahih pelaksanaan monitoring dan evaluasi pelaksanaan program kemitraan, tingkat kepuasan mitra kerjasama bidang pendidikan, penelitian dan PKM yang diukur dengan instrumen yang sahih, serta melakukan
+perbaikan mutu jejaring dan kemitraan secara berkala untuk menjamin ketercapaian visi, misi dan tujuan strategis institusi</t>
+  </si>
+  <si>
+    <t>Undana memiliki bukti yang sahih hasil kerja sama memberikan manfaat bagi institusi/program srtudi dalam pemenuhan proses pembelajaran, Penelitian, PKM, dan peningkatan sarana prasarana pendukung</t>
+  </si>
+  <si>
+    <t>Undana memiliki bukti hasil survei kepuasan pemangku kepentingan internal dan eksternal pada kriteria tata pamong dan kerjasama, mahasiswa, sumber daya manusia, keuangan, sarana dan prasarana, pendidikan, penelitian dan pengabdian kepada masyarakat, dipublikasi dan ditindaklanjuti untuk perbaikan dan peningkatan mutu proses pendidikan, penelitian dan pengabdian kepada masyarakat</t>
+  </si>
+  <si>
+    <t>Perguruan tinggi memiliki bukti instrumen survei kepuasan yang digunakan sahih, andal, mudah digunakan, bukti pelaksanaan survei secara berkala, serta datanya terekam secara komprehensif, dianalisis dengan metode yang tepat</t>
+  </si>
+  <si>
+    <t>Standar Penerimaan Mahasiswa Baru</t>
+  </si>
+  <si>
+    <t>Tersedia program kegiatan dan anggaran promosi yang sistimatis untuk menjaring calon mahasiswa berkualitas</t>
+  </si>
+  <si>
+    <t>Tersedianya Dokumen seleksi dan penerimaan mahasiswa baru yang memuat tentang perencanaan, pelaksanaan, pemantauan dan pertanggungjawaban mahasiswa baru (yang bertugas panitian penerimaan mahasiswa baru.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya daftar mahasiswa yang melakukan pendaftaran mahasiswa baru misalnya meliputi nama, nilai raport dll (yang bertugas panitia penerimaan mahasiswa baru) </t>
+  </si>
+  <si>
+    <t>Tersedianya Daftar calon mahasiswa baru yang mengikuti seleksi dan yang dinyatakan lulus dengan ketentuan surat keputusan rector (yang bertugas panitia penerimaan mahasiswa baru)</t>
+  </si>
+  <si>
+    <t>Tersedianya Daftar calon yang dinyatakan lulus seleksi dan melakukan pendaftaran ulang (yang bertugas panitia penerimaan mahasiswa baru)</t>
+  </si>
+  <si>
+    <t>Tersedianya Ketentuan ketetatan seleksi penerimaan mahasiswa baru</t>
+  </si>
+  <si>
+    <t>Mahasiswa Undana berasal dari minimal 7 Provinsi di luar Provinsi NTT</t>
+  </si>
+  <si>
+    <t>Tersedia peraturan Dekan tentang sistem penerimaan mahasiswa baru yang diperbaharui setiap tahun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya peraturan Dekan tentang peluang kepada mahasiswa yang memiliki potensi akademik tetapi tidak mampu secara ekonomi dan cacat fisik </t>
+  </si>
+  <si>
+    <t>Tersedia pedoman seleksi penerimaan mahasiswa baru untuk jalur seleksi mandiri yang diperbaharui setiap tahun</t>
+  </si>
+  <si>
+    <t>Tersedia keputusan Dekan tentang daya tampung program studi</t>
+  </si>
+  <si>
+    <t>Tersedianya Pedoman penerimaan mahasiswa baru yang update dapat diakses di situs web Undana</t>
+  </si>
+  <si>
+    <t>Tersedia keputusan Dekan tentang panitia penerimaan mahasiswa baru untuk semua jenjang dan jalur penerimaan</t>
+  </si>
+  <si>
+    <t>Tersedia sistem informasi penerimaan mahasiswa baru untuk semua jenjang dan jalur penerimaan</t>
+  </si>
+  <si>
+    <t>Mahasiswa baru program sarjana jalur SNMPTN memenuhi kuota minimal 20%</t>
+  </si>
+  <si>
+    <t>Mahasiswa baru program sarjana jalur SBMPTN memenuhi kuota minimal 50%</t>
+  </si>
+  <si>
+    <t>Rasio jumlah mahasiswa yang daftar ulang terhadap jumlah
+mahasiswa yang lulus seleksi pada semua jenjang minimal 95%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rasio jumlah mahasiswa baru transfer terhadap jumlah mahasiswa baru bukan transfer maksimal 25% </t>
+  </si>
+  <si>
+    <t>20% mahasiswa baru berasal dari masyarakat ekonomi lemah</t>
+  </si>
+  <si>
+    <t>Terdapat akses yang memadai untuk mahasiswa berkebutuhan khusus</t>
+  </si>
+  <si>
+    <t>Jumlah mahasiswa baru negara asing maksimal 10% dari daya tampung</t>
+  </si>
+  <si>
+    <t>Tersedia keputusan Dekan tentang kelulusan calon mahasiswa baru semua jenjang dan jalur masuk</t>
+  </si>
+  <si>
+    <t>Tersedia informasi kelulusan calon mahasiswa baru semua jenjang dan jalur masuk di situs web Undana</t>
+  </si>
+  <si>
+    <t>Tersedia laporan umum penerimaan mahasiswa baru Undana setiap tahun</t>
+  </si>
+  <si>
+    <t>Rasio jumlah mahasiswa baru transfer terhadap jumlah mahasiswa baru bukan transfer</t>
+  </si>
+  <si>
+    <t>Tersedia hasil rapat tinjauan manajeman terhadap laporan
+monev penerimaan mahasiswa baru tahun sebelumnya</t>
+  </si>
+  <si>
+    <t>Tersedia laporan monitoring dan evaluasi peleksanaan seleksi
+penerimaan mahasiswa baru yang dilaporkan ke pimpinan Undana</t>
+  </si>
+  <si>
+    <t>Standar Suasana Akademik</t>
+  </si>
+  <si>
+    <t>Tersedianya Sarana dan prasarana yang memadai dalam menunjang pelaksanaan akademik</t>
+  </si>
+  <si>
+    <t>Tersedianya Sarana dan prasarana yang mendukung
+pengembangan bakat, minat mahasiswa</t>
+  </si>
+  <si>
+    <t>Tersedianya Standar etika bagi dosen, mahasiswa dan tenaga
+kependidikan</t>
+  </si>
+  <si>
+    <t>Tersedianya perpustakaan dan kemudahan mengakses</t>
+  </si>
+  <si>
+    <t>Tersedianya Jumlah dan mutu laboratorium yang memadai dan digunakan untuk pengembangan aspek  psikomotorik dan lain-lain</t>
+  </si>
+  <si>
+    <t>Standar Layanan Kemahasiswaan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tersedia pedoman tertulis kebijakan tentang peningkatan mutu mahasiswa baru melalui peningkatan </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>capasity building</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Tersedianya aksesbilitas dan layanan unit pembinaan dan pengembangan bidang bimbingan dan konseling, minat dan bakat, pembinaan soft skills, beasiswa dan kesehatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya instrumen kepuasan mahasiswa terhadap layanan kemahasiswaan yang memenuhi kriteria sahih, andal, mudah digunakan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya laporan hasil survei kepuasan mahasiswa terhadap layanan kemahasiswaan yang dilaksanakan setiap semester dan tindak lanjut </t>
+  </si>
+  <si>
+    <t>Tersedianyan aksesibilitas dan layanan unit pembinaan dan pengembangan bidang: bimbingan dan konseling, minat dan bakat, pembinaan soft skills, beasiswa dan kesehatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya dokumen formal kebijakan dan program terjadwal tentang pemberian layanan bimbingan karir dan informasi kerja bagi mahasiswa serta lulusan, yang mencakupi (1) penyebaran informasi kerja (2)  penyelenggaraan bursa kerja secara berkala  (3) perencanaan karir  (4) pelatihan melamar kerja (5) layanan penempatan kerja. </t>
+  </si>
+  <si>
+    <t>Jumlah seminar/ Pelatihan  yang melibatkan tenaga    profesional  IDUKA (kegiatan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah PKM yang lolos PIMNAS (Kelompok) </t>
+  </si>
+  <si>
+    <t>Persentase mahasiswa yang mengikuti metode pembelajaran pertukaran pelajar dalam Universitas (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah karya mahasiswa disajikan dalam kegiatan ilmiah nasional [selain PIMNAS] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah karya mahasiswa disajikan dalam kegiatan ilmiah internasional </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jumlah mahasiswa yang mengikuti kegiatan </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>future skills platform</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (orang)</t>
+    </r>
+  </si>
+  <si>
+    <t>Standar Pengelolaan Alumni</t>
+  </si>
+  <si>
+    <t>Terbentuknya Organisasi IKA</t>
+  </si>
+  <si>
+    <t>Terjadinya Pertemuan tahunan IKA-Undana</t>
+  </si>
+  <si>
+    <t>Meningkatnya Jumlah partisipasi Alumni Undana, minimal 4 bentuk partisipasi Alumni.</t>
+  </si>
+  <si>
+    <t>Tersedianya Data dan informasi tentang:  (1)  Kepuasan pemakai alumni; (2) laju serapan alumni di pasar kerja ;(3) rata-rata gaji alumni; (4) kesesuaian kompetensi keilmuan dengan bidang kerja; dan (5) sektor bidang kerja</t>
+  </si>
+  <si>
+    <t>Tersedianya Dokumen sistem evaluasi lulusan yang efektif</t>
+  </si>
+  <si>
+    <t>Tersedianya Pedoman studi pelacakan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tersedianya Pangkalan data alumni terintegrasi dengan pangkalan data Universitas Nusa Cendana</t>
+  </si>
+  <si>
+    <t>Tersedianya Program kerja pengelolahan alumni.</t>
+  </si>
+  <si>
+    <t>Standar Kompetensi Lulusan</t>
+  </si>
+  <si>
+    <t>Rumusan kompetensi lulusan prodi mengacu pada KKNI dan kebijakan Merdeka Belajar kampus Merdeka (MBKM).</t>
+  </si>
+  <si>
+    <t>Rata-rata IPK lulusan ≥ 3,43 secara konsisten setiap tahun.</t>
+  </si>
+  <si>
+    <t>100% lulusan prodi memiliki kompetensi sesuai profil (keilmuan, managerial, entrepreneurship) secara kontinu</t>
+  </si>
+  <si>
+    <t>100% lulusan prodi memiliki kompetensi sesuai standar kompetensi lulusan secara kontinu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ≤ 6%  mahasiswa  yang  dropout  atau  mengundurkan  diri setiap tahun akademik.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80% Lulusan yang langsung mendapat  Pekerjaan, melanjutkan Studi, atau menjadi Wiraswasta. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">≥ 50% mahasiswa lulusan mendapatkan pekerjaan pertama kurang dari 6 bulan setelah diwisuda. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">≥ 50% mahasiswa lulus tepat waktu dalam setiap angkatan bulan setelah diwisuda. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">≥ 60%  lulusan  bekerja  sesuai  dengan  bidang  keahliannya secara
+berkelanjutan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">90% pengguna lulusan menilai baik terhadap kualitas lulusan dari aspek integritas (etika dan moral) profesionalisme, kemampuan bahasa Inggris, penggunaan teknologi informasi dan komunikasi, kerjasama dan pengembangan diri secara berkelanjutan. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya pembekalan bagi lulusan untuk memasuki dunia kerja setiap tahun. </t>
+  </si>
+  <si>
+    <t>Standar Isi Pembelajaran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100%    Program    Studi    memiliki kurikulum yang
+mengandung penciri Program Studi secara konsisten setiap tahun. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Program Studi mengimplementasikan Kurikulum Mengacu KKNI dan kebijakan MBKM secara konsisten setiap tahun. </t>
+  </si>
+  <si>
+    <t>100% kurikulum Program Studi memuat mata kuliah pendidikan agama, kewarganegaraan, bahasa Inggris, statistik atau matematika, dan mata kuliah yang
+mengembangkan kepribadian dan kebudayaan secara kontinu</t>
+  </si>
+  <si>
+    <t>100% mata kuliah sesuai dengan standar kompetensi yang telah ditetapkan secara kontinu</t>
+  </si>
+  <si>
+    <r>
+      <t>100% mata kuliah dilengkapi dengan silabus (RPS) secara kontinu dan 35% RPS Mata kuliah memuat metode pembelajaran</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> case method</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> dan/ atau</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> team base project</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Program Studi melakukan peninjauan kembali sebelum merevisi kurikulum secara kontinu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Program Studi dalam menyusun kurikulum melibatkan stakeholder dan alumni dalam setiap peninjauan kurikulum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Program Studi dalam menyusun kurikulum menyesuaikan dengan perkembangan Ipteks dan kebutuhan    stakeholder dalam setiap peninjauan
+kurikulum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Program Studi memiliki beban studi sesuai dengan ketentuan dalam setiap peninjauan kurikulum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Program Studi menjalankan kegiatan akademik sesuai kalender akademik yang telah ditetapkan setiap
+tahun akademik </t>
+  </si>
+  <si>
+    <t>Standar Proses Pembelajaran</t>
+  </si>
+  <si>
+    <t>100% dosen yang berkompetensi menyatakan bersedia dan 100% mata kuliah perkuliahannya terjadwal dan memiliki dengan RPS 100 % mata kuliah terjadwal perkuliahan sesuai dengan RPS.</t>
+  </si>
+  <si>
+    <t>100% mata kuliah dilaksanakan tepat waktu sesuai RPS.</t>
+  </si>
+  <si>
+    <t>100% mahasiswa mampu meraih kompetensi pembelajaran yang diharapkan.</t>
+  </si>
+  <si>
+    <t>100% mahasiswa mengambil beban SKS sesuai dengan
+perolehan Indeks Prestasi Kumulatif (IPK) .</t>
+  </si>
+  <si>
+    <t>Mahasiswa yang memiliki keterlambatan akademik dapat
+mengikuti program semester antara.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% atau 16 kali kehadiran dosen dalam semua mata kuliah sesuai dengan Pedoman Akademik Undana. </t>
+  </si>
+  <si>
+    <t>95% mahasiswa hadir mengikuti setiap mata kuliah yang diprogramkan.</t>
+  </si>
+  <si>
+    <t>100% kehadiran dosen dan mahasiswa dalam kegiatan praktikum setiap mata kuliah</t>
+  </si>
+  <si>
+    <t>100% dosen memberikan tugas mandiri setiap mata kuliah yang diampu.</t>
+  </si>
+  <si>
+    <t>100% mahasiswa menyelesaikan tugas mandiri yang diberikan dosen pengampu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% mata kuliah memiliki tutorial/ response </t>
+  </si>
+  <si>
+    <t>Standar Penilaian Pembelajaran</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang standar penilaian pembelajaran yang merupakan kriteria minimal tentang penilaian proses dan hasil belajar mahasiswa dalam rangka pemenuhan capaian pembelajaran lulusan yang sesuai dan layak untuk setiap prodi secara konsisten yang ditetapkan masing-masing prodi.</t>
+  </si>
+  <si>
+    <t>Terdapat bukti sahih tentang dipenuhinya 5 prinsip penilaian yang dilakukan secara terintegrasi dan dilengkapi dengan rubrik/portofolio penilaian minimum 70% jumlah matakuliah</t>
+  </si>
+  <si>
+    <t>Terdapat bukti sahih yang menunjukkan kesesuaian teknik dan instrumen penilaian terhadap capaian pembelajaran minimum 75% dari jumlah matakuliah</t>
+  </si>
+  <si>
+    <t>Terdapat bukti sahih pelaksanaan penilaian mencakup 7 unsur</t>
+  </si>
+  <si>
+    <t>Terdapat umpan balik perbaikan pembelajaran</t>
+  </si>
+  <si>
+    <t>Tersedianya tim pelaksanaan penilian sesuai dengan kebutuhannya</t>
+  </si>
+  <si>
+    <t>Penetuan nilai akhir hasil belajar mahasiswa dengan konversinya terdapat dalam pedoman penyelenggaraan Pendidikan</t>
+  </si>
+  <si>
+    <r>
+      <t>Presentasi matakuliah yang 50% dari bobot nilai akhir harus berdasarkan kualitas partisipasi diskusi kelas (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>case methods</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)dan atau presentasi akhir </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>project based learning</t>
+    </r>
+  </si>
+  <si>
+    <t>Nilai mata kuliah masuk tepat waktu (3 hari) setelah ujian.</t>
+  </si>
+  <si>
+    <t>Tersedianya Pedoman penyelenggaraan pendidikan memuat tentang :Predikat kelulusan mahasiswa program sarjana : memuaskan (IPK 2.76- 3.00), sangat memuaskan( IPK 3.01- 3.50) , atau pujian (IPK &gt;3.50)</t>
+  </si>
+  <si>
+    <t>Standar Dosen dan Tenaga Kependidikan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undana memiliki kriteria minimal tentang kualifikasi dan kompetensi dari Dosen dan Tenaga Kependidikan yang sesuai dan layak untuk setiap program studi dalam rangka pemenuhan capaian pembelajaran lulusan yang ditetapkan masing-masing program studi. 
+</t>
+  </si>
+  <si>
+    <t>`127</t>
+  </si>
+  <si>
+    <t>100 persen Dosen memiliki kualifikasi akademik dan kompetensi pendidik, sehat jasmani dan rohani, serta memiliki kemampuan untuk menyelenggarakan pendidikan
+dalam rangka pemenuhan capaian pembelajaran lulusan;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 persen Dosen program sarjana harus berkualifikasi akademik paling rendah lulusan magister atau magister terapan yang relevan dengan Program Studi dari Perguruan Tinggi Terakreditasi Baik Sekali
+</t>
+  </si>
+  <si>
+    <t>100 persen Dosen program sarjana harus memiliki sertifikat pendidik (dosen), dan/atau sertifikat profesi yang relevan dengan Program Studi dan berkualifikasi paling rendah setara dengan jenjang 8 (delapan) KKNI.</t>
+  </si>
+  <si>
+    <t>Setiap dosen program sarjana, magister, dan doktor harus mengembangkan pola pembelajaran mata kuliah menggunakan pendekatan kasus dan masalah</t>
+  </si>
+  <si>
+    <t>Undana memiliki penghitungan beban kerja dosen yang didasarkan atas kegiatan pokok dosen yaitu Pendidikan, Penelitian; dan Pengabdian kepada Masyarakat maksimal</t>
+  </si>
+  <si>
+    <t>SKS per semester, kegiatan dalam bentuk pelaksanaan tugas tambahan maskimal 6 SKS per semester; dan kegiatan penunjang 2 SKS per semester.</t>
+  </si>
+  <si>
+    <t>100% Dosen sebagai pembimbing utama dalam penelitian terstuktur dalam rangka penyusunan: skripsi/tugas akhir setidaknya memiliki jabatan akademik lektor</t>
+  </si>
+  <si>
+    <t>Setiap dosen memiliki jumlah mahasiswa bimbingan sebagai pembimbing utama  untuk semua jenjang Pendidikanakademik paling banyak 10 (sepuluh) mahasiswa.</t>
+  </si>
+  <si>
+    <t>Nisbah Dosen dan mahasiswa untuk kelompok sains  1,25</t>
+  </si>
+  <si>
+    <t>Jumlah Dosen tetap pada Perguruan Tinggi paling sedikit 70% (tujuh puluh persen) dari jumlah seluruh dosen yang relevan dengan Program Studi.</t>
+  </si>
+  <si>
+    <t>Jumlah Dosen yang ditugaskan untuk menjalankan proses pembelajaran pada setiap Program Studi paling sedikit 12 (dua belas) orang yang relevan serta tetap memperhatikan nisbah dosen dan mahasiswa.</t>
+  </si>
+  <si>
+    <t>50 % tenaga Kependidikan memiliki kualifikasi  akademik paling rendah lulusan program diploma 3 (tiga) yang dinyatakan dengan ijazah sesuai dengan  kualifikasi  tugas pokok dan fungsinya  serta  telah  memiliki  pengalaman minimal 3 tahun di bidangnya dan menguasai minimal  1 aplikasi (perpustakaan).</t>
+  </si>
+  <si>
+    <t>50 % tenaga administrasi memiliki kualifikasi akademik paling rendah diploma 1 (satu) yang dinyatakan dengan ijazah sesuai dengan kualifikasi tugas pokok dan fungsinya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 % tenaga kependidikan (pustakawan) wajib memiliki sertifikat kompetensi pustakawan sesuai dengan bidang tugas dan keahlian perpustakaan. </t>
+  </si>
+  <si>
+    <t>Standar Sarana dan Prasarana Pembelajaran</t>
+  </si>
+  <si>
+    <t>100% PS memiliki sarana dan prasarana yang memadai sesuai dengan kebutuhan sehingga dapat mewujudkan pembelajaran yang berkualitas</t>
+  </si>
+  <si>
+    <t>100% Sarana dan prasarana yang dimiliki PS mudah untuk diakses sehingga dapat mewujudkan pembelajaran yang berkualitas</t>
+  </si>
+  <si>
+    <t>100% sarana dan prasarana PS dapat digunakan oleh mahasiswa, dosen dan atau tenaga kependidikan yang berkebutuhan khusus</t>
+  </si>
+  <si>
+    <t>100% sarana dan prasarana yang dimiliki oleh program studi memiliki kartu informasi yang memuat catatan mengenai pemeliharaan, perbaikan, pemutakhiran dan penggantian</t>
+  </si>
+  <si>
+    <t>100% sarana dan prasarana memiliki dokumen standar prosedur operasional sehingga meningkatkan efektifitas dan efisiensi penggunaan</t>
+  </si>
+  <si>
+    <t>Tersedia dokumen kebijakan pengelolaan sarana dan prasarana</t>
+  </si>
+  <si>
+    <t>100% mahasiswa memperoleh sosialisasi dan atau pelatihan serta memahami teknik penggunaan sarana dan prasarana yang dimiliki PS</t>
+  </si>
+  <si>
+    <t>Tersedia rencana dasar (master plan) dan rencana pengembangannya terhadap infrastruktur fasilitas fisik yang meliputi gedung dan lab, alat transportasi, sarana seni, olahraga, dan fasilitas lainnya</t>
+  </si>
+  <si>
+    <t>100% ruang perkuliahan memiliki sarana penunjang pembelajaran minimal papan tulis dan LCD</t>
+  </si>
+  <si>
+    <t>Tersedia laboratorium untuk menunjang proses pembelajaran dengan peralatan yang lengkap sebagaimana dipersyaratkan</t>
+  </si>
+  <si>
+    <t>Setiap Fakultas memiliki prasana gedung dan halaman yang memadai untuk menunjang proses pembelajaran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedia fasilitas internet yang lancar dan dapat diakses dengan mudah oleh sivitas akademika </t>
+  </si>
+  <si>
+    <t>Standar Pengelolaan Pembelajaran</t>
+  </si>
+  <si>
+    <t>Tersedia laporan pengelolaan pembelajaran sesuai siklus PPEPP setiap semester dan ditindaklanjuti di tingkat program studi dan UPPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% kegiatan pengelolaan pembelajaran harus menjamin bahwa pengelolaan pembelajaran mengacu pada:standar kompetensi lulusan, standar isi pembelajaran, standar proses pembelajaran, standar dosen dan tenaga kependidikan serta standar sarana dan prasarana </t>
+  </si>
+  <si>
+    <t>100% kegiatan pengelolaan pembelajaran dosen di evaluasi secara internal oleh GKM/GPM pada setiap semester</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengelolaan pembelajaran mahasiswa dibimbing dan di MONEV oleh dosen yang berkompeten di bidangnya pada setiap semester</t>
+  </si>
+  <si>
+    <t>Tersedia rekomendasi tindak lanjut dari hasil Monev secara
+periodik</t>
+  </si>
+  <si>
+    <t>Jumlah Program Studi yang menyelenggarakan Sistem Layanan pembelajaran multi media teritegrasi (elearning,)</t>
+  </si>
+  <si>
+    <t>Persentase mahasiswa yang mengikuti metode pembelajaran luar universitas dan konsep merdeka belajar (8 kegiatan: magang/praktik, proyek desa, pertukaran pelajar, penelitian, kegiatan wirausaha, studi proyek independent, proyek
+kemanusisan,)</t>
+  </si>
+  <si>
+    <t>Persentase MK yang menerapkan metode Pembelajaran pemecahan kasus dan berbasis Proyek</t>
+  </si>
+  <si>
+    <t>Tersedia bahan ajar berbasis Penelitian dan Pengabdian untuk Inovasi Pengembangan Pembelajaran</t>
+  </si>
+  <si>
+    <t>Presentasi prodi penyelengaraan SPMI Pembelajaran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentasi Program Studi yang sudah melakukan penyesuaian kurikulum untuk penyelenggaraan pendidikan wirausaha </t>
+  </si>
+  <si>
+    <t>Standar Pembiayaan Pembelajaran</t>
+  </si>
+  <si>
+    <t>100% Program Studi  memiliki DOP (Dana Operasional Pendidikan)  Rata-rata  dana operasional pendidikan/ mahasiswa/ tahun (dalam juta rupiah), Ratarata dana PKM dosen (DPKMD)/ tahun dalam 3 tahun terakhir</t>
+  </si>
+  <si>
+    <t>100% Program Studi  memiliki Realisasi investasi (SDM, sarana dan prasarana) memenuhi seluruh kebutuhan akan penyelenggaraan program pendidikan, penelitian dan PKM serta memenuhi standar perguruan tinggi terkait pendidikan, penelitian dan PKM</t>
+  </si>
+  <si>
+    <t>100% Program Studi memiliki Kecukupan dana untuk menjamin pengembangan tridharma</t>
+  </si>
+  <si>
+    <t>Standar Hasil Penelitian</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang mutu hasil penelitian yang memenuhi kaidah dan metode ilmiah secara sistematis sesuai otonomi keilmuan dan budaya akademik.</t>
+  </si>
+  <si>
+    <t>Hasil penelitian peneliti di Undana 100% diarahkan dalam rangka mengembangkan ilmu pengetahuan dan teknologi, serta meningkatkan kesejahteraan masyarakat dan daya saing bangsa secara konsisten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasil penelitian mahasiswa 100% harus memenuhi ketentuan dalam rangka mengembangkan ilmu pengetahuan dan teknologi, serta meningkatkan kesejahteraan masyarakat dan daya saing bangsa, capaian pembelajaran lulusan, dan ketentuan peraturan di Undana secara konsisten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasil penelitian peneliti di Undana 100% tidak bersifat rahasia, tidak mengganggu dan/atau tidak membahayakan kepentingan umum atau nasional wajib disebarluaskan dengan cara diseminarkan, dipublikasikan, dipatenkan,
+dan/atau cara lain yang dapat digunakan untuk  menyampaikan hasil Penelitian kepada masyarakat pada tingkat nasional dan internasional. </t>
+  </si>
+  <si>
+    <t>Hasil penelitian 100 % dapat dilaporkan tepat waktu setiap tahun.</t>
+  </si>
+  <si>
+    <t>Hasil penelitian para peneliti dosen 100% didiseminasikan dalam kerangka mempertanggungjawabkan dan menyebarluaskan hasil penelitiannya setiap tahun.</t>
+  </si>
+  <si>
+    <t>Hasil penelitian 100% memenuhi persyaratan sesuai pedoman yang berlaku dan memenuhi luaran wajib sesuai kontrak yang berlaku.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasil penelitian lainnya dari peneliti dosen 100% dapat berupa buku ajar, teknologi tepat guna, rekayasa sosial, model, dan atau kebijakan. </t>
+  </si>
+  <si>
+    <t>Standar Isi Penelitian</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang kedalaman dan keluasan materi baik penelitian dasar maupun penelitian terapan.</t>
+  </si>
+  <si>
+    <t>Materi pada Penelitian dasar 100% harus berorientasi pada luaran Penelitian yang berupa penjelasan atau penemuan untuk mengantisipasi suatu gejala, fenomena, kaidah, model, atau postulat baru mencakup materi kajian khusus untuk
+kepentingan nasional.</t>
+  </si>
+  <si>
+    <t>Materi pada Penelitian terapan 100% harus berorientasi pada luaran Penelitian yang berupa inovasi serta pengembangan ilmu pengetahuan dan teknologi yang bermanfaat bagi masyarakat, dunia usaha, dan/atau industry mencakup materi kajian khusus untuk kepentingan nasional.</t>
+  </si>
+  <si>
+    <t>Materi pada penelitian dasar dan penelitian terapan 100% harus memuat prinsip-prinsip kemanfaatan, kemutahiran, dan mengantisipasi kebutuhan masa mendatang.</t>
+  </si>
+  <si>
+    <t>Penelitian yang diusulkan mahasiswa dan dosen peneliti 100% merujuk pada peta jalan penelitian Prodi dalam payung peta jalan penelitian di Fakultas masing-masing dan Rencana Induk Pengembangan LP2M Undana secara konsisten.</t>
+  </si>
+  <si>
+    <t>setiap kegiatan penelitian dosen dengan bidang ilmu sesuai dengan Prodi menjadi rujukan tema tesis/disertasi mahasiswa program studi secara konsisten dan berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Standar Proses Penelitian</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang kegiatan Penelitian yang terdiri atas perencanaan, pelaksanaan, dan pelaporan yang merupakan kegiatan yang memenuhi kaidah dan metode ilmiah secara sistematis sesuai dengan otonomi
+keilmuan dan budaya akademik.</t>
+  </si>
+  <si>
+    <t>Setiap kegiatan penelitian harus mempertimbangkan standar mutu, keselamatan kerja, kesehatan, kenyamanan, serta keamanan peneliti, masyarakat, dan lingkungan secara konsisten.</t>
+  </si>
+  <si>
+    <t>Setiap kegiatan Penelitian yang dilakukan oleh mahasiswa dalam rangka melaksanakan tugas akhir, skripsi, tesis, atau disertasi harus memenuhi ketentuan capaian pembelajaran lulusan, dan ketentuan peraturan di Undana secara konsisten.</t>
+  </si>
+  <si>
+    <t>Setiap kegiatan Penelitian yang dilakukan oleh mahasiswa dinyatakan dalam besaran Satuan Kredit Semester sesuai level KKNI secara konsisten.</t>
+  </si>
+  <si>
+    <t>Setiap kegiatan Penelitian dosen dan mahasiswa melaksanakan penelitian sesuai dengan agenda penelitian dosen yang merujuk kepada peta jalan penelitian.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setiap kegiatan penelitian dosen yang bidang keilmuannya sesuai dengan Prodi dalam pelaksanaannya melibatkan mahasiswa program studi untuk percepatan masa studi secara berkelanjutan </t>
+  </si>
+  <si>
+    <t>Standar Penilaian Penelitian</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang penilaian terhadap proses dan hasil penelitian.</t>
+  </si>
+  <si>
+    <t>Penilaian terhadap proses dan hasil penelitian dilakukan secara terintegrasi paling sedikit memenuhi unsur: edukatif, akuntabel dan transparan.</t>
+  </si>
+  <si>
+    <t>Penilaian proses dan hasil penelitian harus memenuhi prinsip penilaian dan memperhatikan kesesuaian dengan standar hasil, standar isi, dan standar proses penelitian.</t>
+  </si>
+  <si>
+    <t>Penilaian penelitian dapat dilakukan dengan menggunakan metode dan instrumen yang relevan, akuntabel, dan dapat mewakili ukuran ketercapaian kinerja proses serta pencapaian kinerja hasil penelitian.</t>
+  </si>
+  <si>
+    <t>Penilaian penelitian yang dilaksanakan oleh mahasiswa dalam rangka penyusunan laporan tugas akhir, skripsi, tesis, atau disertasi diatur berdasarkan ketentuan peraturan di Undana secara konsisten.</t>
+  </si>
+  <si>
+    <t>Dilakukan evaluasi kesesuaian penelitian dosen dan mahasiswa dengan peta jalan penelitian Prodi, Fakultas dan Rencana Induk Pengembangan Penelitian LP2M Undana</t>
+  </si>
+  <si>
+    <t>Setiap peneliti untuk menggunakan hasil evaluasi untuk perbaikan relevansi penelitian dan pengembangan keilmuan program studi.</t>
+  </si>
+  <si>
+    <t>Penilaian terhadap penelitian dosen menggunakan panduan penilaian penelitian dan instrumen penilaian secara konsisten.</t>
+  </si>
+  <si>
+    <t>Penilaian terhadap penelitian yang dilaksanakan oleh mahasiswa dalam rangka penyusunan laporan tugas akhir, skripsi, tesis, atau disertasi sesuai dengan pedoman akademik Undana</t>
+  </si>
+  <si>
+    <t>Standar Peneliti</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang kemampuan peneliti untuk melaksanakan penelitian.</t>
+  </si>
+  <si>
+    <t>Peneliti di Undana memiliki kemampuan tingkat penguasaan metodologi penelitian yang sesuai dengan bidang keilmuan, objek penelitian, serta tingkat kerumitan dan tingkat kedalaman penelitian yang yang ditentukan berdasarkan kualifikasi akademik dan hasil penelitian.</t>
+  </si>
+  <si>
+    <t>Kewenangan melaksanakan penelitian dengan mengacu pada pedoman yang ditetapkan oleh Direktur Jenderal Penguatan Riset dan Pengembangan.</t>
+  </si>
+  <si>
+    <t>Peneliti sebagai ketua ataupun anggota memiliki syarat kepangkatan dan fungsional yang ditentukan untuk melaksanakan penelitian secara berkelanjutan</t>
+  </si>
+  <si>
+    <t>Peneliti sebagai ketua ataupun anggota mempunyai peta kegiatan penelitian atau rekam jejak (roadmap) yang jelas dan relevan dengan bidang ilmu yang dikembangkannya secara konsisten.</t>
+  </si>
+  <si>
+    <t>Standar Sarana dan Prasarana Penelitian</t>
+  </si>
+  <si>
+    <t>Tersedia Sarana dan prasarana penelitian dan laboratoium yang menunjang proses pembelajaran/praktikum, dan kebutuhan standar isi, standar proses penelitian dalam rangka memenuhi standar hasil penelitian</t>
+  </si>
+  <si>
+    <t>Sarana prasarana penelitian, laboratorium memenuhi standar mutu, dan standar Kesehatan dan keselamatan kerja dan lingkungan secara konsisten</t>
+  </si>
+  <si>
+    <t>Tersedianya peraturan Dekan dan panduan, SOP pengelolaan, perawaran dan revitalisasi sarana prasarana penelitian dan laboratorium</t>
+  </si>
+  <si>
+    <t>Tersedia jadwal Perawatan sarana dan prasarana penelitian di lingkungan Undana</t>
+  </si>
+  <si>
+    <t>Terlaksana revitalisasi dan perawatan sarana prasarana penelitian dan laboratorium sesuai standar mutu penelitian internasional</t>
+  </si>
+  <si>
+    <t>80% penelitian Dasar, Terapan dan penelitian Pengembangan menggunakan sarana dan prasarana penelitian internal</t>
+  </si>
+  <si>
+    <t>100% program studi memiliki laboratorium yang mendukung penelitian</t>
+  </si>
+  <si>
+    <t>100% pendapatan yang bersumber dari penggunaan sarana prasarana penelitian dan laboratorium</t>
+  </si>
+  <si>
+    <t>Standar Pengelolaan Penelitian</t>
+  </si>
+  <si>
+    <t>Tersedia dokumen formal perencanaan, pelaksanaan, pengendalian, pemantauan dan evaluasi, serta pelaporan kegiatan penelitian setiap tahun</t>
+  </si>
+  <si>
+    <t>Tersedia panduan penelitian yang mengacu pada standar mutu penelitian Undana</t>
+  </si>
+  <si>
+    <t>Tersedia rencana induk penelitian yang memuat rencana jangka pendek, jangka menengah dan jangka Panjang</t>
+  </si>
+  <si>
+    <t>Tersedia system informasi penelitiian yang dapat diakses oleh pemangku kepentingan internal dan eksternal</t>
+  </si>
+  <si>
+    <t>Tersedia kriteria dan prosedur penilaian paling sedikit menyangkut aspek peningkatan jumlah publikasi ilmiah, penemuan baru di bidang ilmu pengetahuan dan teknologi,dan jumlah dan mutu bahan ajar berbasis hasil penelitian</t>
+  </si>
+  <si>
+    <t>Tersedianya laporan pelaksanaan PPEPP penelitian setiap tahun</t>
+  </si>
+  <si>
+    <t>Tersedia laporan audit mutu penelitian setiap tahun</t>
+  </si>
+  <si>
+    <t>Terlaksana diseminasi hasil penelitian di forum nasional atau internasional sesuai jadwal</t>
+  </si>
+  <si>
+    <t>Tersedia system seleksi, penilaian dan pemberian penghargaan kepada peneliti berprestasi.</t>
+  </si>
+  <si>
+    <t>Terlaksana kegiatan seleksi, dan pemberian penghargaan secara kontinyu setiap tahun</t>
+  </si>
+  <si>
+    <t>Tersedia informasi penyelenggaraan penelitian pada sistem informasi penelitian dan pangkalan data PT</t>
+  </si>
+  <si>
+    <t>Standar Pendanaan dan Pembiayaan Penelitian</t>
+  </si>
+  <si>
+    <t>Tersedianya anggaran penelitian untuk membiayai manajemen penelitian, peningkatan kapasitas peneliti dan insentif publikasi, HaKI, Paten</t>
+  </si>
+  <si>
+    <t>Tersedia mekanisme dan pedoman pembiayaan penelitian</t>
+  </si>
+  <si>
+    <t>Tersedia dana untuk penelitian dosen bersama mahasiswa</t>
+  </si>
+  <si>
+    <t>Ratio dana penelitian yang bersumber dari pendanaan penelitain lainnya terhadap total penerimaan dana Undana</t>
+  </si>
+  <si>
+    <t>Tersedia dokumen pedoman pelaksanaan penelitian mandiri bagi dosen Undana</t>
+  </si>
+  <si>
+    <t>Standar Hasil Pengabdian</t>
+  </si>
+  <si>
+    <t>100% hasil pengabdian dosen dan mahasiswa terdokumentasi di Repository Undana setiap tahun.</t>
+  </si>
+  <si>
+    <t>Hasil pengabdian kepada masyarakat dosen dan mahasiswa dapat: a. dimanfaatkan untuk pengayaan pembelajaran dan penelitian; b. diterapkan langsung oleh masyarakat pengguna; c. dimanfaatkan untuk meningkatkan taraf hidup, kesejahteraan masyarakat, dan pemberdayaan masyarakat; d. dimanfaatkan sebagai model pemecahan masalah, rekayasa sosial; e. diterapkan langsung oleh masyarakat, dunia usaha, industri, dan/atau Pemerintah dan atau f. dapat direkognisi secara nasional atau internasional.</t>
+  </si>
+  <si>
+    <t>Standar Isi Pengabdian</t>
+  </si>
+  <si>
+    <t>100% kedalaman dan keluasan isi pengabdian kepda masyarakat sesuai dan bersumber dari hasil penelitian atau pengembangan ilmu pengetahuan dan teknologi yang sesuai dengan kebutuhan masyarakat</t>
+  </si>
+  <si>
+    <t>50% kegiatan pengabdian dosen dan mahasiswa dapat memecahkan masalah di masyarakat dan selaras dengan kebijakan merdeka belajar-kampus merdeka</t>
+  </si>
+  <si>
+    <t>100% hasil pengabdian oleh dosen dan mahasiswa telah sesuai dengan road map pengabdian universitas dan fakultas</t>
+  </si>
+  <si>
+    <t>Standar Proses Pengabdian</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian dosen dan mahasiswa melalui proses yang benar dan bermutu sesuai pedoman yang berlaku setiap tahun.</t>
+  </si>
+  <si>
+    <t>100% proses pengabdian oleh dosen dan mahasiswa dapat berjalan dengan baik dan dapat dipertanggungjawabkan setiap tahun.</t>
+  </si>
+  <si>
+    <t>Standar Penilaian Pengabdian</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian dosen dan mahasiswa relevan dengan peta jalan pengabdian sesuai bidang keilmuan PS pada tahun 2025</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian dosen dan mahasiswa telah direview oleh Reviewer yang telah ditunjuk dan berkompeten pada tahun 2025</t>
+  </si>
+  <si>
+    <t>100% proses dan hasil pengabdian dosen dan mahasiswa telah melalui penilaian sesuai instrumen yang tersedia pada tahun 2025</t>
+  </si>
+  <si>
+    <t>Standar Pelaksana Pengabdian</t>
+  </si>
+  <si>
+    <t>Undana memiliki kriteria minimal tentang kemampuan pelaksana berdasarkan kualifikasi akademik dan hasil pengabdian kepada masyarakat untuk melaksanakan Pengabdian kepada Masyarakat.</t>
+  </si>
+  <si>
+    <t>Pelaksana Pengabdian kepada Masyarakat wajib memiliki penguasaan metodologi penerapan keilmuan yang sesuai dengan bidang keahlian, jenis kegiatan, serta tingkat kerumitan dan kedalaman sasaran kegiatan</t>
+  </si>
+  <si>
+    <t>Kemampuan pelaksana Pengabdian kepada Masyarakat untuk menentukan kewenangan melaksanakan Pengabdian kepada Masyarakat secara konsisten.</t>
+  </si>
+  <si>
+    <t>Pedoman mengenai kewenangan melaksanakan Pengabdian kepada Masyarakat ditetapkan oleh Direktur Jenderal Penguatan Riset dan Pengembangan.</t>
+  </si>
+  <si>
+    <t>Pelaksana PkM mempublikasikan hasil PkM pada jurnal nasional.</t>
+  </si>
+  <si>
+    <t>Standar Sarana dan Prasarana Pengabdian</t>
+  </si>
+  <si>
+    <t>100% Program studi memiliki sarana dan prasarana pengabdian yang memenuhi syarat pada tahun 2025.</t>
+  </si>
+  <si>
+    <t>100% Program studi memiliki minimal 1 desa binaan pada tahun 2025</t>
+  </si>
+  <si>
+    <t>100% Program studi memiliki minimal 10 kelompok mitra binaan pada tahun 2025</t>
+  </si>
+  <si>
+    <t>100% Desa Binaan Program studi di Undana memiliki anggaran operasional pada tahun 2025</t>
+  </si>
+  <si>
+    <t>Standar Pengelolaan Pengabdian</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian relevan dengan peta jalan pengabdian sesuai bidang keilmuan PS setiap tahun.</t>
+  </si>
+  <si>
+    <t>100% proses dan hasil pengabdian oleh dosen dan mahasiswa telah melalui penilaian sesuai instrumen yang tersedia pada tahun 2025</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian dosen di MONEV secara internal oleh LP2M setiap tahun</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian mahasiswa dibimbing dan di MONEV oleh 1 orang dosen yang berkompeten di bidangnya setiap tahun</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian dosen tercatat di SINTA setiap tahun</t>
+  </si>
+  <si>
+    <t>Standar Pembiayaan Pengabdian</t>
+  </si>
+  <si>
+    <t>100% Program Studi memiliki anggaran DIPA untuk pengabdian minimal 2 kegiatan pengabdian yang berkelanjutan pada tahun 2025</t>
+  </si>
+  <si>
+    <t>100% Program Studi memiliki dana pengabdian minimal 10 juta/dosen secaraberkelanjutan pada tahun 2025</t>
+  </si>
+  <si>
+    <t>2% dosen dan 0.1% mahasiswa dapat mempublikasikan hasil pengabdiannya pada jurnal internasional pada tahun 2025</t>
+  </si>
+  <si>
+    <t>2% dosen dan 0.1% mahasiswa dapat melaksanakan pengabdiannya pada tingkat internasional pada tahun 2025</t>
+  </si>
+  <si>
+    <t>Standar Pembelajaran Merdeka Belajar Kampus Merdeka Universitas Nusa Cendana</t>
+  </si>
+  <si>
+    <t>Tersedia standar pembelajaran MBKM Undana yang selaras dengan SN Dikti dan Panduan Nasional MBKM</t>
+  </si>
+  <si>
+    <t>Minimal 30% Mahasiswa undana terlibat dalam pembelajaran MBKM setiap tahun</t>
+  </si>
+  <si>
+    <t>Tersedianya dokumen Pedoman Program MBKM universitas</t>
+  </si>
+  <si>
+    <t>Tersedia pedoman pengembangan MBKM dan kurikulum MBKM di tingkat fakultas</t>
+  </si>
+  <si>
+    <t>Tersedia mitra MBKM dalam jumlah cukup dan memenuhi persyaratan yang ditetapkan</t>
+  </si>
+  <si>
+    <t>Terlaksananya sosialisasi pelaksanaan MBKM kepada seluruh pemangku kepentingan setiap periode pelaksanaan MBKM</t>
+  </si>
+  <si>
+    <t>Terlaksananya joint kurikulum antara program studi dan mitra dengan pendampingan dari LP3M</t>
+  </si>
+  <si>
+    <t>100 % mahasiswa mendapat pembimbingan dari dosen pembimbing lapangan selama pelaksanaan pembelajaran di luar kampus</t>
+  </si>
+  <si>
+    <t>100% pelaksanaan pembelajaran MBKM sesuai dengan standar mutu pembelajaran yang ditetapkan</t>
+  </si>
+  <si>
+    <t>Standar Luaran Dharma Pendidikan</t>
+  </si>
+  <si>
+    <t>Rata-rata IPK lulusan ≥ 3,30 pada tahun 2025.</t>
+  </si>
+  <si>
+    <t>0.1% mahasiswa memperoleh prestasi internasional pada tahun 2025</t>
+  </si>
+  <si>
+    <t>masa studi lulusan ≥3.5 tahun atau &lt;4.5 tahun pada tahun 2025</t>
+  </si>
+  <si>
+    <t>Rata-rata lulusan mendapat pekerjaan pertama kurang dari 6 bulan setelah diwisuda.</t>
+  </si>
+  <si>
+    <t>≥ 50% mahasiswa lulus tepat waktu pada tahun 2025.</t>
+  </si>
+  <si>
+    <t>≥60% lulusan berkerja sesuai dengan bidang keilmuannya, melanjutkan studi, berwirausaha, dan 20 % lulusan menyelesaikan miniimal 20 SKS di luar (C) secara berkelanjutan.</t>
+  </si>
+  <si>
+    <t>≥5% lulusan bekerja di badan usaha tingkat multinasional/internasional pada tahun 2025</t>
+  </si>
+  <si>
+    <t>90% pengguna lulusan menilai baik terhadap kualitas lulusan dari aspek integritas (etika dan moral) profesionalisme, kemampuan bahasa Inggris, penggunaan teknologi informasi dan komunikasi, kerjasama dan pengembangan diri secara berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Standar Luaran dan Capaian Penelitian Dosen</t>
+  </si>
+  <si>
+    <t>100% Program Studi dapat memiliki minimal 1 paten/HKI pengabdian dosen pada Tahun 2025.</t>
+  </si>
+  <si>
+    <t>20% dosen PS dapat melakukan publikasi hasil pengabdian di jurnal internasional, 80% dijurnal nasional pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>100% hasil pengabdian dosen Program Studi dapat melakukan publikasi hasil pengabdian di media cetak/online internasional/nasiona/lokal serta youtube pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>Hasil pengabdian dosen PS dapat dipublikasi dalam bentuk buku berISBN atau Book Chapter minimal 5 buku secara berkelanjutan pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>80% mitra memberikan penilaian “baik” pada tahun 2025</t>
+  </si>
+  <si>
+    <t>80% hasil pengabdian dosen merupakan inovasi yang diadopsi oleh masyarakat/DUDI pada tahun 2025</t>
+  </si>
+  <si>
+    <t>kegiatan pengabdian dosen melibatkan mahasiswa &gt;30% setiap tahun</t>
+  </si>
+  <si>
+    <t>Standar Luaran dan Capaian Pengabdian Mahasiswa</t>
+  </si>
+  <si>
+    <t>100% kegiatan pengabdian mahasiswa Program Studi sesuai/relevan dengan peta jalan pengabdian Fakultas pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>20% Program studi dapat memiliki minimal 1 paten/HKI pengabdian mahasiswa pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>2% mahasiswa Program Studi dapat melakukan publikasi hasil pengabdian di jurnal internasional, 10% dijurnal nasional, 50% dijurnal lokal pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>100% hasil pengabdian mahasiswa Program Studi dapat melakukan publikasi hasil pengabdian di media cetak/online internasional/nasional /lokal serta youtube pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>Hasil pengabdian mahasiswa Program Studi dapat dipublikasi dalam bentuk buku berISBN atau Book Chapter minimal 5 buku secara berkelanjutan pada Tahun 2025</t>
+  </si>
+  <si>
+    <t>80% mitra menberikan penilaian “baik” pada tahun 2025</t>
+  </si>
+  <si>
+    <t>80% hasil pengabdian mahasiswa diadopsi oleh masyarakat/DUDI pada Tahun 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persentase mahasiswa minimal menyelesaikan 20 SKS di luar dan mendapatkan perhargaan nasional (PIMNAS) melalui KKN Tematik, Magang, Program Kreativitas mahasiswa di tingkat masyarakat/DUDI
+</t>
+  </si>
+  <si>
+    <t>100% Program Studi dapat memiliki minimal 1 paten/HKI Penelitian pada Tahun 2025.</t>
+  </si>
+  <si>
+    <t>20% dosen Program Studi dapat melakukan publikasi hasil pengabdian di jurnal internasional, 80% dijurnal nasional pada Tahun2025.</t>
+  </si>
+  <si>
+    <t>100% hasil Penelitian Program Studi dapat melakukan publikasi hasil pengabdian di media cetak/online internasional/nasiona/lokal serta youtube pada Tahun 2025.</t>
+  </si>
+  <si>
+    <t>Hasil Penelitian Program Studi dapat dipublikasi dalam bentuk buku berISBN atau Book Chapter minimal 5 buku secara berkelanjutan pada Tahun 2025.</t>
+  </si>
+  <si>
+    <t>80% hasil Penelitian merupakan inovasi yang diadopsi oleh masyarakat/DUDI pada Tahun 2025.</t>
+  </si>
+  <si>
+    <t>Kegiatan Penelitian melibatkan mahasiswa &gt;30% setiap tahun.</t>
+  </si>
+  <si>
+    <t>Standar Laboratorium/ Bengkel / Studio</t>
+  </si>
+  <si>
+    <t>Kondisi fisik laboratorium/ bengkel/ studio sudah baik dalam mendukung pelaksanaan praktikum, penelitian atau pengabdian kepada masyarakat</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki instalasi listrik, tegangan listrik, lampu penerangan, proteksi tegangan yang layak untuk mendukung kelancaran praktikum, penelitian atau pengabdian kepada masyarakat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratorium/bengkel/ studio sudah memiliki ruang staff, ruang bekerja dan ruang khusus (ruang persiapan, ruang peralatan, ruang penyimpanan, gudang, atau ruang asam) sesuai kebutuhan
+</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki kelengkapan meja, kursi, laci, papan tulis dan proyektor untuk menunjang kegiatan praktikum dan penelitian mahasiswa</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah tersedia lemari alat-alat gelas, lemari alat-alat optik, lemari bahan/zat.</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah dilengkapi AC/fan/exhause sesuai kebutuhan ruang/alat-alat tertentu.</t>
+  </si>
+  <si>
+    <t>Alat laboratorium/ bengkel/studio layanan jasa sudah terkalibrasi untuk pengujian yang sesuai</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki daftar inventarisasi peralatan laboratorium/bengkel/studio yang dilengkapi dengan nama, spesifikasi, kegunaan, sumber pengadaan, tahun diperoleh, kondisi terakhir perlatan</t>
+  </si>
+  <si>
+    <t>Untuk mempetahankan umur alat dan akurasi pengukuran sudah dilakukan pemeliharaan secara berkala dan ketersediaan suku cadang yang diperlukan</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio menyediakan zat/bahan untuk keperluan praktikum dan penelitian mahasiswa.</t>
+  </si>
+  <si>
+    <t>Sistem organisasi laboratorium/bengkel/studio sudah menjamin pengelolaan laboratorium dapat berjalan dengan lancar.</t>
+  </si>
+  <si>
+    <t>Terlaksananya semua ketentuan praktikum mencakup:.memakai.jas lab/baju bengkel,menjaga kebersihan peralatan/meja, kerapian susunan kursi,
+pemakaian listrik dan air oleh praktikan (mahasiswa).</t>
+  </si>
+  <si>
+    <t>Terlaksananya ketentuan layanan jasa pihak eksternal dalam lingkungan Fakultas Sains dan Teknik Undana dan luar lingkungan Fakultas Sains dan Teknik Undana yang mencakup jenis layanan, administrasi, prosedur dan pertanggungjawaban keuangan.</t>
+  </si>
+  <si>
+    <t>Pemakaian laboratorium/ bengkel/studio diluar jam kantor termasuk pada
+hari libur/bermalam sudah memiliki prosedur yang jelas dan dipertanggungjawabkan.</t>
+  </si>
+  <si>
+    <t>Laboratorium/ bengkel/ studio sudah memiliki laboran/analis/teknisi.</t>
+  </si>
+  <si>
+    <t>Laboran/analis/teknisi laboratorium/bengkel/studio sudah mendapat pelatihan pengembangan untuk jenis layanan dan operasional peralatan yang sesuai</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki agenda layanan praktikum mencakup dosen penanggungjawab, analis/ teknisi dan mahasiswa yang bertugas serta daftar mahasiswa yang praktikum di laboratorium/bengkel/
+studio.</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki daftar kegiatan penelitian dosen mencakup judul, sumber dana, jumlah biaya, mahasiswa yang dilibatkan di laboratorium/bengkel/ studio.</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki daftar kegiatan pengabdian kepada masyarakat yang dilakukan oleh dosen mencakup judul, masyarakat sasaran, sumberdana, jumlah biaya, mahasiswa yang dilibatkan</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki SOP dan instruksi kerja untuk pemakaian peralatan.</t>
+  </si>
+  <si>
+    <t>Laboratorium/bengkel/ studio sudah memiliki Penuntun Praktikum untuk semua matakuliah yang dilayani di laboratorium/ bengkel/ studio.</t>
+  </si>
+  <si>
+    <t>Terpeliharanya Kebersihan lingkungan laboratorium /bengkel/studio</t>
+  </si>
+  <si>
+    <t>Tersedianya pembuangan zat berbahaya/pencemar lingkungan sehingga kesehatan lingkungan di sekitarnya terjaga dengan baik</t>
+  </si>
+  <si>
+    <t>Tersedianya instalasi pengolahan limbah laboratorium di setiap laboratorium/bengkel/studio di lingkungan Fakultas Sains dan Teknik Undana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersedianya alat pemadam kebakaran di laboratorium/bengkel/studio yang berfungsi dan dapat dioperasikan.
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +1469,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1078,6 +2302,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1117,20 +2365,137 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1141,161 +2506,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1851,6 +3075,48 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1501140</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>155363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63C0C07F-EB9B-458E-A760-97B6E3590392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2520950" y="32619950"/>
+          <a:ext cx="1501140" cy="1361863"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2674,7 +3940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N342"/>
+  <dimension ref="A1:N360"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.54296875" style="1" customWidth="1"/>
@@ -2697,67 +3963,67 @@
       <c r="A1" s="78"/>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="147"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="80"/>
-      <c r="D2" s="148" t="s">
+      <c r="D2" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="149"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="91"/>
     </row>
     <row r="3" spans="1:14" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
-      <c r="D3" s="150" t="s">
+      <c r="D3" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
-      <c r="L3" s="150"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="151"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="80"/>
-      <c r="D4" s="152" t="s">
+      <c r="D4" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="152"/>
-      <c r="L4" s="152"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="153"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="95"/>
     </row>
     <row r="5" spans="1:14" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="80"/>
@@ -2795,114 +4061,114 @@
       <c r="A7" s="81"/>
       <c r="B7" s="82"/>
       <c r="C7" s="82"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="89"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="97"/>
     </row>
     <row r="8" spans="1:14" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
     </row>
     <row r="9" spans="1:14" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="91"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
     </row>
     <row r="10" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="102" t="s">
+      <c r="D10" s="104"/>
+      <c r="E10" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="109"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="109"/>
+      <c r="L10" s="109"/>
+      <c r="M10" s="109"/>
+      <c r="N10" s="109"/>
     </row>
     <row r="11" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="93"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="92" t="s">
+      <c r="A11" s="101"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="103" t="s">
+      <c r="F11" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="104"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="101" t="s">
+      <c r="G11" s="111"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="101" t="s">
+      <c r="J11" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="101" t="s">
+      <c r="K11" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="101" t="s">
+      <c r="L11" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="101" t="s">
+      <c r="M11" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="101" t="s">
+      <c r="N11" s="113" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="94"/>
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="102"/>
       <c r="F12" s="73" t="s">
         <v>13</v>
       </c>
@@ -2912,12 +4178,12 @@
       <c r="H12" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="101"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="23">
@@ -2964,10 +4230,10 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="157">
+      <c r="A14" s="114">
         <v>1</v>
       </c>
-      <c r="B14" s="158"/>
+      <c r="B14" s="115"/>
       <c r="C14" s="26"/>
       <c r="D14" s="3"/>
       <c r="E14" s="27"/>
@@ -2982,8 +4248,8 @@
       <c r="N14" s="29"/>
     </row>
     <row r="15" spans="1:14" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="157"/>
-      <c r="B15" s="159"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="116"/>
       <c r="C15" s="26"/>
       <c r="D15" s="11"/>
       <c r="E15" s="30"/>
@@ -2998,8 +4264,8 @@
       <c r="N15" s="29"/>
     </row>
     <row r="16" spans="1:14" ht="59.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="157"/>
-      <c r="B16" s="159"/>
+      <c r="A16" s="114"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="26"/>
       <c r="D16" s="12"/>
       <c r="E16" s="32"/>
@@ -3014,8 +4280,8 @@
       <c r="N16" s="29"/>
     </row>
     <row r="17" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="157"/>
-      <c r="B17" s="159"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="26"/>
       <c r="D17" s="11"/>
       <c r="E17" s="32"/>
@@ -3030,8 +4296,8 @@
       <c r="N17" s="29"/>
     </row>
     <row r="18" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="157"/>
-      <c r="B18" s="159"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="26"/>
       <c r="D18" s="11"/>
       <c r="E18" s="32"/>
@@ -3046,8 +4312,8 @@
       <c r="N18" s="29"/>
     </row>
     <row r="19" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="157"/>
-      <c r="B19" s="159"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="116"/>
       <c r="C19" s="26"/>
       <c r="D19" s="11"/>
       <c r="E19" s="34"/>
@@ -3062,8 +4328,8 @@
       <c r="N19" s="29"/>
     </row>
     <row r="20" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="157"/>
-      <c r="B20" s="159"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="26"/>
       <c r="D20" s="11"/>
       <c r="E20" s="32"/>
@@ -3078,8 +4344,8 @@
       <c r="N20" s="29"/>
     </row>
     <row r="21" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="157"/>
-      <c r="B21" s="159"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="26"/>
       <c r="D21" s="11"/>
       <c r="E21" s="32"/>
@@ -3094,8 +4360,8 @@
       <c r="N21" s="29"/>
     </row>
     <row r="22" spans="1:14" ht="78.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="157"/>
-      <c r="B22" s="160"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="117"/>
       <c r="C22" s="26"/>
       <c r="D22" s="11"/>
       <c r="E22" s="32"/>
@@ -3110,10 +4376,10 @@
       <c r="N22" s="29"/>
     </row>
     <row r="23" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="126">
+      <c r="A23" s="118">
         <v>2</v>
       </c>
-      <c r="B23" s="129"/>
+      <c r="B23" s="121"/>
       <c r="C23" s="26"/>
       <c r="D23" s="11"/>
       <c r="E23" s="32"/>
@@ -3128,8 +4394,8 @@
       <c r="N23" s="29"/>
     </row>
     <row r="24" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="127"/>
-      <c r="B24" s="130"/>
+      <c r="A24" s="119"/>
+      <c r="B24" s="122"/>
       <c r="C24" s="26"/>
       <c r="D24" s="11"/>
       <c r="E24" s="32"/>
@@ -3144,8 +4410,8 @@
       <c r="N24" s="29"/>
     </row>
     <row r="25" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="127"/>
-      <c r="B25" s="130"/>
+      <c r="A25" s="119"/>
+      <c r="B25" s="122"/>
       <c r="C25" s="26"/>
       <c r="D25" s="12"/>
       <c r="E25" s="32"/>
@@ -3160,8 +4426,8 @@
       <c r="N25" s="29"/>
     </row>
     <row r="26" spans="1:14" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="127"/>
-      <c r="B26" s="130"/>
+      <c r="A26" s="119"/>
+      <c r="B26" s="122"/>
       <c r="C26" s="26"/>
       <c r="D26" s="11"/>
       <c r="E26" s="32"/>
@@ -3176,8 +4442,8 @@
       <c r="N26" s="29"/>
     </row>
     <row r="27" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="127"/>
-      <c r="B27" s="130"/>
+      <c r="A27" s="119"/>
+      <c r="B27" s="122"/>
       <c r="C27" s="26"/>
       <c r="D27" s="11"/>
       <c r="E27" s="34"/>
@@ -3192,8 +4458,8 @@
       <c r="N27" s="29"/>
     </row>
     <row r="28" spans="1:14" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="128"/>
-      <c r="B28" s="131"/>
+      <c r="A28" s="120"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="26"/>
       <c r="D28" s="11"/>
       <c r="E28" s="34"/>
@@ -3208,10 +4474,10 @@
       <c r="N28" s="29"/>
     </row>
     <row r="29" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="126">
+      <c r="A29" s="118">
         <v>3</v>
       </c>
-      <c r="B29" s="132"/>
+      <c r="B29" s="131"/>
       <c r="C29" s="26"/>
       <c r="D29" s="11"/>
       <c r="E29" s="34"/>
@@ -3226,8 +4492,8 @@
       <c r="N29" s="29"/>
     </row>
     <row r="30" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="127"/>
-      <c r="B30" s="133"/>
+      <c r="A30" s="119"/>
+      <c r="B30" s="132"/>
       <c r="C30" s="26"/>
       <c r="D30" s="11"/>
       <c r="E30" s="34"/>
@@ -3242,8 +4508,8 @@
       <c r="N30" s="29"/>
     </row>
     <row r="31" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="127"/>
-      <c r="B31" s="133"/>
+      <c r="A31" s="119"/>
+      <c r="B31" s="132"/>
       <c r="C31" s="26"/>
       <c r="D31" s="11"/>
       <c r="E31" s="32"/>
@@ -3258,8 +4524,8 @@
       <c r="N31" s="29"/>
     </row>
     <row r="32" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="127"/>
-      <c r="B32" s="133"/>
+      <c r="A32" s="119"/>
+      <c r="B32" s="132"/>
       <c r="C32" s="26"/>
       <c r="D32" s="11"/>
       <c r="E32" s="32"/>
@@ -3274,8 +4540,8 @@
       <c r="N32" s="29"/>
     </row>
     <row r="33" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="127"/>
-      <c r="B33" s="133"/>
+      <c r="A33" s="119"/>
+      <c r="B33" s="132"/>
       <c r="C33" s="26"/>
       <c r="D33" s="11"/>
       <c r="E33" s="34"/>
@@ -3290,8 +4556,8 @@
       <c r="N33" s="29"/>
     </row>
     <row r="34" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="127"/>
-      <c r="B34" s="133"/>
+      <c r="A34" s="119"/>
+      <c r="B34" s="132"/>
       <c r="C34" s="26"/>
       <c r="D34" s="11"/>
       <c r="E34" s="34"/>
@@ -3306,8 +4572,8 @@
       <c r="N34" s="29"/>
     </row>
     <row r="35" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="127"/>
-      <c r="B35" s="133"/>
+      <c r="A35" s="119"/>
+      <c r="B35" s="132"/>
       <c r="C35" s="26"/>
       <c r="D35" s="11"/>
       <c r="E35" s="34"/>
@@ -3322,8 +4588,8 @@
       <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="127"/>
-      <c r="B36" s="133"/>
+      <c r="A36" s="119"/>
+      <c r="B36" s="132"/>
       <c r="C36" s="26"/>
       <c r="D36" s="11"/>
       <c r="E36" s="34"/>
@@ -3338,8 +4604,8 @@
       <c r="N36" s="29"/>
     </row>
     <row r="37" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="128"/>
-      <c r="B37" s="134"/>
+      <c r="A37" s="120"/>
+      <c r="B37" s="133"/>
       <c r="C37" s="26"/>
       <c r="D37" s="11"/>
       <c r="E37" s="34"/>
@@ -3354,10 +4620,10 @@
       <c r="N37" s="29"/>
     </row>
     <row r="38" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="135">
+      <c r="A38" s="138">
         <v>4</v>
       </c>
-      <c r="B38" s="129"/>
+      <c r="B38" s="121"/>
       <c r="C38" s="26"/>
       <c r="D38" s="11"/>
       <c r="E38" s="32"/>
@@ -3372,8 +4638,8 @@
       <c r="N38" s="29"/>
     </row>
     <row r="39" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="136"/>
-      <c r="B39" s="130"/>
+      <c r="A39" s="139"/>
+      <c r="B39" s="122"/>
       <c r="C39" s="26"/>
       <c r="D39" s="11"/>
       <c r="E39" s="34"/>
@@ -3388,8 +4654,8 @@
       <c r="N39" s="29"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="136"/>
-      <c r="B40" s="130"/>
+      <c r="A40" s="139"/>
+      <c r="B40" s="122"/>
       <c r="C40" s="26"/>
       <c r="D40" s="11"/>
       <c r="E40" s="34"/>
@@ -3404,8 +4670,8 @@
       <c r="N40" s="29"/>
     </row>
     <row r="41" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="136"/>
-      <c r="B41" s="130"/>
+      <c r="A41" s="139"/>
+      <c r="B41" s="122"/>
       <c r="C41" s="26"/>
       <c r="D41" s="11"/>
       <c r="E41" s="34"/>
@@ -3420,8 +4686,8 @@
       <c r="N41" s="29"/>
     </row>
     <row r="42" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="136"/>
-      <c r="B42" s="130"/>
+      <c r="A42" s="139"/>
+      <c r="B42" s="122"/>
       <c r="C42" s="26"/>
       <c r="D42" s="11"/>
       <c r="E42" s="34"/>
@@ -3436,8 +4702,8 @@
       <c r="N42" s="29"/>
     </row>
     <row r="43" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="136"/>
-      <c r="B43" s="130"/>
+      <c r="A43" s="139"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="26"/>
       <c r="D43" s="11"/>
       <c r="E43" s="34"/>
@@ -3452,8 +4718,8 @@
       <c r="N43" s="29"/>
     </row>
     <row r="44" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="137"/>
-      <c r="B44" s="131"/>
+      <c r="A44" s="140"/>
+      <c r="B44" s="123"/>
       <c r="C44" s="26"/>
       <c r="D44" s="11"/>
       <c r="E44" s="34"/>
@@ -3468,12 +4734,18 @@
       <c r="N44" s="29"/>
     </row>
     <row r="45" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="126">
-        <v>5</v>
-      </c>
-      <c r="B45" s="129"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="11"/>
+      <c r="A45" s="114">
+        <v>1</v>
+      </c>
+      <c r="B45" s="115" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="26">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="E45" s="34"/>
       <c r="F45" s="34"/>
       <c r="G45" s="35"/>
@@ -3486,10 +4758,14 @@
       <c r="N45" s="29"/>
     </row>
     <row r="46" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="127"/>
-      <c r="B46" s="130"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="11"/>
+      <c r="A46" s="114"/>
+      <c r="B46" s="116"/>
+      <c r="C46" s="26">
+        <v>2</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="E46" s="34"/>
       <c r="F46" s="34"/>
       <c r="G46" s="35"/>
@@ -3502,10 +4778,14 @@
       <c r="N46" s="29"/>
     </row>
     <row r="47" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="127"/>
-      <c r="B47" s="130"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="11"/>
+      <c r="A47" s="114"/>
+      <c r="B47" s="116"/>
+      <c r="C47" s="26">
+        <v>3</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="E47" s="34"/>
       <c r="F47" s="34"/>
       <c r="G47" s="35"/>
@@ -3517,11 +4797,15 @@
       <c r="M47" s="29"/>
       <c r="N47" s="29"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="127"/>
-      <c r="B48" s="130"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="11"/>
+    <row r="48" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="114"/>
+      <c r="B48" s="116"/>
+      <c r="C48" s="26">
+        <v>4</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="E48" s="32"/>
       <c r="F48" s="32"/>
       <c r="G48" s="33"/>
@@ -3534,10 +4818,14 @@
       <c r="N48" s="29"/>
     </row>
     <row r="49" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="127"/>
-      <c r="B49" s="130"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="11"/>
+      <c r="A49" s="114"/>
+      <c r="B49" s="116"/>
+      <c r="C49" s="26">
+        <v>5</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="E49" s="34"/>
       <c r="F49" s="34"/>
       <c r="G49" s="35"/>
@@ -3549,11 +4837,15 @@
       <c r="M49" s="29"/>
       <c r="N49" s="29"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="127"/>
-      <c r="B50" s="130"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="11"/>
+    <row r="50" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="114"/>
+      <c r="B50" s="116"/>
+      <c r="C50" s="26">
+        <v>6</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="E50" s="34"/>
       <c r="F50" s="34"/>
       <c r="G50" s="35"/>
@@ -3566,10 +4858,14 @@
       <c r="N50" s="29"/>
     </row>
     <row r="51" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="127"/>
-      <c r="B51" s="130"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="11"/>
+      <c r="A51" s="114"/>
+      <c r="B51" s="116"/>
+      <c r="C51" s="26">
+        <v>7</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="E51" s="34"/>
       <c r="F51" s="34"/>
       <c r="G51" s="35"/>
@@ -3582,10 +4878,14 @@
       <c r="N51" s="29"/>
     </row>
     <row r="52" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="127"/>
-      <c r="B52" s="130"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="11"/>
+      <c r="A52" s="114"/>
+      <c r="B52" s="116"/>
+      <c r="C52" s="26">
+        <v>8</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="E52" s="34"/>
       <c r="F52" s="34"/>
       <c r="G52" s="35"/>
@@ -3598,10 +4898,14 @@
       <c r="N52" s="29"/>
     </row>
     <row r="53" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="127"/>
-      <c r="B53" s="130"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="11"/>
+      <c r="A53" s="114"/>
+      <c r="B53" s="117"/>
+      <c r="C53" s="26">
+        <v>9</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="E53" s="34"/>
       <c r="F53" s="34"/>
       <c r="G53" s="35"/>
@@ -3613,11 +4917,19 @@
       <c r="M53" s="29"/>
       <c r="N53" s="29"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="127"/>
-      <c r="B54" s="130"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="11"/>
+    <row r="54" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="118">
+        <v>2</v>
+      </c>
+      <c r="B54" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="26">
+        <v>10</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="E54" s="34"/>
       <c r="F54" s="34"/>
       <c r="G54" s="35"/>
@@ -3630,10 +4942,14 @@
       <c r="N54" s="29"/>
     </row>
     <row r="55" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="127"/>
-      <c r="B55" s="130"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="11"/>
+      <c r="A55" s="119"/>
+      <c r="B55" s="122"/>
+      <c r="C55" s="26">
+        <v>11</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="E55" s="34"/>
       <c r="F55" s="34"/>
       <c r="G55" s="35"/>
@@ -3646,10 +4962,14 @@
       <c r="N55" s="29"/>
     </row>
     <row r="56" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="127"/>
-      <c r="B56" s="130"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="11"/>
+      <c r="A56" s="119"/>
+      <c r="B56" s="122"/>
+      <c r="C56" s="26">
+        <v>12</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="E56" s="34"/>
       <c r="F56" s="34"/>
       <c r="G56" s="35"/>
@@ -3662,10 +4982,14 @@
       <c r="N56" s="29"/>
     </row>
     <row r="57" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="127"/>
-      <c r="B57" s="130"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="11"/>
+      <c r="A57" s="119"/>
+      <c r="B57" s="122"/>
+      <c r="C57" s="26">
+        <v>13</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="E57" s="34"/>
       <c r="F57" s="34"/>
       <c r="G57" s="35"/>
@@ -3678,10 +5002,14 @@
       <c r="N57" s="29"/>
     </row>
     <row r="58" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="127"/>
-      <c r="B58" s="130"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="11"/>
+      <c r="A58" s="119"/>
+      <c r="B58" s="122"/>
+      <c r="C58" s="26">
+        <v>14</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="E58" s="34"/>
       <c r="F58" s="34"/>
       <c r="G58" s="35"/>
@@ -3694,10 +5022,14 @@
       <c r="N58" s="29"/>
     </row>
     <row r="59" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="127"/>
-      <c r="B59" s="130"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="11"/>
+      <c r="A59" s="120"/>
+      <c r="B59" s="123"/>
+      <c r="C59" s="26">
+        <v>15</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="E59" s="34"/>
       <c r="F59" s="34"/>
       <c r="G59" s="35"/>
@@ -3710,10 +5042,18 @@
       <c r="N59" s="29"/>
     </row>
     <row r="60" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="127"/>
-      <c r="B60" s="130"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="11"/>
+      <c r="A60" s="118">
+        <v>3</v>
+      </c>
+      <c r="B60" s="131" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="26">
+        <v>16</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="E60" s="34"/>
       <c r="F60" s="34"/>
       <c r="G60" s="35"/>
@@ -3726,10 +5066,14 @@
       <c r="N60" s="29"/>
     </row>
     <row r="61" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="127"/>
-      <c r="B61" s="130"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="11"/>
+      <c r="A61" s="119"/>
+      <c r="B61" s="132"/>
+      <c r="C61" s="26">
+        <v>17</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="E61" s="34"/>
       <c r="F61" s="34"/>
       <c r="G61" s="35"/>
@@ -3742,10 +5086,14 @@
       <c r="N61" s="29"/>
     </row>
     <row r="62" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="127"/>
-      <c r="B62" s="130"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="11"/>
+      <c r="A62" s="119"/>
+      <c r="B62" s="132"/>
+      <c r="C62" s="26">
+        <v>18</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="E62" s="34"/>
       <c r="F62" s="34"/>
       <c r="G62" s="35"/>
@@ -3758,10 +5106,14 @@
       <c r="N62" s="29"/>
     </row>
     <row r="63" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="127"/>
-      <c r="B63" s="130"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="11"/>
+      <c r="A63" s="119"/>
+      <c r="B63" s="132"/>
+      <c r="C63" s="26">
+        <v>19</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="E63" s="34"/>
       <c r="F63" s="34"/>
       <c r="G63" s="35"/>
@@ -3773,11 +5125,15 @@
       <c r="M63" s="29"/>
       <c r="N63" s="29"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="127"/>
-      <c r="B64" s="130"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="11"/>
+    <row r="64" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="119"/>
+      <c r="B64" s="132"/>
+      <c r="C64" s="26">
+        <v>20</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="E64" s="34"/>
       <c r="F64" s="34"/>
       <c r="G64" s="35"/>
@@ -3790,10 +5146,14 @@
       <c r="N64" s="29"/>
     </row>
     <row r="65" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="127"/>
-      <c r="B65" s="130"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="11"/>
+      <c r="A65" s="119"/>
+      <c r="B65" s="132"/>
+      <c r="C65" s="26">
+        <v>21</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>52</v>
+      </c>
       <c r="E65" s="34"/>
       <c r="F65" s="34"/>
       <c r="G65" s="35"/>
@@ -3806,10 +5166,14 @@
       <c r="N65" s="29"/>
     </row>
     <row r="66" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="127"/>
-      <c r="B66" s="130"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="11"/>
+      <c r="A66" s="119"/>
+      <c r="B66" s="132"/>
+      <c r="C66" s="26">
+        <v>22</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="E66" s="34"/>
       <c r="F66" s="34"/>
       <c r="G66" s="35"/>
@@ -3822,10 +5186,14 @@
       <c r="N66" s="29"/>
     </row>
     <row r="67" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="127"/>
-      <c r="B67" s="130"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="11"/>
+      <c r="A67" s="119"/>
+      <c r="B67" s="132"/>
+      <c r="C67" s="26">
+        <v>23</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="E67" s="32"/>
       <c r="F67" s="32"/>
       <c r="G67" s="33"/>
@@ -3838,10 +5206,14 @@
       <c r="N67" s="29"/>
     </row>
     <row r="68" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="127"/>
-      <c r="B68" s="130"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="11"/>
+      <c r="A68" s="120"/>
+      <c r="B68" s="133"/>
+      <c r="C68" s="26">
+        <v>24</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="E68" s="34"/>
       <c r="F68" s="34"/>
       <c r="G68" s="35"/>
@@ -3854,10 +5226,18 @@
       <c r="N68" s="29"/>
     </row>
     <row r="69" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="127"/>
-      <c r="B69" s="130"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="11"/>
+      <c r="A69" s="138">
+        <v>4</v>
+      </c>
+      <c r="B69" s="121" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="26">
+        <v>25</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="E69" s="34"/>
       <c r="F69" s="34"/>
       <c r="G69" s="35"/>
@@ -3869,11 +5249,15 @@
       <c r="M69" s="29"/>
       <c r="N69" s="29"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="127"/>
-      <c r="B70" s="130"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="12"/>
+    <row r="70" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="139"/>
+      <c r="B70" s="122"/>
+      <c r="C70" s="26">
+        <v>26</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="E70" s="32"/>
       <c r="F70" s="32"/>
       <c r="G70" s="33"/>
@@ -3886,10 +5270,14 @@
       <c r="N70" s="29"/>
     </row>
     <row r="71" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="128"/>
-      <c r="B71" s="131"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="12"/>
+      <c r="A71" s="139"/>
+      <c r="B71" s="122"/>
+      <c r="C71" s="26">
+        <v>27</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="E71" s="32"/>
       <c r="F71" s="32"/>
       <c r="G71" s="33"/>
@@ -3902,12 +5290,14 @@
       <c r="N71" s="29"/>
     </row>
     <row r="72" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="126">
-        <v>6</v>
-      </c>
-      <c r="B72" s="129"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="76"/>
+      <c r="A72" s="139"/>
+      <c r="B72" s="122"/>
+      <c r="C72" s="26">
+        <v>28</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>60</v>
+      </c>
       <c r="E72" s="34"/>
       <c r="F72" s="34"/>
       <c r="G72" s="35"/>
@@ -3919,11 +5309,15 @@
       <c r="M72" s="29"/>
       <c r="N72" s="29"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="127"/>
-      <c r="B73" s="130"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="10"/>
+    <row r="73" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="139"/>
+      <c r="B73" s="122"/>
+      <c r="C73" s="26">
+        <v>29</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="E73" s="11"/>
       <c r="F73" s="34"/>
       <c r="G73" s="35"/>
@@ -3935,11 +5329,15 @@
       <c r="M73" s="29"/>
       <c r="N73" s="29"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="127"/>
-      <c r="B74" s="130"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="77"/>
+    <row r="74" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="139"/>
+      <c r="B74" s="122"/>
+      <c r="C74" s="26">
+        <v>30</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="E74" s="34"/>
       <c r="F74" s="34"/>
       <c r="G74" s="35"/>
@@ -3951,11 +5349,15 @@
       <c r="M74" s="29"/>
       <c r="N74" s="29"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="127"/>
-      <c r="B75" s="130"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="11"/>
+    <row r="75" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="140"/>
+      <c r="B75" s="123"/>
+      <c r="C75" s="26">
+        <v>31</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="E75" s="34"/>
       <c r="F75" s="34"/>
       <c r="G75" s="35"/>
@@ -3968,10 +5370,18 @@
       <c r="N75" s="29"/>
     </row>
     <row r="76" spans="1:14" ht="37.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="128"/>
-      <c r="B76" s="131"/>
-      <c r="C76" s="26"/>
-      <c r="D76" s="11"/>
+      <c r="A76" s="118">
+        <v>5</v>
+      </c>
+      <c r="B76" s="121" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" s="26">
+        <v>32</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="E76" s="34"/>
       <c r="F76" s="34"/>
       <c r="G76" s="35"/>
@@ -3984,12 +5394,14 @@
       <c r="N76" s="29"/>
     </row>
     <row r="77" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="135">
-        <v>7</v>
-      </c>
-      <c r="B77" s="129"/>
-      <c r="C77" s="26"/>
-      <c r="D77" s="11"/>
+      <c r="A77" s="119"/>
+      <c r="B77" s="122"/>
+      <c r="C77" s="26">
+        <v>33</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="E77" s="32"/>
       <c r="F77" s="32"/>
       <c r="G77" s="33"/>
@@ -4002,10 +5414,14 @@
       <c r="N77" s="29"/>
     </row>
     <row r="78" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="136"/>
-      <c r="B78" s="130"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="11"/>
+      <c r="A78" s="119"/>
+      <c r="B78" s="122"/>
+      <c r="C78" s="26">
+        <v>34</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="E78" s="32"/>
       <c r="F78" s="32"/>
       <c r="G78" s="35"/>
@@ -4018,10 +5434,14 @@
       <c r="N78" s="29"/>
     </row>
     <row r="79" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="136"/>
-      <c r="B79" s="130"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="12"/>
+      <c r="A79" s="119"/>
+      <c r="B79" s="122"/>
+      <c r="C79" s="26">
+        <v>35</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>68</v>
+      </c>
       <c r="E79" s="32"/>
       <c r="F79" s="32"/>
       <c r="G79" s="35"/>
@@ -4034,10 +5454,14 @@
       <c r="N79" s="29"/>
     </row>
     <row r="80" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="136"/>
-      <c r="B80" s="130"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="11"/>
+      <c r="A80" s="119"/>
+      <c r="B80" s="122"/>
+      <c r="C80" s="26">
+        <v>36</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="E80" s="32"/>
       <c r="F80" s="32"/>
       <c r="G80" s="35"/>
@@ -4050,10 +5474,14 @@
       <c r="N80" s="29"/>
     </row>
     <row r="81" spans="1:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="136"/>
-      <c r="B81" s="130"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="11"/>
+      <c r="A81" s="119"/>
+      <c r="B81" s="122"/>
+      <c r="C81" s="26">
+        <v>37</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>70</v>
+      </c>
       <c r="E81" s="32"/>
       <c r="F81" s="32"/>
       <c r="G81" s="33"/>
@@ -4065,11 +5493,15 @@
       <c r="M81" s="29"/>
       <c r="N81" s="29"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="136"/>
-      <c r="B82" s="130"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="11"/>
+    <row r="82" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="119"/>
+      <c r="B82" s="122"/>
+      <c r="C82" s="26">
+        <v>38</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>71</v>
+      </c>
       <c r="E82" s="32"/>
       <c r="F82" s="32"/>
       <c r="G82" s="33"/>
@@ -4082,10 +5514,14 @@
       <c r="N82" s="29"/>
     </row>
     <row r="83" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="136"/>
-      <c r="B83" s="130"/>
-      <c r="C83" s="26"/>
-      <c r="D83" s="11"/>
+      <c r="A83" s="119"/>
+      <c r="B83" s="122"/>
+      <c r="C83" s="26">
+        <v>39</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="E83" s="32"/>
       <c r="F83" s="32"/>
       <c r="G83" s="33"/>
@@ -4098,10 +5534,14 @@
       <c r="N83" s="29"/>
     </row>
     <row r="84" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="136"/>
-      <c r="B84" s="130"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="12"/>
+      <c r="A84" s="119"/>
+      <c r="B84" s="122"/>
+      <c r="C84" s="26">
+        <v>40</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="E84" s="32"/>
       <c r="F84" s="32"/>
       <c r="G84" s="33"/>
@@ -4114,10 +5554,14 @@
       <c r="N84" s="29"/>
     </row>
     <row r="85" spans="1:14" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="136"/>
-      <c r="B85" s="130"/>
-      <c r="C85" s="26"/>
-      <c r="D85" s="11"/>
+      <c r="A85" s="119"/>
+      <c r="B85" s="122"/>
+      <c r="C85" s="26">
+        <v>41</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="E85" s="32"/>
       <c r="F85" s="32"/>
       <c r="G85" s="33"/>
@@ -4130,10 +5574,14 @@
       <c r="N85" s="29"/>
     </row>
     <row r="86" spans="1:14" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="136"/>
-      <c r="B86" s="130"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="12"/>
+      <c r="A86" s="119"/>
+      <c r="B86" s="122"/>
+      <c r="C86" s="26">
+        <v>42</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="E86" s="32"/>
       <c r="F86" s="32"/>
       <c r="G86" s="33"/>
@@ -4146,10 +5594,14 @@
       <c r="N86" s="29"/>
     </row>
     <row r="87" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="136"/>
-      <c r="B87" s="130"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="12"/>
+      <c r="A87" s="119"/>
+      <c r="B87" s="122"/>
+      <c r="C87" s="26">
+        <v>43</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>76</v>
+      </c>
       <c r="E87" s="32"/>
       <c r="F87" s="32"/>
       <c r="G87" s="33"/>
@@ -4162,10 +5614,14 @@
       <c r="N87" s="29"/>
     </row>
     <row r="88" spans="1:14" ht="23.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="137"/>
-      <c r="B88" s="131"/>
-      <c r="C88" s="26"/>
-      <c r="D88" s="12"/>
+      <c r="A88" s="119"/>
+      <c r="B88" s="122"/>
+      <c r="C88" s="26">
+        <v>44</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="E88" s="32"/>
       <c r="F88" s="32"/>
       <c r="G88" s="33"/>
@@ -4178,12 +5634,14 @@
       <c r="N88" s="29"/>
     </row>
     <row r="89" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="126">
-        <v>8</v>
-      </c>
-      <c r="B89" s="129"/>
-      <c r="C89" s="26"/>
-      <c r="D89" s="12"/>
+      <c r="A89" s="119"/>
+      <c r="B89" s="122"/>
+      <c r="C89" s="26">
+        <v>45</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>78</v>
+      </c>
       <c r="E89" s="32"/>
       <c r="F89" s="32"/>
       <c r="G89" s="35"/>
@@ -4196,10 +5654,14 @@
       <c r="N89" s="29"/>
     </row>
     <row r="90" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="127"/>
-      <c r="B90" s="130"/>
-      <c r="C90" s="26"/>
-      <c r="D90" s="12"/>
+      <c r="A90" s="119"/>
+      <c r="B90" s="122"/>
+      <c r="C90" s="26">
+        <v>46</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="E90" s="32"/>
       <c r="F90" s="32"/>
       <c r="G90" s="33"/>
@@ -4212,10 +5674,14 @@
       <c r="N90" s="29"/>
     </row>
     <row r="91" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="127"/>
-      <c r="B91" s="130"/>
-      <c r="C91" s="26"/>
-      <c r="D91" s="11"/>
+      <c r="A91" s="119"/>
+      <c r="B91" s="122"/>
+      <c r="C91" s="26">
+        <v>47</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="E91" s="32"/>
       <c r="F91" s="32"/>
       <c r="G91" s="33"/>
@@ -4228,10 +5694,14 @@
       <c r="N91" s="29"/>
     </row>
     <row r="92" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="127"/>
-      <c r="B92" s="130"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="12"/>
+      <c r="A92" s="119"/>
+      <c r="B92" s="122"/>
+      <c r="C92" s="26">
+        <v>48</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="E92" s="32"/>
       <c r="F92" s="32"/>
       <c r="G92" s="35"/>
@@ -4244,10 +5714,14 @@
       <c r="N92" s="29"/>
     </row>
     <row r="93" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="127"/>
-      <c r="B93" s="130"/>
-      <c r="C93" s="26"/>
-      <c r="D93" s="12"/>
+      <c r="A93" s="119"/>
+      <c r="B93" s="122"/>
+      <c r="C93" s="26">
+        <v>49</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>82</v>
+      </c>
       <c r="E93" s="32"/>
       <c r="F93" s="32"/>
       <c r="G93" s="35"/>
@@ -4260,10 +5734,14 @@
       <c r="N93" s="29"/>
     </row>
     <row r="94" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="127"/>
-      <c r="B94" s="130"/>
-      <c r="C94" s="26"/>
-      <c r="D94" s="12"/>
+      <c r="A94" s="119"/>
+      <c r="B94" s="122"/>
+      <c r="C94" s="26">
+        <v>50</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>83</v>
+      </c>
       <c r="E94" s="32"/>
       <c r="F94" s="32"/>
       <c r="G94" s="35"/>
@@ -4275,11 +5753,15 @@
       <c r="M94" s="29"/>
       <c r="N94" s="29"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A95" s="127"/>
-      <c r="B95" s="130"/>
-      <c r="C95" s="26"/>
-      <c r="D95" s="12"/>
+    <row r="95" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="119"/>
+      <c r="B95" s="122"/>
+      <c r="C95" s="26">
+        <v>51</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="E95" s="32"/>
       <c r="F95" s="32"/>
       <c r="G95" s="35"/>
@@ -4292,10 +5774,14 @@
       <c r="N95" s="29"/>
     </row>
     <row r="96" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="127"/>
-      <c r="B96" s="130"/>
-      <c r="C96" s="26"/>
-      <c r="D96" s="12"/>
+      <c r="A96" s="119"/>
+      <c r="B96" s="122"/>
+      <c r="C96" s="26">
+        <v>52</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="E96" s="32"/>
       <c r="F96" s="32"/>
       <c r="G96" s="33"/>
@@ -4308,12 +5794,14 @@
       <c r="N96" s="29"/>
     </row>
     <row r="97" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="126">
-        <v>9</v>
-      </c>
-      <c r="B97" s="129"/>
-      <c r="C97" s="26"/>
-      <c r="D97" s="12"/>
+      <c r="A97" s="119"/>
+      <c r="B97" s="122"/>
+      <c r="C97" s="26">
+        <v>53</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="E97" s="34"/>
       <c r="F97" s="34"/>
       <c r="G97" s="33"/>
@@ -4326,10 +5814,14 @@
       <c r="N97" s="29"/>
     </row>
     <row r="98" spans="1:14" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="127"/>
-      <c r="B98" s="130"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="12"/>
+      <c r="A98" s="119"/>
+      <c r="B98" s="122"/>
+      <c r="C98" s="26">
+        <v>54</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>87</v>
+      </c>
       <c r="E98" s="34"/>
       <c r="F98" s="34"/>
       <c r="G98" s="35"/>
@@ -4342,10 +5834,14 @@
       <c r="N98" s="29"/>
     </row>
     <row r="99" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="127"/>
-      <c r="B99" s="130"/>
-      <c r="C99" s="26"/>
-      <c r="D99" s="11"/>
+      <c r="A99" s="119"/>
+      <c r="B99" s="122"/>
+      <c r="C99" s="26">
+        <v>55</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>88</v>
+      </c>
       <c r="E99" s="36"/>
       <c r="F99" s="34"/>
       <c r="G99" s="33"/>
@@ -4358,10 +5854,14 @@
       <c r="N99" s="29"/>
     </row>
     <row r="100" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="127"/>
-      <c r="B100" s="130"/>
-      <c r="C100" s="26"/>
-      <c r="D100" s="11"/>
+      <c r="A100" s="119"/>
+      <c r="B100" s="122"/>
+      <c r="C100" s="26">
+        <v>56</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="F100" s="34"/>
       <c r="G100" s="35"/>
       <c r="H100" s="29"/>
@@ -4373,10 +5873,14 @@
       <c r="N100" s="29"/>
     </row>
     <row r="101" spans="1:14" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="127"/>
-      <c r="B101" s="130"/>
-      <c r="C101" s="26"/>
-      <c r="D101" s="12"/>
+      <c r="A101" s="119"/>
+      <c r="B101" s="122"/>
+      <c r="C101" s="26">
+        <v>57</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="E101" s="37"/>
       <c r="F101" s="34"/>
       <c r="G101" s="33"/>
@@ -4389,10 +5893,14 @@
       <c r="N101" s="29"/>
     </row>
     <row r="102" spans="1:14" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="127"/>
-      <c r="B102" s="130"/>
-      <c r="C102" s="26"/>
-      <c r="D102" s="11"/>
+      <c r="A102" s="120"/>
+      <c r="B102" s="123"/>
+      <c r="C102" s="26">
+        <v>58</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>91</v>
+      </c>
       <c r="E102" s="37"/>
       <c r="F102" s="34"/>
       <c r="G102" s="35"/>
@@ -4405,10 +5913,18 @@
       <c r="N102" s="29"/>
     </row>
     <row r="103" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="127"/>
-      <c r="B103" s="130"/>
-      <c r="C103" s="26"/>
-      <c r="D103" s="12"/>
+      <c r="A103" s="118">
+        <v>6</v>
+      </c>
+      <c r="B103" s="121" t="s">
+        <v>92</v>
+      </c>
+      <c r="C103" s="26">
+        <v>59</v>
+      </c>
+      <c r="D103" s="76" t="s">
+        <v>93</v>
+      </c>
       <c r="E103" s="37"/>
       <c r="F103" s="38"/>
       <c r="G103" s="35"/>
@@ -4421,10 +5937,14 @@
       <c r="N103" s="29"/>
     </row>
     <row r="104" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="127"/>
-      <c r="B104" s="130"/>
-      <c r="C104" s="26"/>
-      <c r="D104" s="11"/>
+      <c r="A104" s="119"/>
+      <c r="B104" s="122"/>
+      <c r="C104" s="26">
+        <v>60</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>94</v>
+      </c>
       <c r="E104" s="37"/>
       <c r="F104" s="34"/>
       <c r="G104" s="33"/>
@@ -4437,10 +5957,14 @@
       <c r="N104" s="29"/>
     </row>
     <row r="105" spans="1:14" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="127"/>
-      <c r="B105" s="130"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="11"/>
+      <c r="A105" s="119"/>
+      <c r="B105" s="122"/>
+      <c r="C105" s="26">
+        <v>61</v>
+      </c>
+      <c r="D105" s="77" t="s">
+        <v>95</v>
+      </c>
       <c r="E105" s="36"/>
       <c r="F105" s="34"/>
       <c r="G105" s="35"/>
@@ -4453,10 +5977,14 @@
       <c r="N105" s="29"/>
     </row>
     <row r="106" spans="1:14" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="127"/>
-      <c r="B106" s="130"/>
-      <c r="C106" s="26"/>
-      <c r="D106" s="11"/>
+      <c r="A106" s="119"/>
+      <c r="B106" s="122"/>
+      <c r="C106" s="26">
+        <v>62</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="E106" s="36"/>
       <c r="F106" s="34"/>
       <c r="G106" s="35"/>
@@ -4469,10 +5997,14 @@
       <c r="N106" s="29"/>
     </row>
     <row r="107" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="128"/>
-      <c r="B107" s="131"/>
-      <c r="C107" s="26"/>
-      <c r="D107" s="12"/>
+      <c r="A107" s="120"/>
+      <c r="B107" s="123"/>
+      <c r="C107" s="26">
+        <v>63</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="E107" s="37"/>
       <c r="F107" s="34"/>
       <c r="G107" s="35"/>
@@ -4484,13 +6016,19 @@
       <c r="M107" s="29"/>
       <c r="N107" s="29"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A108" s="126">
-        <v>10</v>
-      </c>
-      <c r="B108" s="129"/>
-      <c r="C108" s="26"/>
-      <c r="D108" s="12"/>
+    <row r="108" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="138">
+        <v>7</v>
+      </c>
+      <c r="B108" s="121" t="s">
+        <v>98</v>
+      </c>
+      <c r="C108" s="26">
+        <v>64</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="E108" s="36"/>
       <c r="F108" s="34"/>
       <c r="G108" s="35"/>
@@ -4503,10 +6041,14 @@
       <c r="N108" s="29"/>
     </row>
     <row r="109" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="127"/>
-      <c r="B109" s="130"/>
-      <c r="C109" s="26"/>
-      <c r="D109" s="12"/>
+      <c r="A109" s="139"/>
+      <c r="B109" s="122"/>
+      <c r="C109" s="26">
+        <v>65</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="E109" s="36"/>
       <c r="F109" s="34"/>
       <c r="G109" s="35"/>
@@ -4519,10 +6061,14 @@
       <c r="N109" s="29"/>
     </row>
     <row r="110" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="127"/>
-      <c r="B110" s="130"/>
-      <c r="C110" s="26"/>
-      <c r="D110" s="11"/>
+      <c r="A110" s="139"/>
+      <c r="B110" s="122"/>
+      <c r="C110" s="26">
+        <v>66</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="E110" s="36"/>
       <c r="F110" s="34"/>
       <c r="G110" s="35"/>
@@ -4535,10 +6081,14 @@
       <c r="N110" s="29"/>
     </row>
     <row r="111" spans="1:14" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="127"/>
-      <c r="B111" s="130"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="11"/>
+      <c r="A111" s="139"/>
+      <c r="B111" s="122"/>
+      <c r="C111" s="26">
+        <v>67</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>102</v>
+      </c>
       <c r="E111" s="36"/>
       <c r="F111" s="34"/>
       <c r="G111" s="35"/>
@@ -4551,10 +6101,14 @@
       <c r="N111" s="29"/>
     </row>
     <row r="112" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="127"/>
-      <c r="B112" s="130"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="11"/>
+      <c r="A112" s="139"/>
+      <c r="B112" s="122"/>
+      <c r="C112" s="26">
+        <v>68</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="E112" s="36"/>
       <c r="F112" s="34"/>
       <c r="G112" s="35"/>
@@ -4567,10 +6121,14 @@
       <c r="N112" s="29"/>
     </row>
     <row r="113" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="127"/>
-      <c r="B113" s="130"/>
-      <c r="C113" s="26"/>
-      <c r="D113" s="12"/>
+      <c r="A113" s="139"/>
+      <c r="B113" s="122"/>
+      <c r="C113" s="26">
+        <v>69</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>104</v>
+      </c>
       <c r="E113" s="36"/>
       <c r="F113" s="34"/>
       <c r="G113" s="35"/>
@@ -4583,10 +6141,14 @@
       <c r="N113" s="29"/>
     </row>
     <row r="114" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="127"/>
-      <c r="B114" s="130"/>
-      <c r="C114" s="26"/>
-      <c r="D114" s="12"/>
+      <c r="A114" s="139"/>
+      <c r="B114" s="122"/>
+      <c r="C114" s="26">
+        <v>70</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="E114" s="36"/>
       <c r="F114" s="34"/>
       <c r="G114" s="35"/>
@@ -4599,10 +6161,14 @@
       <c r="N114" s="29"/>
     </row>
     <row r="115" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="127"/>
-      <c r="B115" s="130"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="12"/>
+      <c r="A115" s="139"/>
+      <c r="B115" s="122"/>
+      <c r="C115" s="26">
+        <v>71</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>106</v>
+      </c>
       <c r="E115" s="36"/>
       <c r="F115" s="34"/>
       <c r="G115" s="35"/>
@@ -4615,10 +6181,14 @@
       <c r="N115" s="29"/>
     </row>
     <row r="116" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="127"/>
-      <c r="B116" s="130"/>
-      <c r="C116" s="26"/>
-      <c r="D116" s="12"/>
+      <c r="A116" s="139"/>
+      <c r="B116" s="122"/>
+      <c r="C116" s="26">
+        <v>72</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>107</v>
+      </c>
       <c r="E116" s="36"/>
       <c r="F116" s="34"/>
       <c r="G116" s="35"/>
@@ -4630,11 +6200,15 @@
       <c r="M116" s="29"/>
       <c r="N116" s="29"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="128"/>
-      <c r="B117" s="131"/>
-      <c r="C117" s="26"/>
-      <c r="D117" s="12"/>
+    <row r="117" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="139"/>
+      <c r="B117" s="122"/>
+      <c r="C117" s="26">
+        <v>73</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="E117" s="36"/>
       <c r="F117" s="34"/>
       <c r="G117" s="35"/>
@@ -4647,12 +6221,14 @@
       <c r="N117" s="29"/>
     </row>
     <row r="118" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="126">
-        <v>11</v>
-      </c>
-      <c r="B118" s="129"/>
-      <c r="C118" s="26"/>
-      <c r="D118" s="11"/>
+      <c r="A118" s="139"/>
+      <c r="B118" s="122"/>
+      <c r="C118" s="26">
+        <v>74</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="E118" s="36"/>
       <c r="F118" s="34"/>
       <c r="G118" s="35"/>
@@ -4665,10 +6241,14 @@
       <c r="N118" s="29"/>
     </row>
     <row r="119" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="127"/>
-      <c r="B119" s="130"/>
-      <c r="C119" s="26"/>
-      <c r="D119" s="12"/>
+      <c r="A119" s="140"/>
+      <c r="B119" s="123"/>
+      <c r="C119" s="26">
+        <v>75</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="E119" s="36"/>
       <c r="F119" s="34"/>
       <c r="G119" s="35"/>
@@ -4681,10 +6261,18 @@
       <c r="N119" s="29"/>
     </row>
     <row r="120" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="127"/>
-      <c r="B120" s="130"/>
-      <c r="C120" s="26"/>
-      <c r="D120" s="11"/>
+      <c r="A120" s="118">
+        <v>8</v>
+      </c>
+      <c r="B120" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="C120" s="26">
+        <v>76</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="E120" s="36"/>
       <c r="F120" s="34"/>
       <c r="G120" s="35"/>
@@ -4696,11 +6284,15 @@
       <c r="M120" s="29"/>
       <c r="N120" s="29"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="127"/>
-      <c r="B121" s="130"/>
-      <c r="C121" s="26"/>
-      <c r="D121" s="12"/>
+    <row r="121" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="119"/>
+      <c r="B121" s="122"/>
+      <c r="C121" s="26">
+        <v>77</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>113</v>
+      </c>
       <c r="E121" s="36"/>
       <c r="F121" s="34"/>
       <c r="G121" s="35"/>
@@ -4713,10 +6305,14 @@
       <c r="N121" s="29"/>
     </row>
     <row r="122" spans="1:14" ht="40.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="127"/>
-      <c r="B122" s="130"/>
-      <c r="C122" s="26"/>
-      <c r="D122" s="12"/>
+      <c r="A122" s="119"/>
+      <c r="B122" s="122"/>
+      <c r="C122" s="26">
+        <v>78</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>114</v>
+      </c>
       <c r="E122" s="36"/>
       <c r="F122" s="34"/>
       <c r="G122" s="33"/>
@@ -4728,11 +6324,15 @@
       <c r="M122" s="29"/>
       <c r="N122" s="29"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A123" s="127"/>
-      <c r="B123" s="130"/>
-      <c r="C123" s="26"/>
-      <c r="D123" s="12"/>
+    <row r="123" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="119"/>
+      <c r="B123" s="122"/>
+      <c r="C123" s="26">
+        <v>79</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>115</v>
+      </c>
       <c r="E123" s="36"/>
       <c r="F123" s="34"/>
       <c r="G123" s="35"/>
@@ -4745,10 +6345,14 @@
       <c r="N123" s="29"/>
     </row>
     <row r="124" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="127"/>
-      <c r="B124" s="130"/>
-      <c r="C124" s="26"/>
-      <c r="D124" s="12"/>
+      <c r="A124" s="119"/>
+      <c r="B124" s="122"/>
+      <c r="C124" s="26">
+        <v>80</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>116</v>
+      </c>
       <c r="E124" s="36"/>
       <c r="F124" s="34"/>
       <c r="G124" s="35"/>
@@ -4761,10 +6365,14 @@
       <c r="N124" s="29"/>
     </row>
     <row r="125" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="127"/>
-      <c r="B125" s="130"/>
-      <c r="C125" s="26"/>
-      <c r="D125" s="12"/>
+      <c r="A125" s="119"/>
+      <c r="B125" s="122"/>
+      <c r="C125" s="26">
+        <v>81</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="E125" s="36"/>
       <c r="F125" s="34"/>
       <c r="G125" s="35"/>
@@ -4777,10 +6385,14 @@
       <c r="N125" s="29"/>
     </row>
     <row r="126" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="127"/>
-      <c r="B126" s="130"/>
-      <c r="C126" s="26"/>
-      <c r="D126" s="12"/>
+      <c r="A126" s="119"/>
+      <c r="B126" s="122"/>
+      <c r="C126" s="26">
+        <v>82</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>118</v>
+      </c>
       <c r="E126" s="36"/>
       <c r="F126" s="34"/>
       <c r="G126" s="35"/>
@@ -4793,10 +6405,14 @@
       <c r="N126" s="29"/>
     </row>
     <row r="127" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="127"/>
-      <c r="B127" s="130"/>
-      <c r="C127" s="26"/>
-      <c r="D127" s="12"/>
+      <c r="A127" s="119"/>
+      <c r="B127" s="122"/>
+      <c r="C127" s="26">
+        <v>83</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>119</v>
+      </c>
       <c r="E127" s="36"/>
       <c r="F127" s="34"/>
       <c r="G127" s="35"/>
@@ -4809,10 +6425,18 @@
       <c r="N127" s="29"/>
     </row>
     <row r="128" spans="1:14" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="128"/>
-      <c r="B128" s="131"/>
-      <c r="C128" s="26"/>
-      <c r="D128" s="12"/>
+      <c r="A128" s="118">
+        <v>9</v>
+      </c>
+      <c r="B128" s="121" t="s">
+        <v>120</v>
+      </c>
+      <c r="C128" s="26">
+        <v>84</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="E128" s="36"/>
       <c r="F128" s="34"/>
       <c r="G128" s="35"/>
@@ -4825,12 +6449,14 @@
       <c r="N128" s="29"/>
     </row>
     <row r="129" spans="1:14" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="126">
-        <v>12</v>
-      </c>
-      <c r="B129" s="129"/>
-      <c r="C129" s="26"/>
-      <c r="D129" s="11"/>
+      <c r="A129" s="119"/>
+      <c r="B129" s="122"/>
+      <c r="C129" s="26">
+        <v>85</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>122</v>
+      </c>
       <c r="E129" s="37"/>
       <c r="F129" s="34"/>
       <c r="G129" s="35"/>
@@ -4843,10 +6469,14 @@
       <c r="N129" s="29"/>
     </row>
     <row r="130" spans="1:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="127"/>
-      <c r="B130" s="130"/>
-      <c r="C130" s="26"/>
-      <c r="D130" s="11"/>
+      <c r="A130" s="119"/>
+      <c r="B130" s="122"/>
+      <c r="C130" s="26">
+        <v>86</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="E130" s="36"/>
       <c r="F130" s="34"/>
       <c r="G130" s="33"/>
@@ -4858,11 +6488,15 @@
       <c r="M130" s="29"/>
       <c r="N130" s="29"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A131" s="127"/>
-      <c r="B131" s="130"/>
-      <c r="C131" s="26"/>
-      <c r="D131" s="11"/>
+    <row r="131" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="119"/>
+      <c r="B131" s="122"/>
+      <c r="C131" s="26">
+        <v>87</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>124</v>
+      </c>
       <c r="E131" s="36"/>
       <c r="F131" s="34"/>
       <c r="G131" s="33"/>
@@ -4875,10 +6509,14 @@
       <c r="N131" s="29"/>
     </row>
     <row r="132" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="127"/>
-      <c r="B132" s="130"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="12"/>
+      <c r="A132" s="119"/>
+      <c r="B132" s="122"/>
+      <c r="C132" s="26">
+        <v>88</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="E132" s="36"/>
       <c r="F132" s="34"/>
       <c r="G132" s="33"/>
@@ -4891,10 +6529,14 @@
       <c r="N132" s="29"/>
     </row>
     <row r="133" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="127"/>
-      <c r="B133" s="130"/>
-      <c r="C133" s="26"/>
-      <c r="D133" s="12"/>
+      <c r="A133" s="119"/>
+      <c r="B133" s="122"/>
+      <c r="C133" s="26">
+        <v>89</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E133" s="36"/>
       <c r="F133" s="34"/>
       <c r="G133" s="33"/>
@@ -4907,10 +6549,14 @@
       <c r="N133" s="29"/>
     </row>
     <row r="134" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="127"/>
-      <c r="B134" s="130"/>
-      <c r="C134" s="26"/>
-      <c r="D134" s="11"/>
+      <c r="A134" s="119"/>
+      <c r="B134" s="122"/>
+      <c r="C134" s="26">
+        <v>90</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>127</v>
+      </c>
       <c r="E134" s="36"/>
       <c r="F134" s="34"/>
       <c r="G134" s="33"/>
@@ -4923,10 +6569,14 @@
       <c r="N134" s="29"/>
     </row>
     <row r="135" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="127"/>
-      <c r="B135" s="130"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="11"/>
+      <c r="A135" s="119"/>
+      <c r="B135" s="122"/>
+      <c r="C135" s="26">
+        <v>91</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="E135" s="36"/>
       <c r="F135" s="34"/>
       <c r="G135" s="35"/>
@@ -4939,10 +6589,14 @@
       <c r="N135" s="29"/>
     </row>
     <row r="136" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="127"/>
-      <c r="B136" s="130"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="11"/>
+      <c r="A136" s="119"/>
+      <c r="B136" s="122"/>
+      <c r="C136" s="26">
+        <v>92</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="E136" s="36"/>
       <c r="F136" s="34"/>
       <c r="G136" s="33"/>
@@ -4955,10 +6609,14 @@
       <c r="N136" s="29"/>
     </row>
     <row r="137" spans="1:14" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="127"/>
-      <c r="B137" s="130"/>
-      <c r="C137" s="26"/>
-      <c r="D137" s="12"/>
+      <c r="A137" s="119"/>
+      <c r="B137" s="122"/>
+      <c r="C137" s="26">
+        <v>93</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="E137" s="32"/>
       <c r="F137" s="32"/>
       <c r="G137" s="35"/>
@@ -4971,10 +6629,14 @@
       <c r="N137" s="29"/>
     </row>
     <row r="138" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="128"/>
-      <c r="B138" s="131"/>
-      <c r="C138" s="26"/>
-      <c r="D138" s="11"/>
+      <c r="A138" s="120"/>
+      <c r="B138" s="123"/>
+      <c r="C138" s="26">
+        <v>94</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="E138" s="36"/>
       <c r="F138" s="34"/>
       <c r="G138" s="35"/>
@@ -4987,12 +6649,18 @@
       <c r="N138" s="29"/>
     </row>
     <row r="139" spans="1:14" ht="49.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="126">
-        <v>13</v>
-      </c>
-      <c r="B139" s="132"/>
-      <c r="C139" s="26"/>
-      <c r="D139" s="11"/>
+      <c r="A139" s="118">
+        <v>10</v>
+      </c>
+      <c r="B139" s="121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C139" s="26">
+        <v>95</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>133</v>
+      </c>
       <c r="E139" s="36"/>
       <c r="F139" s="34"/>
       <c r="G139" s="35"/>
@@ -5005,10 +6673,14 @@
       <c r="N139" s="29"/>
     </row>
     <row r="140" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="127"/>
-      <c r="B140" s="133"/>
-      <c r="C140" s="26"/>
-      <c r="D140" s="11"/>
+      <c r="A140" s="119"/>
+      <c r="B140" s="122"/>
+      <c r="C140" s="26">
+        <v>96</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>134</v>
+      </c>
       <c r="E140" s="36"/>
       <c r="F140" s="34"/>
       <c r="G140" s="35"/>
@@ -5021,10 +6693,14 @@
       <c r="N140" s="29"/>
     </row>
     <row r="141" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="127"/>
-      <c r="B141" s="133"/>
-      <c r="C141" s="26"/>
-      <c r="D141" s="11"/>
+      <c r="A141" s="119"/>
+      <c r="B141" s="122"/>
+      <c r="C141" s="26">
+        <v>97</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="E141" s="34"/>
       <c r="F141" s="34"/>
       <c r="G141" s="35"/>
@@ -5037,10 +6713,14 @@
       <c r="N141" s="29"/>
     </row>
     <row r="142" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="127"/>
-      <c r="B142" s="133"/>
-      <c r="C142" s="26"/>
-      <c r="D142" s="11"/>
+      <c r="A142" s="119"/>
+      <c r="B142" s="122"/>
+      <c r="C142" s="26">
+        <v>98</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>136</v>
+      </c>
       <c r="E142" s="32"/>
       <c r="F142" s="32"/>
       <c r="G142" s="35"/>
@@ -5053,10 +6733,14 @@
       <c r="N142" s="29"/>
     </row>
     <row r="143" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="127"/>
-      <c r="B143" s="133"/>
-      <c r="C143" s="26"/>
-      <c r="D143" s="11"/>
+      <c r="A143" s="119"/>
+      <c r="B143" s="122"/>
+      <c r="C143" s="26">
+        <v>99</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>137</v>
+      </c>
       <c r="E143" s="36"/>
       <c r="F143" s="34"/>
       <c r="G143" s="33"/>
@@ -5069,10 +6753,14 @@
       <c r="N143" s="29"/>
     </row>
     <row r="144" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="127"/>
-      <c r="B144" s="133"/>
-      <c r="C144" s="26"/>
-      <c r="D144" s="11"/>
+      <c r="A144" s="119"/>
+      <c r="B144" s="122"/>
+      <c r="C144" s="26">
+        <v>100</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="E144" s="32"/>
       <c r="F144" s="32"/>
       <c r="G144" s="35"/>
@@ -5085,10 +6773,14 @@
       <c r="N144" s="29"/>
     </row>
     <row r="145" spans="1:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="127"/>
-      <c r="B145" s="133"/>
-      <c r="C145" s="26"/>
-      <c r="D145" s="11"/>
+      <c r="A145" s="119"/>
+      <c r="B145" s="122"/>
+      <c r="C145" s="26">
+        <v>101</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>139</v>
+      </c>
       <c r="E145" s="32"/>
       <c r="F145" s="32"/>
       <c r="G145" s="33"/>
@@ -5101,10 +6793,14 @@
       <c r="N145" s="29"/>
     </row>
     <row r="146" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="127"/>
-      <c r="B146" s="133"/>
-      <c r="C146" s="26"/>
-      <c r="D146" s="11"/>
+      <c r="A146" s="119"/>
+      <c r="B146" s="122"/>
+      <c r="C146" s="26">
+        <v>102</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>140</v>
+      </c>
       <c r="E146" s="36"/>
       <c r="F146" s="32"/>
       <c r="G146" s="35"/>
@@ -5117,10 +6813,14 @@
       <c r="N146" s="29"/>
     </row>
     <row r="147" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="127"/>
-      <c r="B147" s="133"/>
-      <c r="C147" s="26"/>
-      <c r="D147" s="11"/>
+      <c r="A147" s="119"/>
+      <c r="B147" s="122"/>
+      <c r="C147" s="26">
+        <v>103</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="E147" s="32"/>
       <c r="F147" s="32"/>
       <c r="G147" s="35"/>
@@ -5133,10 +6833,14 @@
       <c r="N147" s="29"/>
     </row>
     <row r="148" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="127"/>
-      <c r="B148" s="133"/>
-      <c r="C148" s="26"/>
-      <c r="D148" s="12"/>
+      <c r="A148" s="120"/>
+      <c r="B148" s="123"/>
+      <c r="C148" s="26">
+        <v>104</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="E148" s="39"/>
       <c r="F148" s="32"/>
       <c r="G148" s="35"/>
@@ -5149,10 +6853,18 @@
       <c r="N148" s="29"/>
     </row>
     <row r="149" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="127"/>
-      <c r="B149" s="133"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="12"/>
+      <c r="A149" s="118">
+        <v>11</v>
+      </c>
+      <c r="B149" s="121" t="s">
+        <v>143</v>
+      </c>
+      <c r="C149" s="26">
+        <v>105</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>144</v>
+      </c>
       <c r="E149" s="32"/>
       <c r="F149" s="32"/>
       <c r="G149" s="35"/>
@@ -5165,10 +6877,14 @@
       <c r="N149" s="29"/>
     </row>
     <row r="150" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="127"/>
-      <c r="B150" s="133"/>
-      <c r="C150" s="26"/>
-      <c r="D150" s="11"/>
+      <c r="A150" s="119"/>
+      <c r="B150" s="122"/>
+      <c r="C150" s="26">
+        <v>106</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="E150" s="32"/>
       <c r="F150" s="32"/>
       <c r="G150" s="35"/>
@@ -5181,10 +6897,14 @@
       <c r="N150" s="29"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A151" s="127"/>
-      <c r="B151" s="133"/>
-      <c r="C151" s="26"/>
-      <c r="D151" s="11"/>
+      <c r="A151" s="119"/>
+      <c r="B151" s="122"/>
+      <c r="C151" s="26">
+        <v>107</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="E151" s="37"/>
       <c r="F151" s="32"/>
       <c r="G151" s="33"/>
@@ -5197,10 +6917,14 @@
       <c r="N151" s="29"/>
     </row>
     <row r="152" spans="1:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="127"/>
-      <c r="B152" s="133"/>
-      <c r="C152" s="26"/>
-      <c r="D152" s="12"/>
+      <c r="A152" s="119"/>
+      <c r="B152" s="122"/>
+      <c r="C152" s="26">
+        <v>108</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="E152" s="32"/>
       <c r="F152" s="32"/>
       <c r="G152" s="33"/>
@@ -5213,10 +6937,14 @@
       <c r="N152" s="29"/>
     </row>
     <row r="153" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="127"/>
-      <c r="B153" s="133"/>
-      <c r="C153" s="26"/>
-      <c r="D153" s="11"/>
+      <c r="A153" s="119"/>
+      <c r="B153" s="122"/>
+      <c r="C153" s="26">
+        <v>109</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="E153" s="32"/>
       <c r="F153" s="32"/>
       <c r="G153" s="33"/>
@@ -5229,12 +6957,14 @@
       <c r="N153" s="29"/>
     </row>
     <row r="154" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="126">
-        <v>14</v>
-      </c>
-      <c r="B154" s="132"/>
-      <c r="C154" s="26"/>
-      <c r="D154" s="13"/>
+      <c r="A154" s="119"/>
+      <c r="B154" s="122"/>
+      <c r="C154" s="26">
+        <v>110</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>149</v>
+      </c>
       <c r="E154" s="40"/>
       <c r="F154" s="40"/>
       <c r="G154" s="41"/>
@@ -5247,10 +6977,14 @@
       <c r="N154" s="29"/>
     </row>
     <row r="155" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="127"/>
-      <c r="B155" s="133"/>
-      <c r="C155" s="26"/>
-      <c r="D155" s="13"/>
+      <c r="A155" s="119"/>
+      <c r="B155" s="122"/>
+      <c r="C155" s="26">
+        <v>111</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>150</v>
+      </c>
       <c r="E155" s="40"/>
       <c r="F155" s="40"/>
       <c r="G155" s="41"/>
@@ -5263,10 +6997,14 @@
       <c r="N155" s="29"/>
     </row>
     <row r="156" spans="1:14" ht="42.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="127"/>
-      <c r="B156" s="133"/>
-      <c r="C156" s="26"/>
-      <c r="D156" s="13"/>
+      <c r="A156" s="119"/>
+      <c r="B156" s="122"/>
+      <c r="C156" s="26">
+        <v>112</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>151</v>
+      </c>
       <c r="E156" s="40"/>
       <c r="F156" s="40"/>
       <c r="G156" s="35"/>
@@ -5279,10 +7017,14 @@
       <c r="N156" s="29"/>
     </row>
     <row r="157" spans="1:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="127"/>
-      <c r="B157" s="133"/>
-      <c r="C157" s="26"/>
-      <c r="D157" s="13"/>
+      <c r="A157" s="119"/>
+      <c r="B157" s="122"/>
+      <c r="C157" s="26">
+        <v>113</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>152</v>
+      </c>
       <c r="E157" s="42"/>
       <c r="F157" s="40"/>
       <c r="G157" s="43"/>
@@ -5295,10 +7037,14 @@
       <c r="N157" s="29"/>
     </row>
     <row r="158" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="127"/>
-      <c r="B158" s="133"/>
-      <c r="C158" s="26"/>
-      <c r="D158" s="20"/>
+      <c r="A158" s="119"/>
+      <c r="B158" s="122"/>
+      <c r="C158" s="26">
+        <v>114</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>153</v>
+      </c>
       <c r="E158" s="44"/>
       <c r="F158" s="14"/>
       <c r="G158" s="43"/>
@@ -5311,10 +7057,14 @@
       <c r="N158" s="29"/>
     </row>
     <row r="159" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="127"/>
-      <c r="B159" s="133"/>
-      <c r="C159" s="26"/>
-      <c r="D159" s="14"/>
+      <c r="A159" s="120"/>
+      <c r="B159" s="123"/>
+      <c r="C159" s="26">
+        <v>115</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>154</v>
+      </c>
       <c r="E159" s="45"/>
       <c r="F159" s="34"/>
       <c r="G159" s="35"/>
@@ -5327,10 +7077,18 @@
       <c r="N159" s="29"/>
     </row>
     <row r="160" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="127"/>
-      <c r="B160" s="133"/>
-      <c r="C160" s="26"/>
-      <c r="D160" s="13"/>
+      <c r="A160" s="118">
+        <v>12</v>
+      </c>
+      <c r="B160" s="121" t="s">
+        <v>155</v>
+      </c>
+      <c r="C160" s="26">
+        <v>116</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>156</v>
+      </c>
       <c r="E160" s="46"/>
       <c r="F160" s="46"/>
       <c r="G160" s="43"/>
@@ -5343,10 +7101,14 @@
       <c r="N160" s="29"/>
     </row>
     <row r="161" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="127"/>
-      <c r="B161" s="133"/>
-      <c r="C161" s="26"/>
-      <c r="D161" s="13"/>
+      <c r="A161" s="119"/>
+      <c r="B161" s="122"/>
+      <c r="C161" s="26">
+        <v>117</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>157</v>
+      </c>
       <c r="E161" s="40"/>
       <c r="F161" s="40"/>
       <c r="G161" s="43"/>
@@ -5359,10 +7121,14 @@
       <c r="N161" s="29"/>
     </row>
     <row r="162" spans="1:14" ht="34.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="127"/>
-      <c r="B162" s="133"/>
-      <c r="C162" s="26"/>
-      <c r="D162" s="13"/>
+      <c r="A162" s="119"/>
+      <c r="B162" s="122"/>
+      <c r="C162" s="26">
+        <v>118</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>158</v>
+      </c>
       <c r="E162" s="36"/>
       <c r="F162" s="34"/>
       <c r="G162" s="41"/>
@@ -5375,10 +7141,14 @@
       <c r="N162" s="29"/>
     </row>
     <row r="163" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="127"/>
-      <c r="B163" s="133"/>
-      <c r="C163" s="26"/>
-      <c r="D163" s="13"/>
+      <c r="A163" s="119"/>
+      <c r="B163" s="122"/>
+      <c r="C163" s="26">
+        <v>119</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>159</v>
+      </c>
       <c r="E163" s="36"/>
       <c r="F163" s="34"/>
       <c r="G163" s="35"/>
@@ -5391,10 +7161,14 @@
       <c r="N163" s="29"/>
     </row>
     <row r="164" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="127"/>
-      <c r="B164" s="133"/>
-      <c r="C164" s="26"/>
-      <c r="D164" s="13"/>
+      <c r="A164" s="119"/>
+      <c r="B164" s="122"/>
+      <c r="C164" s="26">
+        <v>120</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>160</v>
+      </c>
       <c r="E164" s="46"/>
       <c r="F164" s="34"/>
       <c r="G164" s="35"/>
@@ -5407,10 +7181,14 @@
       <c r="N164" s="29"/>
     </row>
     <row r="165" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="127"/>
-      <c r="B165" s="133"/>
-      <c r="C165" s="26"/>
-      <c r="D165" s="14"/>
+      <c r="A165" s="119"/>
+      <c r="B165" s="122"/>
+      <c r="C165" s="26">
+        <v>121</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>161</v>
+      </c>
       <c r="E165" s="36"/>
       <c r="F165" s="34"/>
       <c r="G165" s="35"/>
@@ -5423,12 +7201,14 @@
       <c r="N165" s="29"/>
     </row>
     <row r="166" spans="1:14" ht="34.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="126">
-        <v>15</v>
-      </c>
-      <c r="B166" s="132"/>
-      <c r="C166" s="26"/>
-      <c r="D166" s="11"/>
+      <c r="A166" s="119"/>
+      <c r="B166" s="122"/>
+      <c r="C166" s="26">
+        <v>122</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>162</v>
+      </c>
       <c r="E166" s="37"/>
       <c r="F166" s="34"/>
       <c r="G166" s="33"/>
@@ -5441,10 +7221,14 @@
       <c r="N166" s="29"/>
     </row>
     <row r="167" spans="1:14" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="127"/>
-      <c r="B167" s="133"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="11"/>
+      <c r="A167" s="119"/>
+      <c r="B167" s="122"/>
+      <c r="C167" s="26">
+        <v>123</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>163</v>
+      </c>
       <c r="E167" s="36"/>
       <c r="F167" s="34"/>
       <c r="G167" s="35"/>
@@ -5457,10 +7241,14 @@
       <c r="N167" s="29"/>
     </row>
     <row r="168" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="127"/>
-      <c r="B168" s="133"/>
-      <c r="C168" s="26"/>
-      <c r="D168" s="12"/>
+      <c r="A168" s="119"/>
+      <c r="B168" s="122"/>
+      <c r="C168" s="26">
+        <v>124</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="E168" s="36"/>
       <c r="F168" s="34"/>
       <c r="G168" s="35"/>
@@ -5472,11 +7260,15 @@
       <c r="M168" s="29"/>
       <c r="N168" s="29"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A169" s="127"/>
-      <c r="B169" s="133"/>
-      <c r="C169" s="26"/>
-      <c r="D169" s="11"/>
+    <row r="169" spans="1:14" ht="39" x14ac:dyDescent="0.35">
+      <c r="A169" s="120"/>
+      <c r="B169" s="123"/>
+      <c r="C169" s="26">
+        <v>125</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>165</v>
+      </c>
       <c r="E169" s="34"/>
       <c r="F169" s="34"/>
       <c r="G169" s="33"/>
@@ -5488,11 +7280,19 @@
       <c r="M169" s="29"/>
       <c r="N169" s="29"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A170" s="127"/>
-      <c r="B170" s="133"/>
-      <c r="C170" s="26"/>
-      <c r="D170" s="12"/>
+    <row r="170" spans="1:14" ht="65" x14ac:dyDescent="0.35">
+      <c r="A170" s="118">
+        <v>13</v>
+      </c>
+      <c r="B170" s="131" t="s">
+        <v>166</v>
+      </c>
+      <c r="C170" s="26">
+        <v>126</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>167</v>
+      </c>
       <c r="E170" s="34"/>
       <c r="F170" s="34"/>
       <c r="G170" s="35"/>
@@ -5504,11 +7304,15 @@
       <c r="M170" s="29"/>
       <c r="N170" s="29"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A171" s="127"/>
-      <c r="B171" s="133"/>
-      <c r="C171" s="26"/>
-      <c r="D171" s="12"/>
+    <row r="171" spans="1:14" ht="52" x14ac:dyDescent="0.35">
+      <c r="A171" s="119"/>
+      <c r="B171" s="132"/>
+      <c r="C171" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>169</v>
+      </c>
       <c r="E171" s="34"/>
       <c r="F171" s="34"/>
       <c r="G171" s="33"/>
@@ -5521,10 +7325,14 @@
       <c r="N171" s="29"/>
     </row>
     <row r="172" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="127"/>
-      <c r="B172" s="133"/>
-      <c r="C172" s="26"/>
-      <c r="D172" s="12"/>
+      <c r="A172" s="119"/>
+      <c r="B172" s="132"/>
+      <c r="C172" s="26">
+        <v>128</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="E172" s="36"/>
       <c r="F172" s="34"/>
       <c r="G172" s="33"/>
@@ -5537,10 +7345,14 @@
       <c r="N172" s="29"/>
     </row>
     <row r="173" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="127"/>
-      <c r="B173" s="133"/>
-      <c r="C173" s="26"/>
-      <c r="D173" s="11"/>
+      <c r="A173" s="119"/>
+      <c r="B173" s="132"/>
+      <c r="C173" s="26">
+        <v>129</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>171</v>
+      </c>
       <c r="E173" s="36"/>
       <c r="F173" s="32"/>
       <c r="G173" s="33"/>
@@ -5553,10 +7365,14 @@
       <c r="N173" s="29"/>
     </row>
     <row r="174" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="127"/>
-      <c r="B174" s="133"/>
-      <c r="C174" s="26"/>
-      <c r="D174" s="12"/>
+      <c r="A174" s="119"/>
+      <c r="B174" s="132"/>
+      <c r="C174" s="26">
+        <v>130</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>172</v>
+      </c>
       <c r="E174" s="32"/>
       <c r="F174" s="32"/>
       <c r="G174" s="33"/>
@@ -5569,10 +7385,14 @@
       <c r="N174" s="29"/>
     </row>
     <row r="175" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="127"/>
-      <c r="B175" s="133"/>
-      <c r="C175" s="26"/>
-      <c r="D175" s="11"/>
+      <c r="A175" s="119"/>
+      <c r="B175" s="132"/>
+      <c r="C175" s="26">
+        <v>131</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>173</v>
+      </c>
       <c r="E175" s="32"/>
       <c r="F175" s="32"/>
       <c r="G175" s="33"/>
@@ -5585,10 +7405,14 @@
       <c r="N175" s="29"/>
     </row>
     <row r="176" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="128"/>
-      <c r="B176" s="134"/>
-      <c r="C176" s="26"/>
-      <c r="D176" s="11"/>
+      <c r="A176" s="119"/>
+      <c r="B176" s="132"/>
+      <c r="C176" s="26">
+        <v>132</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>174</v>
+      </c>
       <c r="E176" s="32"/>
       <c r="F176" s="32"/>
       <c r="G176" s="33"/>
@@ -5601,12 +7425,14 @@
       <c r="N176" s="29"/>
     </row>
     <row r="177" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="126">
-        <v>16</v>
-      </c>
-      <c r="B177" s="129"/>
-      <c r="C177" s="26"/>
-      <c r="D177" s="11"/>
+      <c r="A177" s="119"/>
+      <c r="B177" s="132"/>
+      <c r="C177" s="26">
+        <v>133</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>175</v>
+      </c>
       <c r="E177" s="34"/>
       <c r="F177" s="34"/>
       <c r="G177" s="35"/>
@@ -5619,10 +7445,14 @@
       <c r="N177" s="29"/>
     </row>
     <row r="178" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="127"/>
-      <c r="B178" s="130"/>
-      <c r="C178" s="26"/>
-      <c r="D178" s="11"/>
+      <c r="A178" s="119"/>
+      <c r="B178" s="132"/>
+      <c r="C178" s="26">
+        <v>134</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>176</v>
+      </c>
       <c r="E178" s="34"/>
       <c r="F178" s="34"/>
       <c r="G178" s="35"/>
@@ -5635,10 +7465,14 @@
       <c r="N178" s="29"/>
     </row>
     <row r="179" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="128"/>
-      <c r="B179" s="131"/>
-      <c r="C179" s="26"/>
-      <c r="D179" s="11"/>
+      <c r="A179" s="119"/>
+      <c r="B179" s="132"/>
+      <c r="C179" s="26">
+        <v>135</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="E179" s="34"/>
       <c r="F179" s="34"/>
       <c r="G179" s="35"/>
@@ -5651,12 +7485,14 @@
       <c r="N179" s="29"/>
     </row>
     <row r="180" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="126">
-        <v>17</v>
-      </c>
+      <c r="A180" s="119"/>
       <c r="B180" s="132"/>
-      <c r="C180" s="26"/>
-      <c r="D180" s="11"/>
+      <c r="C180" s="26">
+        <v>136</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>178</v>
+      </c>
       <c r="E180" s="34"/>
       <c r="F180" s="34"/>
       <c r="G180" s="35"/>
@@ -5669,10 +7505,14 @@
       <c r="N180" s="29"/>
     </row>
     <row r="181" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="127"/>
-      <c r="B181" s="133"/>
-      <c r="C181" s="26"/>
-      <c r="D181" s="11"/>
+      <c r="A181" s="119"/>
+      <c r="B181" s="132"/>
+      <c r="C181" s="26">
+        <v>137</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>179</v>
+      </c>
       <c r="E181" s="32"/>
       <c r="F181" s="32"/>
       <c r="G181" s="35"/>
@@ -5685,10 +7525,14 @@
       <c r="N181" s="29"/>
     </row>
     <row r="182" spans="1:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="127"/>
-      <c r="B182" s="133"/>
-      <c r="C182" s="26"/>
-      <c r="D182" s="11"/>
+      <c r="A182" s="119"/>
+      <c r="B182" s="132"/>
+      <c r="C182" s="26">
+        <v>138</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>180</v>
+      </c>
       <c r="E182" s="36"/>
       <c r="F182" s="34"/>
       <c r="G182" s="33"/>
@@ -5701,10 +7545,14 @@
       <c r="N182" s="29"/>
     </row>
     <row r="183" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="127"/>
-      <c r="B183" s="133"/>
-      <c r="C183" s="26"/>
-      <c r="D183" s="11"/>
+      <c r="A183" s="119"/>
+      <c r="B183" s="132"/>
+      <c r="C183" s="26">
+        <v>139</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>181</v>
+      </c>
       <c r="E183" s="36"/>
       <c r="F183" s="34"/>
       <c r="G183" s="35"/>
@@ -5717,10 +7565,14 @@
       <c r="N183" s="29"/>
     </row>
     <row r="184" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="127"/>
-      <c r="B184" s="133"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="11"/>
+      <c r="A184" s="119"/>
+      <c r="B184" s="132"/>
+      <c r="C184" s="26">
+        <v>140</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>182</v>
+      </c>
       <c r="E184" s="36"/>
       <c r="F184" s="34"/>
       <c r="G184" s="35"/>
@@ -5733,10 +7585,18 @@
       <c r="N184" s="29"/>
     </row>
     <row r="185" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="127"/>
-      <c r="B185" s="133"/>
-      <c r="C185" s="26"/>
-      <c r="D185" s="11"/>
+      <c r="A185" s="118">
+        <v>14</v>
+      </c>
+      <c r="B185" s="131" t="s">
+        <v>183</v>
+      </c>
+      <c r="C185" s="26">
+        <v>141</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>184</v>
+      </c>
       <c r="E185" s="36"/>
       <c r="F185" s="34"/>
       <c r="G185" s="35"/>
@@ -5749,10 +7609,14 @@
       <c r="N185" s="29"/>
     </row>
     <row r="186" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="127"/>
-      <c r="B186" s="133"/>
-      <c r="C186" s="26"/>
-      <c r="D186" s="11"/>
+      <c r="A186" s="119"/>
+      <c r="B186" s="132"/>
+      <c r="C186" s="26">
+        <v>142</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>185</v>
+      </c>
       <c r="E186" s="36"/>
       <c r="F186" s="34"/>
       <c r="G186" s="35"/>
@@ -5764,11 +7628,15 @@
       <c r="M186" s="29"/>
       <c r="N186" s="29"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A187" s="128"/>
-      <c r="B187" s="134"/>
-      <c r="C187" s="26"/>
-      <c r="D187" s="11"/>
+    <row r="187" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+      <c r="A187" s="119"/>
+      <c r="B187" s="132"/>
+      <c r="C187" s="26">
+        <v>143</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>186</v>
+      </c>
       <c r="E187" s="32"/>
       <c r="F187" s="32"/>
       <c r="G187" s="33"/>
@@ -5781,12 +7649,14 @@
       <c r="N187" s="29"/>
     </row>
     <row r="188" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="126">
-        <v>18</v>
-      </c>
-      <c r="B188" s="129"/>
-      <c r="C188" s="26"/>
-      <c r="D188" s="12"/>
+      <c r="A188" s="119"/>
+      <c r="B188" s="132"/>
+      <c r="C188" s="26">
+        <v>144</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>187</v>
+      </c>
       <c r="E188" s="34"/>
       <c r="F188" s="34"/>
       <c r="G188" s="35"/>
@@ -5799,10 +7669,14 @@
       <c r="N188" s="29"/>
     </row>
     <row r="189" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="127"/>
-      <c r="B189" s="130"/>
-      <c r="C189" s="26"/>
-      <c r="D189" s="11"/>
+      <c r="A189" s="119"/>
+      <c r="B189" s="132"/>
+      <c r="C189" s="26">
+        <v>145</v>
+      </c>
+      <c r="D189" s="20" t="s">
+        <v>188</v>
+      </c>
       <c r="E189" s="36"/>
       <c r="F189" s="34"/>
       <c r="G189" s="33"/>
@@ -5815,10 +7689,14 @@
       <c r="N189" s="29"/>
     </row>
     <row r="190" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="127"/>
-      <c r="B190" s="130"/>
-      <c r="C190" s="26"/>
-      <c r="D190" s="11"/>
+      <c r="A190" s="119"/>
+      <c r="B190" s="132"/>
+      <c r="C190" s="26">
+        <v>146</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>189</v>
+      </c>
       <c r="E190" s="36"/>
       <c r="F190" s="34"/>
       <c r="G190" s="33"/>
@@ -5831,10 +7709,14 @@
       <c r="N190" s="29"/>
     </row>
     <row r="191" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="127"/>
-      <c r="B191" s="130"/>
-      <c r="C191" s="26"/>
-      <c r="D191" s="11"/>
+      <c r="A191" s="119"/>
+      <c r="B191" s="132"/>
+      <c r="C191" s="26">
+        <v>147</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>190</v>
+      </c>
       <c r="E191" s="36"/>
       <c r="F191" s="34"/>
       <c r="G191" s="33"/>
@@ -5847,10 +7729,14 @@
       <c r="N191" s="29"/>
     </row>
     <row r="192" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="127"/>
-      <c r="B192" s="130"/>
-      <c r="C192" s="26"/>
-      <c r="D192" s="11"/>
+      <c r="A192" s="119"/>
+      <c r="B192" s="132"/>
+      <c r="C192" s="26">
+        <v>148</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>191</v>
+      </c>
       <c r="E192" s="36"/>
       <c r="F192" s="34"/>
       <c r="G192" s="33"/>
@@ -5863,10 +7749,14 @@
       <c r="N192" s="29"/>
     </row>
     <row r="193" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="128"/>
-      <c r="B193" s="131"/>
-      <c r="C193" s="26"/>
-      <c r="D193" s="11"/>
+      <c r="A193" s="119"/>
+      <c r="B193" s="132"/>
+      <c r="C193" s="26">
+        <v>149</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>192</v>
+      </c>
       <c r="E193" s="36"/>
       <c r="F193" s="34"/>
       <c r="G193" s="35"/>
@@ -5879,12 +7769,14 @@
       <c r="N193" s="29"/>
     </row>
     <row r="194" spans="1:14" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="120">
-        <v>19</v>
-      </c>
-      <c r="B194" s="123"/>
-      <c r="C194" s="26"/>
-      <c r="D194" s="11"/>
+      <c r="A194" s="119"/>
+      <c r="B194" s="132"/>
+      <c r="C194" s="26">
+        <v>150</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>193</v>
+      </c>
       <c r="E194" s="34"/>
       <c r="F194" s="34"/>
       <c r="G194" s="35"/>
@@ -5897,10 +7789,14 @@
       <c r="N194" s="29"/>
     </row>
     <row r="195" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="121"/>
-      <c r="B195" s="124"/>
-      <c r="C195" s="26"/>
-      <c r="D195" s="15"/>
+      <c r="A195" s="119"/>
+      <c r="B195" s="132"/>
+      <c r="C195" s="26">
+        <v>151</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>194</v>
+      </c>
       <c r="E195" s="34"/>
       <c r="F195" s="34"/>
       <c r="G195" s="47"/>
@@ -5913,10 +7809,14 @@
       <c r="N195" s="29"/>
     </row>
     <row r="196" spans="1:14" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="121"/>
-      <c r="B196" s="124"/>
-      <c r="C196" s="26"/>
-      <c r="D196" s="15"/>
+      <c r="A196" s="119"/>
+      <c r="B196" s="132"/>
+      <c r="C196" s="26">
+        <v>152</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>195</v>
+      </c>
       <c r="E196" s="34"/>
       <c r="F196" s="34"/>
       <c r="G196" s="47"/>
@@ -5929,10 +7829,18 @@
       <c r="N196" s="29"/>
     </row>
     <row r="197" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="121"/>
-      <c r="B197" s="124"/>
-      <c r="C197" s="26"/>
-      <c r="D197" s="15"/>
+      <c r="A197" s="118">
+        <v>15</v>
+      </c>
+      <c r="B197" s="131" t="s">
+        <v>196</v>
+      </c>
+      <c r="C197" s="26">
+        <v>153</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>197</v>
+      </c>
       <c r="E197" s="34"/>
       <c r="F197" s="34"/>
       <c r="G197" s="47"/>
@@ -5945,10 +7853,14 @@
       <c r="N197" s="29"/>
     </row>
     <row r="198" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A198" s="121"/>
-      <c r="B198" s="124"/>
-      <c r="C198" s="26"/>
-      <c r="D198" s="15"/>
+      <c r="A198" s="119"/>
+      <c r="B198" s="132"/>
+      <c r="C198" s="26">
+        <v>154</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="E198" s="34"/>
       <c r="F198" s="34"/>
       <c r="G198" s="47"/>
@@ -5961,10 +7873,14 @@
       <c r="N198" s="29"/>
     </row>
     <row r="199" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="122"/>
-      <c r="B199" s="125"/>
-      <c r="C199" s="26"/>
-      <c r="D199" s="15"/>
+      <c r="A199" s="119"/>
+      <c r="B199" s="132"/>
+      <c r="C199" s="26">
+        <v>155</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>199</v>
+      </c>
       <c r="E199" s="34"/>
       <c r="F199" s="34"/>
       <c r="G199" s="47"/>
@@ -5977,12 +7893,14 @@
       <c r="N199" s="29"/>
     </row>
     <row r="200" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="154">
-        <v>20</v>
-      </c>
-      <c r="B200" s="114"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="4"/>
+      <c r="A200" s="119"/>
+      <c r="B200" s="132"/>
+      <c r="C200" s="26">
+        <v>156</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="E200" s="34"/>
       <c r="F200" s="34"/>
       <c r="G200" s="48"/>
@@ -5995,10 +7913,14 @@
       <c r="N200" s="29"/>
     </row>
     <row r="201" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="155"/>
-      <c r="B201" s="115"/>
-      <c r="C201" s="26"/>
-      <c r="D201" s="5"/>
+      <c r="A201" s="119"/>
+      <c r="B201" s="132"/>
+      <c r="C201" s="26">
+        <v>157</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>201</v>
+      </c>
       <c r="E201" s="34"/>
       <c r="F201" s="34"/>
       <c r="G201" s="21"/>
@@ -6011,10 +7933,14 @@
       <c r="N201" s="29"/>
     </row>
     <row r="202" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="155"/>
-      <c r="B202" s="115"/>
-      <c r="C202" s="26"/>
-      <c r="D202" s="5"/>
+      <c r="A202" s="119"/>
+      <c r="B202" s="132"/>
+      <c r="C202" s="26">
+        <v>158</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>202</v>
+      </c>
       <c r="E202" s="34"/>
       <c r="F202" s="34"/>
       <c r="G202" s="21"/>
@@ -6027,10 +7953,14 @@
       <c r="N202" s="29"/>
     </row>
     <row r="203" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="155"/>
-      <c r="B203" s="115"/>
-      <c r="C203" s="26"/>
-      <c r="D203" s="6"/>
+      <c r="A203" s="119"/>
+      <c r="B203" s="132"/>
+      <c r="C203" s="26">
+        <v>160</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>203</v>
+      </c>
       <c r="E203" s="34"/>
       <c r="F203" s="34"/>
       <c r="G203" s="49"/>
@@ -6043,10 +7973,14 @@
       <c r="N203" s="29"/>
     </row>
     <row r="204" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="155"/>
-      <c r="B204" s="115"/>
-      <c r="C204" s="26"/>
-      <c r="D204" s="6"/>
+      <c r="A204" s="119"/>
+      <c r="B204" s="132"/>
+      <c r="C204" s="26">
+        <v>161</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>204</v>
+      </c>
       <c r="E204" s="34"/>
       <c r="F204" s="34"/>
       <c r="G204" s="49"/>
@@ -6059,10 +7993,14 @@
       <c r="N204" s="29"/>
     </row>
     <row r="205" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="155"/>
-      <c r="B205" s="115"/>
-      <c r="C205" s="26"/>
-      <c r="D205" s="7"/>
+      <c r="A205" s="119"/>
+      <c r="B205" s="132"/>
+      <c r="C205" s="26">
+        <v>162</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>205</v>
+      </c>
       <c r="E205" s="34"/>
       <c r="F205" s="34"/>
       <c r="G205" s="50"/>
@@ -6075,10 +8013,14 @@
       <c r="N205" s="29"/>
     </row>
     <row r="206" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="155"/>
-      <c r="B206" s="115"/>
-      <c r="C206" s="26"/>
-      <c r="D206" s="16"/>
+      <c r="A206" s="119"/>
+      <c r="B206" s="132"/>
+      <c r="C206" s="26">
+        <v>163</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>206</v>
+      </c>
       <c r="E206" s="34"/>
       <c r="F206" s="34"/>
       <c r="G206" s="51"/>
@@ -6091,10 +8033,14 @@
       <c r="N206" s="29"/>
     </row>
     <row r="207" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="155"/>
-      <c r="B207" s="115"/>
-      <c r="C207" s="26"/>
-      <c r="D207" s="8"/>
+      <c r="A207" s="120"/>
+      <c r="B207" s="133"/>
+      <c r="C207" s="26">
+        <v>164</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>207</v>
+      </c>
       <c r="E207" s="34"/>
       <c r="F207" s="34"/>
       <c r="G207" s="52"/>
@@ -6107,10 +8053,18 @@
       <c r="N207" s="29"/>
     </row>
     <row r="208" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="155"/>
-      <c r="B208" s="116"/>
-      <c r="C208" s="26"/>
-      <c r="D208" s="5"/>
+      <c r="A208" s="118">
+        <v>16</v>
+      </c>
+      <c r="B208" s="121" t="s">
+        <v>208</v>
+      </c>
+      <c r="C208" s="26">
+        <v>165</v>
+      </c>
+      <c r="D208" s="11" t="s">
+        <v>209</v>
+      </c>
       <c r="E208" s="34"/>
       <c r="F208" s="34"/>
       <c r="G208" s="21"/>
@@ -6123,12 +8077,14 @@
       <c r="N208" s="29"/>
     </row>
     <row r="209" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="142">
-        <v>21</v>
-      </c>
-      <c r="B209" s="117"/>
-      <c r="C209" s="26"/>
-      <c r="D209" s="17"/>
+      <c r="A209" s="119"/>
+      <c r="B209" s="122"/>
+      <c r="C209" s="26">
+        <v>166</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>210</v>
+      </c>
       <c r="E209" s="34"/>
       <c r="F209" s="34"/>
       <c r="G209" s="53"/>
@@ -6141,10 +8097,14 @@
       <c r="N209" s="29"/>
     </row>
     <row r="210" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="142"/>
-      <c r="B210" s="110"/>
-      <c r="C210" s="26"/>
-      <c r="D210" s="17"/>
+      <c r="A210" s="120"/>
+      <c r="B210" s="123"/>
+      <c r="C210" s="26">
+        <v>167</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>211</v>
+      </c>
       <c r="E210" s="34"/>
       <c r="F210" s="34"/>
       <c r="G210" s="53"/>
@@ -6157,10 +8117,18 @@
       <c r="N210" s="29"/>
     </row>
     <row r="211" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="142"/>
-      <c r="B211" s="110"/>
-      <c r="C211" s="26"/>
-      <c r="D211" s="17"/>
+      <c r="A211" s="118">
+        <v>17</v>
+      </c>
+      <c r="B211" s="131" t="s">
+        <v>212</v>
+      </c>
+      <c r="C211" s="26">
+        <v>168</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>213</v>
+      </c>
       <c r="E211" s="34"/>
       <c r="F211" s="34"/>
       <c r="G211" s="54"/>
@@ -6173,10 +8141,14 @@
       <c r="N211" s="29"/>
     </row>
     <row r="212" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="142"/>
-      <c r="B212" s="110"/>
-      <c r="C212" s="26"/>
-      <c r="D212" s="17"/>
+      <c r="A212" s="119"/>
+      <c r="B212" s="132"/>
+      <c r="C212" s="26">
+        <v>169</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>214</v>
+      </c>
       <c r="E212" s="34"/>
       <c r="F212" s="34"/>
       <c r="G212" s="54"/>
@@ -6188,11 +8160,15 @@
       <c r="M212" s="29"/>
       <c r="N212" s="29"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A213" s="142"/>
-      <c r="B213" s="118"/>
-      <c r="C213" s="26"/>
-      <c r="D213" s="17"/>
+    <row r="213" spans="1:14" ht="65" x14ac:dyDescent="0.35">
+      <c r="A213" s="119"/>
+      <c r="B213" s="132"/>
+      <c r="C213" s="26">
+        <v>170</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>215</v>
+      </c>
       <c r="E213" s="34"/>
       <c r="F213" s="34"/>
       <c r="G213" s="53"/>
@@ -6204,13 +8180,15 @@
       <c r="M213" s="29"/>
       <c r="N213" s="29"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A214" s="156">
-        <v>22</v>
-      </c>
-      <c r="B214" s="106"/>
-      <c r="C214" s="26"/>
-      <c r="D214" s="5"/>
+    <row r="214" spans="1:14" ht="78" x14ac:dyDescent="0.35">
+      <c r="A214" s="119"/>
+      <c r="B214" s="132"/>
+      <c r="C214" s="26">
+        <v>171</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>216</v>
+      </c>
       <c r="E214" s="34"/>
       <c r="F214" s="34"/>
       <c r="G214" s="53"/>
@@ -6223,10 +8201,14 @@
       <c r="N214" s="29"/>
     </row>
     <row r="215" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="156"/>
-      <c r="B215" s="107"/>
-      <c r="C215" s="26"/>
-      <c r="D215" s="7"/>
+      <c r="A215" s="119"/>
+      <c r="B215" s="132"/>
+      <c r="C215" s="26">
+        <v>172</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>217</v>
+      </c>
       <c r="E215" s="34"/>
       <c r="F215" s="34"/>
       <c r="G215" s="55"/>
@@ -6239,10 +8221,14 @@
       <c r="N215" s="29"/>
     </row>
     <row r="216" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="156"/>
-      <c r="B216" s="107"/>
-      <c r="C216" s="26"/>
-      <c r="D216" s="16"/>
+      <c r="A216" s="119"/>
+      <c r="B216" s="132"/>
+      <c r="C216" s="26">
+        <v>173</v>
+      </c>
+      <c r="D216" s="11" t="s">
+        <v>218</v>
+      </c>
       <c r="E216" s="34"/>
       <c r="F216" s="34"/>
       <c r="G216" s="53"/>
@@ -6255,10 +8241,14 @@
       <c r="N216" s="29"/>
     </row>
     <row r="217" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="156"/>
-      <c r="B217" s="107"/>
-      <c r="C217" s="26"/>
-      <c r="D217" s="6"/>
+      <c r="A217" s="119"/>
+      <c r="B217" s="132"/>
+      <c r="C217" s="26">
+        <v>174</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>219</v>
+      </c>
       <c r="E217" s="56"/>
       <c r="F217" s="56"/>
       <c r="G217" s="57"/>
@@ -6271,10 +8261,14 @@
       <c r="N217" s="29"/>
     </row>
     <row r="218" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="156"/>
-      <c r="B218" s="107"/>
-      <c r="C218" s="26"/>
-      <c r="D218" s="5"/>
+      <c r="A218" s="120"/>
+      <c r="B218" s="133"/>
+      <c r="C218" s="26">
+        <v>175</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>220</v>
+      </c>
       <c r="E218" s="58"/>
       <c r="F218" s="58"/>
       <c r="G218" s="59"/>
@@ -6287,10 +8281,18 @@
       <c r="N218" s="29"/>
     </row>
     <row r="219" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="156"/>
-      <c r="B219" s="107"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="5"/>
+      <c r="A219" s="118">
+        <v>18</v>
+      </c>
+      <c r="B219" s="121" t="s">
+        <v>221</v>
+      </c>
+      <c r="C219" s="26">
+        <v>176</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>222</v>
+      </c>
       <c r="E219" s="60"/>
       <c r="F219" s="58"/>
       <c r="G219" s="59"/>
@@ -6303,10 +8305,14 @@
       <c r="N219" s="29"/>
     </row>
     <row r="220" spans="1:14" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="156"/>
-      <c r="B220" s="107"/>
-      <c r="C220" s="26"/>
-      <c r="D220" s="5"/>
+      <c r="A220" s="119"/>
+      <c r="B220" s="122"/>
+      <c r="C220" s="26">
+        <v>177</v>
+      </c>
+      <c r="D220" s="11" t="s">
+        <v>223</v>
+      </c>
       <c r="E220" s="58"/>
       <c r="F220" s="58"/>
       <c r="G220" s="59"/>
@@ -6319,10 +8325,14 @@
       <c r="N220" s="29"/>
     </row>
     <row r="221" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="156"/>
-      <c r="B221" s="108"/>
-      <c r="C221" s="26"/>
-      <c r="D221" s="5"/>
+      <c r="A221" s="119"/>
+      <c r="B221" s="122"/>
+      <c r="C221" s="26">
+        <v>178</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>224</v>
+      </c>
       <c r="E221" s="58"/>
       <c r="F221" s="58"/>
       <c r="G221" s="59"/>
@@ -6335,12 +8345,14 @@
       <c r="N221" s="29"/>
     </row>
     <row r="222" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="142">
-        <v>23</v>
-      </c>
-      <c r="B222" s="117"/>
-      <c r="C222" s="26"/>
-      <c r="D222" s="7"/>
+      <c r="A222" s="119"/>
+      <c r="B222" s="122"/>
+      <c r="C222" s="26">
+        <v>179</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>225</v>
+      </c>
       <c r="E222" s="34"/>
       <c r="F222" s="34"/>
       <c r="G222" s="55"/>
@@ -6353,10 +8365,14 @@
       <c r="N222" s="29"/>
     </row>
     <row r="223" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="142"/>
-      <c r="B223" s="110"/>
-      <c r="C223" s="26"/>
-      <c r="D223" s="16"/>
+      <c r="A223" s="119"/>
+      <c r="B223" s="122"/>
+      <c r="C223" s="26">
+        <v>180</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>226</v>
+      </c>
       <c r="E223" s="34"/>
       <c r="F223" s="34"/>
       <c r="G223" s="35"/>
@@ -6369,10 +8385,14 @@
       <c r="N223" s="29"/>
     </row>
     <row r="224" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="142"/>
-      <c r="B224" s="110"/>
-      <c r="C224" s="26"/>
-      <c r="D224" s="6"/>
+      <c r="A224" s="120"/>
+      <c r="B224" s="123"/>
+      <c r="C224" s="26">
+        <v>190</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>227</v>
+      </c>
       <c r="E224" s="34"/>
       <c r="F224" s="34"/>
       <c r="G224" s="57"/>
@@ -6385,10 +8405,18 @@
       <c r="N224" s="29"/>
     </row>
     <row r="225" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="142"/>
-      <c r="B225" s="110"/>
-      <c r="C225" s="26"/>
-      <c r="D225" s="5"/>
+      <c r="A225" s="141">
+        <v>19</v>
+      </c>
+      <c r="B225" s="144" t="s">
+        <v>228</v>
+      </c>
+      <c r="C225" s="26">
+        <v>191</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>229</v>
+      </c>
       <c r="E225" s="34"/>
       <c r="F225" s="34"/>
       <c r="G225" s="35"/>
@@ -6402,9 +8430,13 @@
     </row>
     <row r="226" spans="1:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="142"/>
-      <c r="B226" s="110"/>
-      <c r="C226" s="26"/>
-      <c r="D226" s="5"/>
+      <c r="B226" s="145"/>
+      <c r="C226" s="26">
+        <v>192</v>
+      </c>
+      <c r="D226" s="15" t="s">
+        <v>230</v>
+      </c>
       <c r="E226" s="58"/>
       <c r="F226" s="58"/>
       <c r="G226" s="59"/>
@@ -6418,9 +8450,13 @@
     </row>
     <row r="227" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="142"/>
-      <c r="B227" s="110"/>
-      <c r="C227" s="26"/>
-      <c r="D227" s="5"/>
+      <c r="B227" s="145"/>
+      <c r="C227" s="26">
+        <v>193</v>
+      </c>
+      <c r="D227" s="15" t="s">
+        <v>231</v>
+      </c>
       <c r="E227" s="34"/>
       <c r="F227" s="34"/>
       <c r="G227" s="35"/>
@@ -6434,9 +8470,13 @@
     </row>
     <row r="228" spans="1:14" ht="23.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="142"/>
-      <c r="B228" s="110"/>
-      <c r="C228" s="26"/>
-      <c r="D228" s="5"/>
+      <c r="B228" s="145"/>
+      <c r="C228" s="26">
+        <v>194</v>
+      </c>
+      <c r="D228" s="15" t="s">
+        <v>232</v>
+      </c>
       <c r="E228" s="34"/>
       <c r="F228" s="34"/>
       <c r="G228" s="35"/>
@@ -6450,9 +8490,13 @@
     </row>
     <row r="229" spans="1:14" ht="34.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="142"/>
-      <c r="B229" s="110"/>
-      <c r="C229" s="26"/>
-      <c r="D229" s="5"/>
+      <c r="B229" s="145"/>
+      <c r="C229" s="26">
+        <v>195</v>
+      </c>
+      <c r="D229" s="15" t="s">
+        <v>233</v>
+      </c>
       <c r="E229" s="58"/>
       <c r="F229" s="58"/>
       <c r="G229" s="59"/>
@@ -6465,10 +8509,14 @@
       <c r="N229" s="29"/>
     </row>
     <row r="230" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="142"/>
-      <c r="B230" s="110"/>
-      <c r="C230" s="26"/>
-      <c r="D230" s="5"/>
+      <c r="A230" s="143"/>
+      <c r="B230" s="146"/>
+      <c r="C230" s="26">
+        <v>196</v>
+      </c>
+      <c r="D230" s="15" t="s">
+        <v>234</v>
+      </c>
       <c r="E230" s="34"/>
       <c r="F230" s="34"/>
       <c r="G230" s="59"/>
@@ -6481,10 +8529,18 @@
       <c r="N230" s="29"/>
     </row>
     <row r="231" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="142"/>
-      <c r="B231" s="110"/>
-      <c r="C231" s="26"/>
-      <c r="D231" s="5"/>
+      <c r="A231" s="126">
+        <v>20</v>
+      </c>
+      <c r="B231" s="147" t="s">
+        <v>235</v>
+      </c>
+      <c r="C231" s="26">
+        <v>197</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="E231" s="34"/>
       <c r="F231" s="34"/>
       <c r="G231" s="59"/>
@@ -6497,10 +8553,14 @@
       <c r="N231" s="29"/>
     </row>
     <row r="232" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="142"/>
-      <c r="B232" s="110"/>
-      <c r="C232" s="26"/>
-      <c r="D232" s="5"/>
+      <c r="A232" s="127"/>
+      <c r="B232" s="148"/>
+      <c r="C232" s="26">
+        <v>198</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>237</v>
+      </c>
       <c r="E232" s="34"/>
       <c r="F232" s="34"/>
       <c r="G232" s="59"/>
@@ -6513,12 +8573,14 @@
       <c r="N232" s="29"/>
     </row>
     <row r="233" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="138">
-        <v>24</v>
-      </c>
-      <c r="B233" s="119"/>
-      <c r="C233" s="26"/>
-      <c r="D233" s="5"/>
+      <c r="A233" s="127"/>
+      <c r="B233" s="148"/>
+      <c r="C233" s="26">
+        <v>200</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>238</v>
+      </c>
       <c r="E233" s="34"/>
       <c r="F233" s="34"/>
       <c r="G233" s="53"/>
@@ -6531,10 +8593,14 @@
       <c r="N233" s="29"/>
     </row>
     <row r="234" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="139"/>
-      <c r="B234" s="119"/>
-      <c r="C234" s="26"/>
-      <c r="D234" s="5"/>
+      <c r="A234" s="127"/>
+      <c r="B234" s="148"/>
+      <c r="C234" s="26">
+        <v>201</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>239</v>
+      </c>
       <c r="E234" s="34"/>
       <c r="F234" s="34"/>
       <c r="G234" s="59"/>
@@ -6547,10 +8613,14 @@
       <c r="N234" s="29"/>
     </row>
     <row r="235" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="139"/>
-      <c r="B235" s="119"/>
-      <c r="C235" s="26"/>
-      <c r="D235" s="5"/>
+      <c r="A235" s="127"/>
+      <c r="B235" s="148"/>
+      <c r="C235" s="26">
+        <v>202</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>240</v>
+      </c>
       <c r="E235" s="34"/>
       <c r="F235" s="34"/>
       <c r="G235" s="59"/>
@@ -6563,10 +8633,14 @@
       <c r="N235" s="29"/>
     </row>
     <row r="236" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="139"/>
-      <c r="B236" s="119"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="5"/>
+      <c r="A236" s="127"/>
+      <c r="B236" s="148"/>
+      <c r="C236" s="26">
+        <v>203</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>241</v>
+      </c>
       <c r="E236" s="58"/>
       <c r="F236" s="58"/>
       <c r="G236" s="59"/>
@@ -6579,10 +8653,14 @@
       <c r="N236" s="29"/>
     </row>
     <row r="237" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="140"/>
-      <c r="B237" s="119"/>
-      <c r="C237" s="26"/>
-      <c r="D237" s="5"/>
+      <c r="A237" s="127"/>
+      <c r="B237" s="148"/>
+      <c r="C237" s="26">
+        <v>204</v>
+      </c>
+      <c r="D237" s="16" t="s">
+        <v>242</v>
+      </c>
       <c r="E237" s="58"/>
       <c r="F237" s="58"/>
       <c r="G237" s="59"/>
@@ -6595,12 +8673,14 @@
       <c r="N237" s="29"/>
     </row>
     <row r="238" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="138">
-        <v>25</v>
-      </c>
-      <c r="B238" s="107"/>
-      <c r="C238" s="26"/>
-      <c r="D238" s="5"/>
+      <c r="A238" s="127"/>
+      <c r="B238" s="148"/>
+      <c r="C238" s="26">
+        <v>205</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>243</v>
+      </c>
       <c r="E238" s="37"/>
       <c r="F238" s="34"/>
       <c r="G238" s="35"/>
@@ -6613,10 +8693,14 @@
       <c r="N238" s="29"/>
     </row>
     <row r="239" spans="1:14" ht="113.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="140"/>
-      <c r="B239" s="108"/>
-      <c r="C239" s="26"/>
-      <c r="D239" s="5"/>
+      <c r="A239" s="127"/>
+      <c r="B239" s="149"/>
+      <c r="C239" s="26">
+        <v>206</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="E239" s="34"/>
       <c r="F239" s="34"/>
       <c r="G239" s="59"/>
@@ -6629,12 +8713,18 @@
       <c r="N239" s="29"/>
     </row>
     <row r="240" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="138">
-        <v>26</v>
-      </c>
-      <c r="B240" s="106"/>
-      <c r="C240" s="26"/>
-      <c r="D240" s="5"/>
+      <c r="A240" s="128">
+        <v>21</v>
+      </c>
+      <c r="B240" s="150" t="s">
+        <v>245</v>
+      </c>
+      <c r="C240" s="26">
+        <v>207</v>
+      </c>
+      <c r="D240" s="17" t="s">
+        <v>246</v>
+      </c>
       <c r="E240" s="58"/>
       <c r="F240" s="58"/>
       <c r="G240" s="59"/>
@@ -6647,10 +8737,14 @@
       <c r="N240" s="29"/>
     </row>
     <row r="241" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="139"/>
-      <c r="B241" s="107"/>
-      <c r="C241" s="26"/>
-      <c r="D241" s="5"/>
+      <c r="A241" s="128"/>
+      <c r="B241" s="151"/>
+      <c r="C241" s="26">
+        <v>208</v>
+      </c>
+      <c r="D241" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="E241" s="34"/>
       <c r="F241" s="34"/>
       <c r="G241" s="59"/>
@@ -6663,10 +8757,14 @@
       <c r="N241" s="29"/>
     </row>
     <row r="242" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="140"/>
-      <c r="B242" s="107"/>
-      <c r="C242" s="26"/>
-      <c r="D242" s="5"/>
+      <c r="A242" s="128"/>
+      <c r="B242" s="151"/>
+      <c r="C242" s="26">
+        <v>209</v>
+      </c>
+      <c r="D242" s="17" t="s">
+        <v>248</v>
+      </c>
       <c r="E242" s="34"/>
       <c r="F242" s="34"/>
       <c r="G242" s="59"/>
@@ -6679,12 +8777,14 @@
       <c r="N242" s="29"/>
     </row>
     <row r="243" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="144">
-        <v>27</v>
-      </c>
-      <c r="B243" s="112"/>
-      <c r="C243" s="72"/>
-      <c r="D243" s="5"/>
+      <c r="A243" s="128"/>
+      <c r="B243" s="151"/>
+      <c r="C243" s="26">
+        <v>210</v>
+      </c>
+      <c r="D243" s="17" t="s">
+        <v>249</v>
+      </c>
       <c r="E243" s="34"/>
       <c r="F243" s="34"/>
       <c r="G243" s="59"/>
@@ -6697,10 +8797,14 @@
       <c r="N243" s="29"/>
     </row>
     <row r="244" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="145"/>
-      <c r="B244" s="113"/>
-      <c r="C244" s="72"/>
-      <c r="D244" s="5"/>
+      <c r="A244" s="128"/>
+      <c r="B244" s="152"/>
+      <c r="C244" s="26">
+        <v>211</v>
+      </c>
+      <c r="D244" s="17" t="s">
+        <v>250</v>
+      </c>
       <c r="E244" s="34"/>
       <c r="F244" s="34"/>
       <c r="G244" s="59"/>
@@ -6713,12 +8817,18 @@
       <c r="N244" s="29"/>
     </row>
     <row r="245" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="138">
-        <v>28</v>
-      </c>
-      <c r="B245" s="107"/>
-      <c r="C245" s="26"/>
-      <c r="D245" s="5"/>
+      <c r="A245" s="129">
+        <v>22</v>
+      </c>
+      <c r="B245" s="153" t="s">
+        <v>251</v>
+      </c>
+      <c r="C245" s="26">
+        <v>212</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>252</v>
+      </c>
       <c r="E245" s="34"/>
       <c r="F245" s="34"/>
       <c r="G245" s="59"/>
@@ -6731,10 +8841,14 @@
       <c r="N245" s="29"/>
     </row>
     <row r="246" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="139"/>
-      <c r="B246" s="107"/>
-      <c r="C246" s="26"/>
-      <c r="D246" s="5"/>
+      <c r="A246" s="129"/>
+      <c r="B246" s="154"/>
+      <c r="C246" s="26">
+        <v>213</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>253</v>
+      </c>
       <c r="E246" s="34"/>
       <c r="F246" s="34"/>
       <c r="G246" s="59"/>
@@ -6747,10 +8861,14 @@
       <c r="N246" s="29"/>
     </row>
     <row r="247" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="140"/>
-      <c r="B247" s="108"/>
-      <c r="C247" s="26"/>
-      <c r="D247" s="5"/>
+      <c r="A247" s="129"/>
+      <c r="B247" s="154"/>
+      <c r="C247" s="26">
+        <v>214</v>
+      </c>
+      <c r="D247" s="16" t="s">
+        <v>254</v>
+      </c>
       <c r="E247" s="34"/>
       <c r="F247" s="34"/>
       <c r="G247" s="59"/>
@@ -6763,12 +8881,14 @@
       <c r="N247" s="29"/>
     </row>
     <row r="248" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="138">
-        <v>29</v>
-      </c>
-      <c r="B248" s="106"/>
-      <c r="C248" s="26"/>
-      <c r="D248" s="5"/>
+      <c r="A248" s="129"/>
+      <c r="B248" s="154"/>
+      <c r="C248" s="26">
+        <v>215</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="E248" s="10"/>
       <c r="F248" s="10"/>
       <c r="G248" s="53"/>
@@ -6781,10 +8901,14 @@
       <c r="N248" s="29"/>
     </row>
     <row r="249" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="139"/>
-      <c r="B249" s="107"/>
-      <c r="C249" s="26"/>
-      <c r="D249" s="5"/>
+      <c r="A249" s="129"/>
+      <c r="B249" s="154"/>
+      <c r="C249" s="26">
+        <v>216</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
       <c r="G249" s="53"/>
@@ -6797,10 +8921,14 @@
       <c r="N249" s="29"/>
     </row>
     <row r="250" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="139"/>
-      <c r="B250" s="107"/>
-      <c r="C250" s="26"/>
-      <c r="D250" s="5"/>
+      <c r="A250" s="129"/>
+      <c r="B250" s="154"/>
+      <c r="C250" s="26">
+        <v>217</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>257</v>
+      </c>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
       <c r="G250" s="53"/>
@@ -6813,10 +8941,14 @@
       <c r="N250" s="29"/>
     </row>
     <row r="251" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="139"/>
-      <c r="B251" s="107"/>
-      <c r="C251" s="26"/>
-      <c r="D251" s="5"/>
+      <c r="A251" s="129"/>
+      <c r="B251" s="154"/>
+      <c r="C251" s="26">
+        <v>218</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>258</v>
+      </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
       <c r="G251" s="53"/>
@@ -6829,10 +8961,14 @@
       <c r="N251" s="29"/>
     </row>
     <row r="252" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="140"/>
-      <c r="B252" s="108"/>
-      <c r="C252" s="26"/>
-      <c r="D252" s="5"/>
+      <c r="A252" s="129"/>
+      <c r="B252" s="155"/>
+      <c r="C252" s="26">
+        <v>219</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>259</v>
+      </c>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
       <c r="G252" s="53"/>
@@ -6845,12 +8981,18 @@
       <c r="N252" s="29"/>
     </row>
     <row r="253" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="138">
-        <v>30</v>
-      </c>
-      <c r="B253" s="106"/>
-      <c r="C253" s="26"/>
-      <c r="D253" s="5"/>
+      <c r="A253" s="128">
+        <v>23</v>
+      </c>
+      <c r="B253" s="150" t="s">
+        <v>260</v>
+      </c>
+      <c r="C253" s="26">
+        <v>220</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>261</v>
+      </c>
       <c r="E253" s="36"/>
       <c r="F253" s="34"/>
       <c r="G253" s="59"/>
@@ -6863,10 +9005,14 @@
       <c r="N253" s="29"/>
     </row>
     <row r="254" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="139"/>
-      <c r="B254" s="107"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="5"/>
+      <c r="A254" s="128"/>
+      <c r="B254" s="151"/>
+      <c r="C254" s="26">
+        <v>221</v>
+      </c>
+      <c r="D254" s="16" t="s">
+        <v>262</v>
+      </c>
       <c r="E254" s="36"/>
       <c r="F254" s="34"/>
       <c r="G254" s="59"/>
@@ -6879,10 +9025,14 @@
       <c r="N254" s="29"/>
     </row>
     <row r="255" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="139"/>
-      <c r="B255" s="107"/>
-      <c r="C255" s="26"/>
-      <c r="D255" s="5"/>
+      <c r="A255" s="128"/>
+      <c r="B255" s="151"/>
+      <c r="C255" s="26">
+        <v>222</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>263</v>
+      </c>
       <c r="E255" s="36"/>
       <c r="F255" s="34"/>
       <c r="G255" s="59"/>
@@ -6895,10 +9045,14 @@
       <c r="N255" s="29"/>
     </row>
     <row r="256" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="140"/>
-      <c r="B256" s="108"/>
-      <c r="C256" s="26"/>
-      <c r="D256" s="5"/>
+      <c r="A256" s="128"/>
+      <c r="B256" s="151"/>
+      <c r="C256" s="26">
+        <v>223</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>264</v>
+      </c>
       <c r="E256" s="36"/>
       <c r="F256" s="34"/>
       <c r="G256" s="59"/>
@@ -6911,12 +9065,14 @@
       <c r="N256" s="29"/>
     </row>
     <row r="257" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="138">
-        <v>31</v>
-      </c>
-      <c r="B257" s="106"/>
-      <c r="C257" s="26"/>
-      <c r="D257" s="5"/>
+      <c r="A257" s="128"/>
+      <c r="B257" s="151"/>
+      <c r="C257" s="26">
+        <v>224</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="E257" s="36"/>
       <c r="F257" s="34"/>
       <c r="G257" s="35"/>
@@ -6929,10 +9085,14 @@
       <c r="N257" s="29"/>
     </row>
     <row r="258" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="139"/>
-      <c r="B258" s="107"/>
-      <c r="C258" s="26"/>
-      <c r="D258" s="5"/>
+      <c r="A258" s="128"/>
+      <c r="B258" s="151"/>
+      <c r="C258" s="26">
+        <v>225</v>
+      </c>
+      <c r="D258" s="5" t="s">
+        <v>266</v>
+      </c>
       <c r="E258" s="36"/>
       <c r="F258" s="34"/>
       <c r="G258" s="35"/>
@@ -6945,10 +9105,14 @@
       <c r="N258" s="29"/>
     </row>
     <row r="259" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="139"/>
-      <c r="B259" s="107"/>
-      <c r="C259" s="26"/>
-      <c r="D259" s="5"/>
+      <c r="A259" s="128"/>
+      <c r="B259" s="151"/>
+      <c r="C259" s="26">
+        <v>226</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="E259" s="36"/>
       <c r="F259" s="34"/>
       <c r="G259" s="59"/>
@@ -6961,10 +9125,14 @@
       <c r="N259" s="29"/>
     </row>
     <row r="260" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="139"/>
-      <c r="B260" s="107"/>
-      <c r="C260" s="26"/>
-      <c r="D260" s="5"/>
+      <c r="A260" s="128"/>
+      <c r="B260" s="151"/>
+      <c r="C260" s="26">
+        <v>227</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="E260" s="36"/>
       <c r="F260" s="34"/>
       <c r="G260" s="59"/>
@@ -6977,10 +9145,14 @@
       <c r="N260" s="29"/>
     </row>
     <row r="261" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="140"/>
-      <c r="B261" s="108"/>
-      <c r="C261" s="26"/>
-      <c r="D261" s="5"/>
+      <c r="A261" s="128"/>
+      <c r="B261" s="151"/>
+      <c r="C261" s="26">
+        <v>228</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="E261" s="36"/>
       <c r="F261" s="34"/>
       <c r="G261" s="35"/>
@@ -6992,13 +9164,15 @@
       <c r="M261" s="29"/>
       <c r="N261" s="29"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A262" s="138">
-        <v>32</v>
-      </c>
-      <c r="B262" s="106"/>
-      <c r="C262" s="26"/>
-      <c r="D262" s="5"/>
+    <row r="262" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A262" s="128"/>
+      <c r="B262" s="151"/>
+      <c r="C262" s="26">
+        <v>229</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>270</v>
+      </c>
       <c r="E262" s="36"/>
       <c r="F262" s="34"/>
       <c r="G262" s="59"/>
@@ -7010,11 +9184,15 @@
       <c r="M262" s="29"/>
       <c r="N262" s="29"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A263" s="139"/>
-      <c r="B263" s="107"/>
-      <c r="C263" s="26"/>
-      <c r="D263" s="5"/>
+    <row r="263" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A263" s="128"/>
+      <c r="B263" s="151"/>
+      <c r="C263" s="26">
+        <v>230</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>271</v>
+      </c>
       <c r="E263" s="58"/>
       <c r="F263" s="58"/>
       <c r="G263" s="59"/>
@@ -7026,11 +9204,19 @@
       <c r="M263" s="29"/>
       <c r="N263" s="29"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A264" s="139"/>
-      <c r="B264" s="107"/>
-      <c r="C264" s="26"/>
-      <c r="D264" s="5"/>
+    <row r="264" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A264" s="124">
+        <v>24</v>
+      </c>
+      <c r="B264" s="156" t="s">
+        <v>272</v>
+      </c>
+      <c r="C264" s="26">
+        <v>231</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>273</v>
+      </c>
       <c r="E264" s="58"/>
       <c r="F264" s="58"/>
       <c r="G264" s="59"/>
@@ -7043,10 +9229,14 @@
       <c r="N264" s="29"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A265" s="140"/>
-      <c r="B265" s="108"/>
-      <c r="C265" s="26"/>
-      <c r="D265" s="5"/>
+      <c r="A265" s="130"/>
+      <c r="B265" s="156"/>
+      <c r="C265" s="26">
+        <v>232</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>274</v>
+      </c>
       <c r="E265" s="58"/>
       <c r="F265" s="58"/>
       <c r="G265" s="59"/>
@@ -7059,12 +9249,14 @@
       <c r="N265" s="29"/>
     </row>
     <row r="266" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="138">
-        <v>33</v>
-      </c>
-      <c r="B266" s="106"/>
-      <c r="C266" s="26"/>
-      <c r="D266" s="5"/>
+      <c r="A266" s="130"/>
+      <c r="B266" s="156"/>
+      <c r="C266" s="26">
+        <v>233</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="E266" s="34"/>
       <c r="F266" s="34"/>
       <c r="G266" s="59"/>
@@ -7076,11 +9268,15 @@
       <c r="M266" s="29"/>
       <c r="N266" s="29"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A267" s="139"/>
-      <c r="B267" s="107"/>
-      <c r="C267" s="26"/>
-      <c r="D267" s="5"/>
+    <row r="267" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A267" s="130"/>
+      <c r="B267" s="156"/>
+      <c r="C267" s="26">
+        <v>234</v>
+      </c>
+      <c r="D267" s="5" t="s">
+        <v>276</v>
+      </c>
       <c r="E267" s="34"/>
       <c r="F267" s="34"/>
       <c r="G267" s="59"/>
@@ -7093,10 +9289,14 @@
       <c r="N267" s="29"/>
     </row>
     <row r="268" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="139"/>
-      <c r="B268" s="107"/>
-      <c r="C268" s="26"/>
-      <c r="D268" s="5"/>
+      <c r="A268" s="125"/>
+      <c r="B268" s="156"/>
+      <c r="C268" s="26">
+        <v>235</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="E268" s="34"/>
       <c r="F268" s="34"/>
       <c r="G268" s="59"/>
@@ -7108,11 +9308,19 @@
       <c r="M268" s="29"/>
       <c r="N268" s="29"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A269" s="139"/>
-      <c r="B269" s="107"/>
-      <c r="C269" s="26"/>
-      <c r="D269" s="5"/>
+    <row r="269" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A269" s="124">
+        <v>25</v>
+      </c>
+      <c r="B269" s="154" t="s">
+        <v>278</v>
+      </c>
+      <c r="C269" s="26">
+        <v>236</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="E269" s="34"/>
       <c r="F269" s="34"/>
       <c r="G269" s="59"/>
@@ -7125,10 +9333,14 @@
       <c r="N269" s="29"/>
     </row>
     <row r="270" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="139"/>
-      <c r="B270" s="107"/>
-      <c r="C270" s="26"/>
-      <c r="D270" s="5"/>
+      <c r="A270" s="125"/>
+      <c r="B270" s="155"/>
+      <c r="C270" s="26">
+        <v>237</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>280</v>
+      </c>
       <c r="E270" s="58"/>
       <c r="F270" s="58"/>
       <c r="G270" s="59"/>
@@ -7141,10 +9353,18 @@
       <c r="N270" s="29"/>
     </row>
     <row r="271" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="139"/>
-      <c r="B271" s="107"/>
-      <c r="C271" s="26"/>
-      <c r="D271" s="5"/>
+      <c r="A271" s="124">
+        <v>26</v>
+      </c>
+      <c r="B271" s="153" t="s">
+        <v>281</v>
+      </c>
+      <c r="C271" s="26">
+        <v>238</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="E271" s="58"/>
       <c r="F271" s="58"/>
       <c r="G271" s="59"/>
@@ -7156,11 +9376,15 @@
       <c r="M271" s="29"/>
       <c r="N271" s="29"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A272" s="139"/>
-      <c r="B272" s="107"/>
-      <c r="C272" s="26"/>
-      <c r="D272" s="5"/>
+    <row r="272" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A272" s="130"/>
+      <c r="B272" s="154"/>
+      <c r="C272" s="26">
+        <v>239</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="E272" s="58"/>
       <c r="F272" s="58"/>
       <c r="G272" s="59"/>
@@ -7173,10 +9397,14 @@
       <c r="N272" s="29"/>
     </row>
     <row r="273" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="139"/>
-      <c r="B273" s="107"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="5"/>
+      <c r="A273" s="125"/>
+      <c r="B273" s="154"/>
+      <c r="C273" s="26">
+        <v>240</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>284</v>
+      </c>
       <c r="E273" s="58"/>
       <c r="F273" s="58"/>
       <c r="G273" s="54"/>
@@ -7189,10 +9417,18 @@
       <c r="N273" s="29"/>
     </row>
     <row r="274" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="140"/>
-      <c r="B274" s="108"/>
-      <c r="C274" s="26"/>
-      <c r="D274" s="5"/>
+      <c r="A274" s="134">
+        <v>27</v>
+      </c>
+      <c r="B274" s="157" t="s">
+        <v>285</v>
+      </c>
+      <c r="C274" s="72">
+        <v>241</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>286</v>
+      </c>
       <c r="E274" s="58"/>
       <c r="F274" s="58"/>
       <c r="G274" s="54"/>
@@ -7205,12 +9441,14 @@
       <c r="N274" s="29"/>
     </row>
     <row r="275" spans="1:14" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A275" s="138">
-        <v>34</v>
-      </c>
-      <c r="B275" s="106"/>
-      <c r="C275" s="26"/>
-      <c r="D275" s="5"/>
+      <c r="A275" s="135"/>
+      <c r="B275" s="158"/>
+      <c r="C275" s="72">
+        <v>242</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="E275" s="58"/>
       <c r="F275" s="58"/>
       <c r="G275" s="59"/>
@@ -7223,10 +9461,18 @@
       <c r="N275" s="29"/>
     </row>
     <row r="276" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="139"/>
-      <c r="B276" s="107"/>
-      <c r="C276" s="26"/>
-      <c r="D276" s="5"/>
+      <c r="A276" s="124">
+        <v>28</v>
+      </c>
+      <c r="B276" s="154" t="s">
+        <v>288</v>
+      </c>
+      <c r="C276" s="26">
+        <v>243</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>289</v>
+      </c>
       <c r="E276" s="58"/>
       <c r="F276" s="58"/>
       <c r="G276" s="59"/>
@@ -7239,10 +9485,14 @@
       <c r="N276" s="29"/>
     </row>
     <row r="277" spans="1:14" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="139"/>
-      <c r="B277" s="107"/>
-      <c r="C277" s="26"/>
-      <c r="D277" s="5"/>
+      <c r="A277" s="130"/>
+      <c r="B277" s="154"/>
+      <c r="C277" s="26">
+        <v>244</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="E277" s="58"/>
       <c r="F277" s="58"/>
       <c r="G277" s="59"/>
@@ -7255,10 +9505,14 @@
       <c r="N277" s="29"/>
     </row>
     <row r="278" spans="1:14" s="2" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="139"/>
-      <c r="B278" s="107"/>
-      <c r="C278" s="26"/>
-      <c r="D278" s="17"/>
+      <c r="A278" s="125"/>
+      <c r="B278" s="155"/>
+      <c r="C278" s="26">
+        <v>245</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="E278" s="61"/>
       <c r="F278" s="61"/>
       <c r="G278" s="54"/>
@@ -7271,10 +9525,18 @@
       <c r="N278" s="62"/>
     </row>
     <row r="279" spans="1:14" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="139"/>
-      <c r="B279" s="107"/>
-      <c r="C279" s="26"/>
-      <c r="D279" s="7"/>
+      <c r="A279" s="124">
+        <v>29</v>
+      </c>
+      <c r="B279" s="153" t="s">
+        <v>292</v>
+      </c>
+      <c r="C279" s="26">
+        <v>246</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>293</v>
+      </c>
       <c r="E279" s="63"/>
       <c r="F279" s="63"/>
       <c r="G279" s="55"/>
@@ -7286,11 +9548,15 @@
       <c r="M279" s="29"/>
       <c r="N279" s="29"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A280" s="139"/>
-      <c r="B280" s="107"/>
-      <c r="C280" s="26"/>
-      <c r="D280" s="16"/>
+    <row r="280" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A280" s="130"/>
+      <c r="B280" s="154"/>
+      <c r="C280" s="26">
+        <v>247</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>294</v>
+      </c>
       <c r="E280" s="64"/>
       <c r="F280" s="64"/>
       <c r="G280" s="51"/>
@@ -7302,11 +9568,15 @@
       <c r="M280" s="29"/>
       <c r="N280" s="29"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A281" s="139"/>
-      <c r="B281" s="107"/>
-      <c r="C281" s="26"/>
-      <c r="D281" s="8"/>
+    <row r="281" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A281" s="130"/>
+      <c r="B281" s="154"/>
+      <c r="C281" s="26">
+        <v>248</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="E281" s="65"/>
       <c r="F281" s="65"/>
       <c r="G281" s="66"/>
@@ -7318,11 +9588,15 @@
       <c r="M281" s="29"/>
       <c r="N281" s="29"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A282" s="140"/>
-      <c r="B282" s="108"/>
-      <c r="C282" s="26"/>
-      <c r="D282" s="16"/>
+    <row r="282" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A282" s="130"/>
+      <c r="B282" s="154"/>
+      <c r="C282" s="26">
+        <v>249</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="E282" s="64"/>
       <c r="F282" s="64"/>
       <c r="G282" s="51"/>
@@ -7335,12 +9609,14 @@
       <c r="N282" s="29"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A283" s="138">
-        <v>35</v>
-      </c>
-      <c r="B283" s="106"/>
-      <c r="C283" s="26"/>
-      <c r="D283" s="6"/>
+      <c r="A283" s="125"/>
+      <c r="B283" s="155"/>
+      <c r="C283" s="26">
+        <v>250</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="E283" s="56"/>
       <c r="F283" s="56"/>
       <c r="G283" s="57"/>
@@ -7352,11 +9628,19 @@
       <c r="M283" s="29"/>
       <c r="N283" s="29"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A284" s="139"/>
-      <c r="B284" s="107"/>
-      <c r="C284" s="26"/>
-      <c r="D284" s="5"/>
+    <row r="284" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A284" s="124">
+        <v>30</v>
+      </c>
+      <c r="B284" s="153" t="s">
+        <v>298</v>
+      </c>
+      <c r="C284" s="26">
+        <v>251</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>299</v>
+      </c>
       <c r="E284" s="58"/>
       <c r="F284" s="58"/>
       <c r="G284" s="59"/>
@@ -7369,10 +9653,14 @@
       <c r="N284" s="29"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A285" s="139"/>
-      <c r="B285" s="107"/>
-      <c r="C285" s="26"/>
-      <c r="D285" s="5"/>
+      <c r="A285" s="130"/>
+      <c r="B285" s="154"/>
+      <c r="C285" s="26">
+        <v>252</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="E285" s="58"/>
       <c r="F285" s="58"/>
       <c r="G285" s="59"/>
@@ -7384,11 +9672,15 @@
       <c r="M285" s="29"/>
       <c r="N285" s="29"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A286" s="139"/>
-      <c r="B286" s="107"/>
-      <c r="C286" s="26"/>
-      <c r="D286" s="5"/>
+    <row r="286" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A286" s="130"/>
+      <c r="B286" s="154"/>
+      <c r="C286" s="26">
+        <v>253</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="E286" s="58"/>
       <c r="F286" s="58"/>
       <c r="G286" s="59"/>
@@ -7401,10 +9693,14 @@
       <c r="N286" s="29"/>
     </row>
     <row r="287" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="139"/>
-      <c r="B287" s="107"/>
-      <c r="C287" s="26"/>
-      <c r="D287" s="5"/>
+      <c r="A287" s="125"/>
+      <c r="B287" s="155"/>
+      <c r="C287" s="26">
+        <v>254</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="E287" s="58"/>
       <c r="F287" s="58"/>
       <c r="G287" s="59"/>
@@ -7416,11 +9712,19 @@
       <c r="M287" s="29"/>
       <c r="N287" s="29"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A288" s="139"/>
-      <c r="B288" s="107"/>
-      <c r="C288" s="26"/>
-      <c r="D288" s="5"/>
+    <row r="288" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A288" s="124">
+        <v>31</v>
+      </c>
+      <c r="B288" s="153" t="s">
+        <v>303</v>
+      </c>
+      <c r="C288" s="26">
+        <v>256</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="E288" s="58"/>
       <c r="F288" s="58"/>
       <c r="G288" s="59"/>
@@ -7432,11 +9736,15 @@
       <c r="M288" s="29"/>
       <c r="N288" s="29"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A289" s="140"/>
-      <c r="B289" s="108"/>
-      <c r="C289" s="26"/>
-      <c r="D289" s="5"/>
+    <row r="289" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A289" s="130"/>
+      <c r="B289" s="154"/>
+      <c r="C289" s="26">
+        <v>257</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>305</v>
+      </c>
       <c r="E289" s="58"/>
       <c r="F289" s="58"/>
       <c r="G289" s="59"/>
@@ -7449,12 +9757,14 @@
       <c r="N289" s="29"/>
     </row>
     <row r="290" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A290" s="138">
-        <v>36</v>
-      </c>
-      <c r="B290" s="106"/>
-      <c r="C290" s="26"/>
-      <c r="D290" s="5"/>
+      <c r="A290" s="130"/>
+      <c r="B290" s="154"/>
+      <c r="C290" s="26">
+        <v>258</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>306</v>
+      </c>
       <c r="E290" s="60"/>
       <c r="F290" s="58"/>
       <c r="G290" s="59"/>
@@ -7467,10 +9777,14 @@
       <c r="N290" s="29"/>
     </row>
     <row r="291" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A291" s="139"/>
-      <c r="B291" s="107"/>
-      <c r="C291" s="26"/>
-      <c r="D291" s="5"/>
+      <c r="A291" s="130"/>
+      <c r="B291" s="154"/>
+      <c r="C291" s="26">
+        <v>259</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>307</v>
+      </c>
       <c r="E291" s="61"/>
       <c r="G291" s="59"/>
       <c r="H291" s="29"/>
@@ -7482,10 +9796,14 @@
       <c r="N291" s="29"/>
     </row>
     <row r="292" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A292" s="139"/>
-      <c r="B292" s="107"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="5"/>
+      <c r="A292" s="125"/>
+      <c r="B292" s="155"/>
+      <c r="C292" s="26">
+        <v>260</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>308</v>
+      </c>
       <c r="E292" s="60"/>
       <c r="F292" s="58"/>
       <c r="G292" s="59"/>
@@ -7497,11 +9815,19 @@
       <c r="M292" s="29"/>
       <c r="N292" s="29"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A293" s="139"/>
-      <c r="B293" s="107"/>
-      <c r="C293" s="26"/>
-      <c r="D293" s="5"/>
+    <row r="293" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A293" s="124">
+        <v>32</v>
+      </c>
+      <c r="B293" s="153" t="s">
+        <v>309</v>
+      </c>
+      <c r="C293" s="26">
+        <v>261</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="E293" s="58"/>
       <c r="F293" s="58"/>
       <c r="G293" s="59"/>
@@ -7513,11 +9839,15 @@
       <c r="M293" s="29"/>
       <c r="N293" s="29"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A294" s="139"/>
-      <c r="B294" s="107"/>
-      <c r="C294" s="26"/>
-      <c r="D294" s="5"/>
+    <row r="294" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A294" s="130"/>
+      <c r="B294" s="154"/>
+      <c r="C294" s="26">
+        <v>262</v>
+      </c>
+      <c r="D294" s="5" t="s">
+        <v>311</v>
+      </c>
       <c r="E294" s="58"/>
       <c r="F294" s="58"/>
       <c r="G294" s="59"/>
@@ -7530,10 +9860,14 @@
       <c r="N294" s="29"/>
     </row>
     <row r="295" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A295" s="139"/>
-      <c r="B295" s="107"/>
-      <c r="C295" s="26"/>
-      <c r="D295" s="5"/>
+      <c r="A295" s="130"/>
+      <c r="B295" s="154"/>
+      <c r="C295" s="26">
+        <v>263</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>312</v>
+      </c>
       <c r="E295" s="60"/>
       <c r="F295" s="58"/>
       <c r="G295" s="59"/>
@@ -7545,11 +9879,15 @@
       <c r="M295" s="29"/>
       <c r="N295" s="29"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A296" s="139"/>
-      <c r="B296" s="107"/>
-      <c r="C296" s="26"/>
-      <c r="D296" s="21"/>
+    <row r="296" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A296" s="125"/>
+      <c r="B296" s="155"/>
+      <c r="C296" s="26">
+        <v>264</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>313</v>
+      </c>
       <c r="E296" s="58"/>
       <c r="F296" s="58"/>
       <c r="G296" s="59"/>
@@ -7562,10 +9900,18 @@
       <c r="N296" s="29"/>
     </row>
     <row r="297" spans="1:14" ht="47.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A297" s="140"/>
-      <c r="B297" s="108"/>
-      <c r="C297" s="26"/>
-      <c r="D297" s="5"/>
+      <c r="A297" s="124">
+        <v>33</v>
+      </c>
+      <c r="B297" s="153" t="s">
+        <v>314</v>
+      </c>
+      <c r="C297" s="26">
+        <v>265</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>315</v>
+      </c>
       <c r="E297" s="58"/>
       <c r="F297" s="58"/>
       <c r="G297" s="59"/>
@@ -7577,13 +9923,15 @@
       <c r="M297" s="29"/>
       <c r="N297" s="29"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A298" s="138">
-        <v>37</v>
-      </c>
-      <c r="B298" s="106"/>
-      <c r="C298" s="26"/>
-      <c r="D298" s="5"/>
+    <row r="298" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A298" s="130"/>
+      <c r="B298" s="154"/>
+      <c r="C298" s="26">
+        <v>266</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="E298" s="58"/>
       <c r="F298" s="58"/>
       <c r="G298" s="59"/>
@@ -7596,10 +9944,14 @@
       <c r="N298" s="29"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A299" s="139"/>
-      <c r="B299" s="107"/>
-      <c r="C299" s="26"/>
-      <c r="D299" s="5"/>
+      <c r="A299" s="130"/>
+      <c r="B299" s="154"/>
+      <c r="C299" s="26">
+        <v>267</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>317</v>
+      </c>
       <c r="E299" s="58"/>
       <c r="F299" s="58"/>
       <c r="G299" s="59"/>
@@ -7611,11 +9963,15 @@
       <c r="M299" s="29"/>
       <c r="N299" s="29"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A300" s="139"/>
-      <c r="B300" s="107"/>
-      <c r="C300" s="26"/>
-      <c r="D300" s="5"/>
+    <row r="300" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A300" s="130"/>
+      <c r="B300" s="154"/>
+      <c r="C300" s="26">
+        <v>268</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>318</v>
+      </c>
       <c r="E300" s="58"/>
       <c r="F300" s="58"/>
       <c r="G300" s="59"/>
@@ -7628,10 +9984,14 @@
       <c r="N300" s="29"/>
     </row>
     <row r="301" spans="1:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A301" s="139"/>
-      <c r="B301" s="107"/>
-      <c r="C301" s="26"/>
-      <c r="D301" s="5"/>
+      <c r="A301" s="130"/>
+      <c r="B301" s="154"/>
+      <c r="C301" s="26">
+        <v>269</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="E301" s="58"/>
       <c r="F301" s="58"/>
       <c r="G301" s="59"/>
@@ -7644,10 +10004,14 @@
       <c r="N301" s="29"/>
     </row>
     <row r="302" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A302" s="139"/>
-      <c r="B302" s="107"/>
-      <c r="C302" s="26"/>
-      <c r="D302" s="5"/>
+      <c r="A302" s="130"/>
+      <c r="B302" s="154"/>
+      <c r="C302" s="26">
+        <v>270</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>320</v>
+      </c>
       <c r="E302" s="60"/>
       <c r="F302" s="58"/>
       <c r="G302" s="59"/>
@@ -7659,11 +10023,15 @@
       <c r="M302" s="29"/>
       <c r="N302" s="29"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A303" s="139"/>
-      <c r="B303" s="107"/>
-      <c r="C303" s="26"/>
-      <c r="D303" s="5"/>
+    <row r="303" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A303" s="130"/>
+      <c r="B303" s="154"/>
+      <c r="C303" s="26">
+        <v>271</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>321</v>
+      </c>
       <c r="E303" s="58"/>
       <c r="F303" s="58"/>
       <c r="G303" s="59"/>
@@ -7676,10 +10044,14 @@
       <c r="N303" s="29"/>
     </row>
     <row r="304" spans="1:14" ht="23.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A304" s="139"/>
-      <c r="B304" s="107"/>
-      <c r="C304" s="26"/>
-      <c r="D304" s="7"/>
+      <c r="A304" s="130"/>
+      <c r="B304" s="154"/>
+      <c r="C304" s="26">
+        <v>272</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>322</v>
+      </c>
       <c r="E304" s="60"/>
       <c r="F304" s="58"/>
       <c r="G304" s="55"/>
@@ -7692,12 +10064,14 @@
       <c r="N304" s="29"/>
     </row>
     <row r="305" spans="1:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A305" s="141">
-        <v>38</v>
-      </c>
-      <c r="B305" s="109"/>
-      <c r="C305" s="26"/>
-      <c r="D305" s="18"/>
+      <c r="A305" s="125"/>
+      <c r="B305" s="155"/>
+      <c r="C305" s="26">
+        <v>273</v>
+      </c>
+      <c r="D305" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="E305" s="58"/>
       <c r="F305" s="67"/>
       <c r="G305" s="68"/>
@@ -7710,10 +10084,18 @@
       <c r="N305" s="29"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A306" s="142"/>
-      <c r="B306" s="110"/>
-      <c r="C306" s="26"/>
-      <c r="D306" s="16"/>
+      <c r="A306" s="124">
+        <v>34</v>
+      </c>
+      <c r="B306" s="153" t="s">
+        <v>324</v>
+      </c>
+      <c r="C306" s="26">
+        <v>274</v>
+      </c>
+      <c r="D306" s="5" t="s">
+        <v>325</v>
+      </c>
       <c r="E306" s="58"/>
       <c r="F306" s="67"/>
       <c r="G306" s="51"/>
@@ -7726,10 +10108,14 @@
       <c r="N306" s="29"/>
     </row>
     <row r="307" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A307" s="142"/>
-      <c r="B307" s="110"/>
-      <c r="C307" s="26"/>
-      <c r="D307" s="6"/>
+      <c r="A307" s="130"/>
+      <c r="B307" s="154"/>
+      <c r="C307" s="26">
+        <v>275</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>326</v>
+      </c>
       <c r="E307" s="58"/>
       <c r="F307" s="67"/>
       <c r="G307" s="57"/>
@@ -7742,10 +10128,14 @@
       <c r="N307" s="29"/>
     </row>
     <row r="308" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A308" s="142"/>
-      <c r="B308" s="110"/>
-      <c r="C308" s="26"/>
-      <c r="D308" s="5"/>
+      <c r="A308" s="130"/>
+      <c r="B308" s="154"/>
+      <c r="C308" s="26">
+        <v>276</v>
+      </c>
+      <c r="D308" s="5" t="s">
+        <v>327</v>
+      </c>
       <c r="E308" s="58"/>
       <c r="F308" s="67"/>
       <c r="G308" s="59"/>
@@ -7757,11 +10147,15 @@
       <c r="M308" s="29"/>
       <c r="N308" s="29"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A309" s="142"/>
-      <c r="B309" s="110"/>
-      <c r="C309" s="26"/>
-      <c r="D309" s="5"/>
+    <row r="309" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A309" s="130"/>
+      <c r="B309" s="154"/>
+      <c r="C309" s="26">
+        <v>277</v>
+      </c>
+      <c r="D309" s="17" t="s">
+        <v>328</v>
+      </c>
       <c r="E309" s="58"/>
       <c r="F309" s="67"/>
       <c r="G309" s="59"/>
@@ -7774,10 +10168,14 @@
       <c r="N309" s="29"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A310" s="142"/>
-      <c r="B310" s="110"/>
-      <c r="C310" s="26"/>
-      <c r="D310" s="5"/>
+      <c r="A310" s="130"/>
+      <c r="B310" s="154"/>
+      <c r="C310" s="26">
+        <v>278</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="E310" s="58"/>
       <c r="F310" s="67"/>
       <c r="G310" s="59"/>
@@ -7789,11 +10187,15 @@
       <c r="M310" s="29"/>
       <c r="N310" s="29"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A311" s="142"/>
-      <c r="B311" s="110"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="5"/>
+    <row r="311" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A311" s="130"/>
+      <c r="B311" s="154"/>
+      <c r="C311" s="26">
+        <v>279</v>
+      </c>
+      <c r="D311" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="E311" s="69"/>
       <c r="F311" s="69"/>
       <c r="G311" s="59"/>
@@ -7806,10 +10208,14 @@
       <c r="N311" s="29"/>
     </row>
     <row r="312" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A312" s="142"/>
-      <c r="B312" s="110"/>
-      <c r="C312" s="26"/>
-      <c r="D312" s="5"/>
+      <c r="A312" s="130"/>
+      <c r="B312" s="154"/>
+      <c r="C312" s="26">
+        <v>280</v>
+      </c>
+      <c r="D312" s="8" t="s">
+        <v>331</v>
+      </c>
       <c r="E312" s="58"/>
       <c r="F312" s="67"/>
       <c r="G312" s="59"/>
@@ -7822,10 +10228,14 @@
       <c r="N312" s="29"/>
     </row>
     <row r="313" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A313" s="142"/>
-      <c r="B313" s="110"/>
-      <c r="C313" s="26"/>
-      <c r="D313" s="5"/>
+      <c r="A313" s="125"/>
+      <c r="B313" s="155"/>
+      <c r="C313" s="26">
+        <v>281</v>
+      </c>
+      <c r="D313" s="16" t="s">
+        <v>332</v>
+      </c>
       <c r="E313" s="58"/>
       <c r="F313" s="67"/>
       <c r="G313" s="59"/>
@@ -7838,10 +10248,18 @@
       <c r="N313" s="29"/>
     </row>
     <row r="314" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A314" s="142"/>
-      <c r="B314" s="110"/>
-      <c r="C314" s="26"/>
-      <c r="D314" s="5"/>
+      <c r="A314" s="124">
+        <v>35</v>
+      </c>
+      <c r="B314" s="153" t="s">
+        <v>333</v>
+      </c>
+      <c r="C314" s="26">
+        <v>282</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="E314" s="58"/>
       <c r="F314" s="67"/>
       <c r="G314" s="59"/>
@@ -7854,10 +10272,14 @@
       <c r="N314" s="29"/>
     </row>
     <row r="315" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A315" s="142"/>
-      <c r="B315" s="110"/>
-      <c r="C315" s="26"/>
-      <c r="D315" s="5"/>
+      <c r="A315" s="130"/>
+      <c r="B315" s="154"/>
+      <c r="C315" s="26">
+        <v>283</v>
+      </c>
+      <c r="D315" s="5" t="s">
+        <v>335</v>
+      </c>
       <c r="E315" s="58"/>
       <c r="F315" s="67"/>
       <c r="G315" s="59"/>
@@ -7870,10 +10292,14 @@
       <c r="N315" s="29"/>
     </row>
     <row r="316" spans="1:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A316" s="142"/>
-      <c r="B316" s="110"/>
-      <c r="C316" s="26"/>
-      <c r="D316" s="5"/>
+      <c r="A316" s="130"/>
+      <c r="B316" s="154"/>
+      <c r="C316" s="26">
+        <v>284</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>336</v>
+      </c>
       <c r="E316" s="58"/>
       <c r="F316" s="67"/>
       <c r="G316" s="59"/>
@@ -7886,10 +10312,14 @@
       <c r="N316" s="29"/>
     </row>
     <row r="317" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A317" s="142"/>
-      <c r="B317" s="110"/>
-      <c r="C317" s="26"/>
-      <c r="D317" s="5"/>
+      <c r="A317" s="130"/>
+      <c r="B317" s="154"/>
+      <c r="C317" s="26">
+        <v>285</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>337</v>
+      </c>
       <c r="E317" s="69"/>
       <c r="F317" s="69"/>
       <c r="G317" s="59"/>
@@ -7902,10 +10332,14 @@
       <c r="N317" s="29"/>
     </row>
     <row r="318" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A318" s="142"/>
-      <c r="B318" s="110"/>
-      <c r="C318" s="26"/>
-      <c r="D318" s="5"/>
+      <c r="A318" s="130"/>
+      <c r="B318" s="154"/>
+      <c r="C318" s="26">
+        <v>286</v>
+      </c>
+      <c r="D318" s="5" t="s">
+        <v>338</v>
+      </c>
       <c r="E318" s="69"/>
       <c r="F318" s="69"/>
       <c r="G318" s="59"/>
@@ -7918,10 +10352,14 @@
       <c r="N318" s="29"/>
     </row>
     <row r="319" spans="1:14" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A319" s="142"/>
-      <c r="B319" s="110"/>
-      <c r="C319" s="26"/>
-      <c r="D319" s="5"/>
+      <c r="A319" s="130"/>
+      <c r="B319" s="154"/>
+      <c r="C319" s="26">
+        <v>287</v>
+      </c>
+      <c r="D319" s="5" t="s">
+        <v>339</v>
+      </c>
       <c r="E319" s="69"/>
       <c r="F319" s="69"/>
       <c r="G319" s="59"/>
@@ -7934,10 +10372,14 @@
       <c r="N319" s="29"/>
     </row>
     <row r="320" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A320" s="142"/>
-      <c r="B320" s="110"/>
-      <c r="C320" s="26"/>
-      <c r="D320" s="5"/>
+      <c r="A320" s="125"/>
+      <c r="B320" s="155"/>
+      <c r="C320" s="26">
+        <v>288</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>340</v>
+      </c>
       <c r="E320" s="69"/>
       <c r="F320" s="69"/>
       <c r="G320" s="59"/>
@@ -7949,11 +10391,19 @@
       <c r="M320" s="29"/>
       <c r="N320" s="29"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A321" s="142"/>
-      <c r="B321" s="110"/>
-      <c r="C321" s="26"/>
-      <c r="D321" s="5"/>
+    <row r="321" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A321" s="124">
+        <v>36</v>
+      </c>
+      <c r="B321" s="153" t="s">
+        <v>341</v>
+      </c>
+      <c r="C321" s="26">
+        <v>289</v>
+      </c>
+      <c r="D321" s="5" t="s">
+        <v>342</v>
+      </c>
       <c r="E321" s="58"/>
       <c r="F321" s="67"/>
       <c r="G321" s="59"/>
@@ -7965,11 +10415,15 @@
       <c r="M321" s="29"/>
       <c r="N321" s="29"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A322" s="142"/>
-      <c r="B322" s="110"/>
-      <c r="C322" s="26"/>
-      <c r="D322" s="5"/>
+    <row r="322" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A322" s="130"/>
+      <c r="B322" s="154"/>
+      <c r="C322" s="26">
+        <v>290</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>343</v>
+      </c>
       <c r="E322" s="58"/>
       <c r="F322" s="67"/>
       <c r="G322" s="59"/>
@@ -7981,11 +10435,15 @@
       <c r="M322" s="29"/>
       <c r="N322" s="29"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A323" s="142"/>
-      <c r="B323" s="110"/>
-      <c r="C323" s="26"/>
-      <c r="D323" s="5"/>
+    <row r="323" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A323" s="130"/>
+      <c r="B323" s="154"/>
+      <c r="C323" s="26">
+        <v>291</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>344</v>
+      </c>
       <c r="E323" s="58"/>
       <c r="F323" s="67"/>
       <c r="G323" s="59"/>
@@ -7997,11 +10455,15 @@
       <c r="M323" s="29"/>
       <c r="N323" s="29"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A324" s="142"/>
-      <c r="B324" s="110"/>
-      <c r="C324" s="26"/>
-      <c r="D324" s="5"/>
+    <row r="324" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A324" s="130"/>
+      <c r="B324" s="154"/>
+      <c r="C324" s="26">
+        <v>292</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="E324" s="58"/>
       <c r="F324" s="67"/>
       <c r="G324" s="59"/>
@@ -8013,11 +10475,15 @@
       <c r="M324" s="29"/>
       <c r="N324" s="29"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A325" s="142"/>
-      <c r="B325" s="110"/>
-      <c r="C325" s="26"/>
-      <c r="D325" s="9"/>
+    <row r="325" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A325" s="130"/>
+      <c r="B325" s="154"/>
+      <c r="C325" s="26">
+        <v>293</v>
+      </c>
+      <c r="D325" s="5" t="s">
+        <v>346</v>
+      </c>
       <c r="E325" s="58"/>
       <c r="F325" s="67"/>
       <c r="G325" s="70"/>
@@ -8030,10 +10496,14 @@
       <c r="N325" s="29"/>
     </row>
     <row r="326" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A326" s="142"/>
-      <c r="B326" s="110"/>
-      <c r="C326" s="26"/>
-      <c r="D326" s="5"/>
+      <c r="A326" s="130"/>
+      <c r="B326" s="154"/>
+      <c r="C326" s="26">
+        <v>294</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>347</v>
+      </c>
       <c r="E326" s="58"/>
       <c r="F326" s="67"/>
       <c r="G326" s="59"/>
@@ -8046,10 +10516,14 @@
       <c r="N326" s="29"/>
     </row>
     <row r="327" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A327" s="142"/>
-      <c r="B327" s="110"/>
-      <c r="C327" s="26"/>
-      <c r="D327" s="9"/>
+      <c r="A327" s="130"/>
+      <c r="B327" s="154"/>
+      <c r="C327" s="26">
+        <v>295</v>
+      </c>
+      <c r="D327" s="21" t="s">
+        <v>348</v>
+      </c>
       <c r="E327" s="58"/>
       <c r="F327" s="67"/>
       <c r="G327" s="70"/>
@@ -8062,10 +10536,14 @@
       <c r="N327" s="29"/>
     </row>
     <row r="328" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A328" s="142"/>
-      <c r="B328" s="110"/>
-      <c r="C328" s="26"/>
-      <c r="D328" s="9"/>
+      <c r="A328" s="125"/>
+      <c r="B328" s="155"/>
+      <c r="C328" s="26">
+        <v>296</v>
+      </c>
+      <c r="D328" s="5" t="s">
+        <v>349</v>
+      </c>
       <c r="E328" s="58"/>
       <c r="F328" s="67"/>
       <c r="G328" s="70"/>
@@ -8078,10 +10556,18 @@
       <c r="N328" s="29"/>
     </row>
     <row r="329" spans="1:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A329" s="143"/>
-      <c r="B329" s="111"/>
-      <c r="C329" s="26"/>
-      <c r="D329" s="19"/>
+      <c r="A329" s="124">
+        <v>37</v>
+      </c>
+      <c r="B329" s="153" t="s">
+        <v>333</v>
+      </c>
+      <c r="C329" s="26">
+        <v>297</v>
+      </c>
+      <c r="D329" s="5" t="s">
+        <v>350</v>
+      </c>
       <c r="E329" s="58"/>
       <c r="F329" s="67"/>
       <c r="G329" s="71"/>
@@ -8093,7 +10579,45 @@
       <c r="M329" s="29"/>
       <c r="N329" s="29"/>
     </row>
+    <row r="330" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A330" s="130"/>
+      <c r="B330" s="154"/>
+      <c r="C330" s="26">
+        <v>298</v>
+      </c>
+      <c r="D330" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A331" s="130"/>
+      <c r="B331" s="154"/>
+      <c r="C331" s="26">
+        <v>299</v>
+      </c>
+      <c r="D331" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A332" s="130"/>
+      <c r="B332" s="154"/>
+      <c r="C332" s="26">
+        <v>300</v>
+      </c>
+      <c r="D332" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A333" s="130"/>
+      <c r="B333" s="154"/>
+      <c r="C333" s="26">
+        <v>301</v>
+      </c>
+      <c r="D333" s="5" t="s">
+        <v>338</v>
+      </c>
       <c r="E333"/>
       <c r="F333"/>
       <c r="G333"/>
@@ -8104,7 +10628,15 @@
       </c>
       <c r="K333"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A334" s="130"/>
+      <c r="B334" s="154"/>
+      <c r="C334" s="26">
+        <v>302</v>
+      </c>
+      <c r="D334" s="5" t="s">
+        <v>354</v>
+      </c>
       <c r="E334"/>
       <c r="F334"/>
       <c r="G334"/>
@@ -8114,6 +10646,14 @@
       <c r="K334"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A335" s="130"/>
+      <c r="B335" s="154"/>
+      <c r="C335" s="26">
+        <v>303</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>355</v>
+      </c>
       <c r="E335"/>
       <c r="F335"/>
       <c r="G335" s="83"/>
@@ -8122,7 +10662,19 @@
       <c r="J335"/>
       <c r="K335"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A336" s="136">
+        <v>38</v>
+      </c>
+      <c r="B336" s="159" t="s">
+        <v>356</v>
+      </c>
+      <c r="C336" s="26">
+        <v>304</v>
+      </c>
+      <c r="D336" s="18" t="s">
+        <v>357</v>
+      </c>
       <c r="E336"/>
       <c r="F336"/>
       <c r="G336"/>
@@ -8131,7 +10683,15 @@
       <c r="J336"/>
       <c r="K336"/>
     </row>
-    <row r="337" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A337" s="128"/>
+      <c r="B337" s="151"/>
+      <c r="C337" s="26">
+        <v>305</v>
+      </c>
+      <c r="D337" s="16" t="s">
+        <v>358</v>
+      </c>
       <c r="E337"/>
       <c r="F337"/>
       <c r="G337"/>
@@ -8140,7 +10700,15 @@
       <c r="J337"/>
       <c r="K337"/>
     </row>
-    <row r="338" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A338" s="128"/>
+      <c r="B338" s="151"/>
+      <c r="C338" s="26">
+        <v>306</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="E338"/>
       <c r="F338"/>
       <c r="G338"/>
@@ -8149,7 +10717,15 @@
       <c r="J338"/>
       <c r="K338"/>
     </row>
-    <row r="339" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A339" s="128"/>
+      <c r="B339" s="151"/>
+      <c r="C339" s="26">
+        <v>307</v>
+      </c>
+      <c r="D339" s="5" t="s">
+        <v>360</v>
+      </c>
       <c r="E339"/>
       <c r="F339"/>
       <c r="G339"/>
@@ -8158,7 +10734,15 @@
       <c r="J339"/>
       <c r="K339"/>
     </row>
-    <row r="340" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A340" s="128"/>
+      <c r="B340" s="151"/>
+      <c r="C340" s="26">
+        <v>308</v>
+      </c>
+      <c r="D340" s="5" t="s">
+        <v>361</v>
+      </c>
       <c r="E340"/>
       <c r="F340"/>
       <c r="G340"/>
@@ -8167,7 +10751,15 @@
       <c r="J340"/>
       <c r="K340"/>
     </row>
-    <row r="341" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A341" s="128"/>
+      <c r="B341" s="151"/>
+      <c r="C341" s="26">
+        <v>309</v>
+      </c>
+      <c r="D341" s="5" t="s">
+        <v>362</v>
+      </c>
       <c r="E341"/>
       <c r="F341"/>
       <c r="G341"/>
@@ -8176,7 +10768,15 @@
       <c r="J341"/>
       <c r="K341"/>
     </row>
-    <row r="342" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A342" s="128"/>
+      <c r="B342" s="151"/>
+      <c r="C342" s="26">
+        <v>310</v>
+      </c>
+      <c r="D342" s="5" t="s">
+        <v>363</v>
+      </c>
       <c r="E342"/>
       <c r="F342"/>
       <c r="G342"/>
@@ -8185,88 +10785,222 @@
       <c r="J342"/>
       <c r="K342"/>
     </row>
+    <row r="343" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A343" s="128"/>
+      <c r="B343" s="151"/>
+      <c r="C343" s="26">
+        <v>311</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A344" s="128"/>
+      <c r="B344" s="151"/>
+      <c r="C344" s="26">
+        <v>312</v>
+      </c>
+      <c r="D344" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A345" s="128"/>
+      <c r="B345" s="151"/>
+      <c r="C345" s="26">
+        <v>313</v>
+      </c>
+      <c r="D345" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A346" s="128"/>
+      <c r="B346" s="151"/>
+      <c r="C346" s="26">
+        <v>314</v>
+      </c>
+      <c r="D346" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A347" s="128"/>
+      <c r="B347" s="151"/>
+      <c r="C347" s="26">
+        <v>315</v>
+      </c>
+      <c r="D347" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A348" s="128"/>
+      <c r="B348" s="151"/>
+      <c r="C348" s="26">
+        <v>316</v>
+      </c>
+      <c r="D348" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A349" s="128"/>
+      <c r="B349" s="151"/>
+      <c r="C349" s="26">
+        <v>317</v>
+      </c>
+      <c r="D349" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A350" s="128"/>
+      <c r="B350" s="151"/>
+      <c r="C350" s="26">
+        <v>318</v>
+      </c>
+      <c r="D350" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A351" s="128"/>
+      <c r="B351" s="151"/>
+      <c r="C351" s="26">
+        <v>319</v>
+      </c>
+      <c r="D351" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A352" s="128"/>
+      <c r="B352" s="151"/>
+      <c r="C352" s="26">
+        <v>320</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A353" s="128"/>
+      <c r="B353" s="151"/>
+      <c r="C353" s="26">
+        <v>321</v>
+      </c>
+      <c r="D353" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A354" s="128"/>
+      <c r="B354" s="151"/>
+      <c r="C354" s="26">
+        <v>322</v>
+      </c>
+      <c r="D354" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A355" s="128"/>
+      <c r="B355" s="151"/>
+      <c r="C355" s="26">
+        <v>323</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A356" s="128"/>
+      <c r="B356" s="151"/>
+      <c r="C356" s="26">
+        <v>324</v>
+      </c>
+      <c r="D356" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A357" s="128"/>
+      <c r="B357" s="151"/>
+      <c r="C357" s="26">
+        <v>325</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A358" s="128"/>
+      <c r="B358" s="151"/>
+      <c r="C358" s="26">
+        <v>326</v>
+      </c>
+      <c r="D358" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A359" s="128"/>
+      <c r="B359" s="151"/>
+      <c r="C359" s="26">
+        <v>327</v>
+      </c>
+      <c r="D359" s="9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A360" s="137"/>
+      <c r="B360" s="160"/>
+      <c r="C360" s="26">
+        <v>328</v>
+      </c>
+      <c r="D360" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="97">
-    <mergeCell ref="D1:N1"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="A200:A208"/>
-    <mergeCell ref="A209:A213"/>
-    <mergeCell ref="A214:A221"/>
-    <mergeCell ref="A222:A232"/>
-    <mergeCell ref="A233:A237"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="A29:A37"/>
-    <mergeCell ref="B29:B37"/>
-    <mergeCell ref="B14:B22"/>
-    <mergeCell ref="A240:A242"/>
-    <mergeCell ref="A243:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A252"/>
-    <mergeCell ref="A283:A289"/>
-    <mergeCell ref="A290:A297"/>
-    <mergeCell ref="A298:A304"/>
-    <mergeCell ref="A305:A329"/>
-    <mergeCell ref="A253:A256"/>
-    <mergeCell ref="A257:A261"/>
-    <mergeCell ref="A262:A265"/>
-    <mergeCell ref="A266:A274"/>
-    <mergeCell ref="A275:A282"/>
-    <mergeCell ref="A38:A44"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="A45:A71"/>
-    <mergeCell ref="B45:B71"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="A77:A88"/>
-    <mergeCell ref="B77:B88"/>
-    <mergeCell ref="A89:A96"/>
-    <mergeCell ref="B89:B96"/>
-    <mergeCell ref="A97:A107"/>
-    <mergeCell ref="B97:B107"/>
-    <mergeCell ref="A108:A117"/>
-    <mergeCell ref="B108:B117"/>
-    <mergeCell ref="A118:A128"/>
-    <mergeCell ref="B118:B128"/>
-    <mergeCell ref="A129:A138"/>
-    <mergeCell ref="B129:B138"/>
-    <mergeCell ref="A139:A153"/>
-    <mergeCell ref="B139:B153"/>
-    <mergeCell ref="A154:A165"/>
-    <mergeCell ref="B154:B165"/>
-    <mergeCell ref="A166:A176"/>
-    <mergeCell ref="B166:B176"/>
-    <mergeCell ref="A194:A199"/>
-    <mergeCell ref="B194:B199"/>
-    <mergeCell ref="A177:A179"/>
-    <mergeCell ref="B177:B179"/>
-    <mergeCell ref="A180:A187"/>
-    <mergeCell ref="B180:B187"/>
-    <mergeCell ref="A188:A193"/>
-    <mergeCell ref="B188:B193"/>
-    <mergeCell ref="B200:B208"/>
-    <mergeCell ref="B209:B213"/>
-    <mergeCell ref="B214:B221"/>
-    <mergeCell ref="B222:B232"/>
-    <mergeCell ref="B233:B237"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="B240:B242"/>
-    <mergeCell ref="B243:B244"/>
-    <mergeCell ref="B245:B247"/>
-    <mergeCell ref="B248:B252"/>
-    <mergeCell ref="B283:B289"/>
-    <mergeCell ref="B290:B297"/>
-    <mergeCell ref="B298:B304"/>
-    <mergeCell ref="B305:B329"/>
-    <mergeCell ref="B253:B256"/>
-    <mergeCell ref="B257:B261"/>
-    <mergeCell ref="B262:B265"/>
-    <mergeCell ref="B266:B274"/>
-    <mergeCell ref="B275:B282"/>
+  <mergeCells count="105">
+    <mergeCell ref="A321:A328"/>
+    <mergeCell ref="B321:B328"/>
+    <mergeCell ref="A329:A335"/>
+    <mergeCell ref="B329:B335"/>
+    <mergeCell ref="A336:A360"/>
+    <mergeCell ref="B336:B360"/>
+    <mergeCell ref="A297:A305"/>
+    <mergeCell ref="B297:B305"/>
+    <mergeCell ref="A306:A313"/>
+    <mergeCell ref="B306:B313"/>
+    <mergeCell ref="A314:A320"/>
+    <mergeCell ref="B314:B320"/>
+    <mergeCell ref="B284:B287"/>
+    <mergeCell ref="A288:A292"/>
+    <mergeCell ref="B288:B292"/>
+    <mergeCell ref="A293:A296"/>
+    <mergeCell ref="B293:B296"/>
+    <mergeCell ref="A225:A230"/>
+    <mergeCell ref="B225:B230"/>
+    <mergeCell ref="A231:A239"/>
+    <mergeCell ref="B231:B239"/>
+    <mergeCell ref="A240:A244"/>
+    <mergeCell ref="B240:B244"/>
+    <mergeCell ref="A208:A210"/>
+    <mergeCell ref="B208:B210"/>
+    <mergeCell ref="A211:A218"/>
+    <mergeCell ref="B211:B218"/>
+    <mergeCell ref="A219:A224"/>
+    <mergeCell ref="B219:B224"/>
+    <mergeCell ref="D5:N5"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="D7:N7"/>
+    <mergeCell ref="B8:N8"/>
+    <mergeCell ref="B9:N9"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:D12"/>
@@ -8279,11 +11013,65 @@
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="N11:N12"/>
-    <mergeCell ref="D5:N5"/>
-    <mergeCell ref="D6:N6"/>
-    <mergeCell ref="D7:N7"/>
-    <mergeCell ref="B8:N8"/>
-    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="B253:B263"/>
+    <mergeCell ref="B264:B268"/>
+    <mergeCell ref="B269:B270"/>
+    <mergeCell ref="B271:B273"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="B276:B278"/>
+    <mergeCell ref="B279:B283"/>
+    <mergeCell ref="B245:B252"/>
+    <mergeCell ref="B197:B207"/>
+    <mergeCell ref="A170:A184"/>
+    <mergeCell ref="B170:B184"/>
+    <mergeCell ref="A185:A196"/>
+    <mergeCell ref="B185:B196"/>
+    <mergeCell ref="A197:A207"/>
+    <mergeCell ref="A139:A148"/>
+    <mergeCell ref="B139:B148"/>
+    <mergeCell ref="A149:A159"/>
+    <mergeCell ref="B149:B159"/>
+    <mergeCell ref="A160:A169"/>
+    <mergeCell ref="B160:B169"/>
+    <mergeCell ref="A108:A119"/>
+    <mergeCell ref="B108:B119"/>
+    <mergeCell ref="A120:A127"/>
+    <mergeCell ref="B120:B127"/>
+    <mergeCell ref="A128:A138"/>
+    <mergeCell ref="B128:B138"/>
+    <mergeCell ref="A76:A102"/>
+    <mergeCell ref="B76:B102"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="A45:A53"/>
+    <mergeCell ref="B45:B53"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="B54:B59"/>
+    <mergeCell ref="A60:A68"/>
+    <mergeCell ref="B60:B68"/>
+    <mergeCell ref="A69:A75"/>
+    <mergeCell ref="B69:B75"/>
+    <mergeCell ref="A253:A263"/>
+    <mergeCell ref="A264:A268"/>
+    <mergeCell ref="A269:A270"/>
+    <mergeCell ref="A271:A273"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="A276:A278"/>
+    <mergeCell ref="A279:A283"/>
+    <mergeCell ref="A284:A287"/>
+    <mergeCell ref="A245:A252"/>
+    <mergeCell ref="D1:N1"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="A29:A37"/>
+    <mergeCell ref="B29:B37"/>
+    <mergeCell ref="B14:B22"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="122" scale="72" orientation="landscape" r:id="rId1"/>
@@ -8317,75 +11105,75 @@
       <c r="A1" s="78"/>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="89"/>
     </row>
     <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="80"/>
-      <c r="D2" s="148" t="s">
+      <c r="D2" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="149"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="91"/>
     </row>
     <row r="3" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
-      <c r="D3" s="150" t="s">
+      <c r="D3" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
-      <c r="L3" s="150"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="150"/>
-      <c r="O3" s="150"/>
-      <c r="P3" s="151"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="93"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="80"/>
-      <c r="D4" s="152" t="s">
+      <c r="D4" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="152"/>
-      <c r="L4" s="152"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="152"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="153"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="95"/>
     </row>
     <row r="5" spans="1:16" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="80"/>
@@ -8427,130 +11215,130 @@
       <c r="A7" s="81"/>
       <c r="B7" s="82"/>
       <c r="C7" s="82"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="89"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="97"/>
     </row>
     <row r="8" spans="1:16" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
     </row>
     <row r="9" spans="1:16" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="91"/>
-      <c r="P9" s="91"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
     </row>
     <row r="10" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="92" t="s">
+      <c r="D10" s="104"/>
+      <c r="E10" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="92" t="s">
+      <c r="F10" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="102" t="s">
+      <c r="G10" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="109"/>
+      <c r="L10" s="109"/>
+      <c r="M10" s="109"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="109"/>
+      <c r="P10" s="109"/>
     </row>
     <row r="11" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="93"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="92" t="s">
+      <c r="A11" s="101"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="103" t="s">
+      <c r="H11" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="104"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="101" t="s">
+      <c r="I11" s="111"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="L11" s="101" t="s">
+      <c r="L11" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="101" t="s">
+      <c r="M11" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="N11" s="101" t="s">
+      <c r="N11" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="101" t="s">
+      <c r="O11" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="P11" s="101" t="s">
+      <c r="P11" s="113" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
       <c r="H12" s="73" t="s">
         <v>13</v>
       </c>
@@ -8560,12 +11348,12 @@
       <c r="J12" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="113"/>
+      <c r="P12" s="113"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="23">
@@ -8618,10 +11406,10 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="157">
+      <c r="A14" s="114">
         <v>1</v>
       </c>
-      <c r="B14" s="158"/>
+      <c r="B14" s="115"/>
       <c r="C14" s="26">
         <v>1</v>
       </c>
@@ -8640,8 +11428,8 @@
       <c r="P14" s="29"/>
     </row>
     <row r="15" spans="1:16" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="157"/>
-      <c r="B15" s="159"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="116"/>
       <c r="C15" s="26">
         <v>2</v>
       </c>
@@ -8660,8 +11448,8 @@
       <c r="P15" s="29"/>
     </row>
     <row r="16" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="157"/>
-      <c r="B16" s="159"/>
+      <c r="A16" s="114"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="26">
         <v>3</v>
       </c>
@@ -8680,8 +11468,8 @@
       <c r="P16" s="29"/>
     </row>
     <row r="17" spans="1:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="157"/>
-      <c r="B17" s="159"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="26">
         <v>4</v>
       </c>
@@ -8700,8 +11488,8 @@
       <c r="P17" s="29"/>
     </row>
     <row r="18" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="157"/>
-      <c r="B18" s="159"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="26">
         <v>5</v>
       </c>
@@ -8720,8 +11508,8 @@
       <c r="P18" s="29"/>
     </row>
     <row r="19" spans="1:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="157"/>
-      <c r="B19" s="159"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="116"/>
       <c r="C19" s="26">
         <v>6</v>
       </c>
@@ -8740,8 +11528,8 @@
       <c r="P19" s="29"/>
     </row>
     <row r="20" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="157"/>
-      <c r="B20" s="159"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="26">
         <v>7</v>
       </c>
@@ -8760,8 +11548,8 @@
       <c r="P20" s="29"/>
     </row>
     <row r="21" spans="1:16" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="157"/>
-      <c r="B21" s="159"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="26">
         <v>8</v>
       </c>
@@ -8780,8 +11568,8 @@
       <c r="P21" s="29"/>
     </row>
     <row r="22" spans="1:16" ht="31.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="157"/>
-      <c r="B22" s="160"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="117"/>
       <c r="C22" s="26">
         <v>9</v>
       </c>
@@ -8800,10 +11588,10 @@
       <c r="P22" s="29"/>
     </row>
     <row r="23" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="126">
+      <c r="A23" s="118">
         <v>2</v>
       </c>
-      <c r="B23" s="129"/>
+      <c r="B23" s="121"/>
       <c r="C23" s="26">
         <v>10</v>
       </c>
@@ -8822,8 +11610,8 @@
       <c r="P23" s="29"/>
     </row>
     <row r="24" spans="1:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="127"/>
-      <c r="B24" s="130"/>
+      <c r="A24" s="119"/>
+      <c r="B24" s="122"/>
       <c r="C24" s="26">
         <v>11</v>
       </c>
@@ -8842,8 +11630,8 @@
       <c r="P24" s="29"/>
     </row>
     <row r="25" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="127"/>
-      <c r="B25" s="130"/>
+      <c r="A25" s="119"/>
+      <c r="B25" s="122"/>
       <c r="C25" s="26">
         <v>12</v>
       </c>
@@ -8862,8 +11650,8 @@
       <c r="P25" s="29"/>
     </row>
     <row r="26" spans="1:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="127"/>
-      <c r="B26" s="130"/>
+      <c r="A26" s="119"/>
+      <c r="B26" s="122"/>
       <c r="C26" s="26">
         <v>13</v>
       </c>
@@ -8882,8 +11670,8 @@
       <c r="P26" s="29"/>
     </row>
     <row r="27" spans="1:16" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="127"/>
-      <c r="B27" s="130"/>
+      <c r="A27" s="119"/>
+      <c r="B27" s="122"/>
       <c r="C27" s="26">
         <v>14</v>
       </c>
@@ -8902,8 +11690,8 @@
       <c r="P27" s="29"/>
     </row>
     <row r="28" spans="1:16" ht="53.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="128"/>
-      <c r="B28" s="131"/>
+      <c r="A28" s="120"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="26">
         <v>15</v>
       </c>
@@ -9015,12 +11803,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D6:P6"/>
-    <mergeCell ref="D1:P1"/>
-    <mergeCell ref="D2:P2"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="D4:P4"/>
-    <mergeCell ref="D5:P5"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B14:B22"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B23:B28"/>
     <mergeCell ref="D7:P7"/>
     <mergeCell ref="B8:P8"/>
     <mergeCell ref="B9:P9"/>
@@ -9036,12 +11824,12 @@
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="P11:P12"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B14:B22"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="D6:P6"/>
+    <mergeCell ref="D1:P1"/>
+    <mergeCell ref="D2:P2"/>
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="D4:P4"/>
+    <mergeCell ref="D5:P5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="122" scale="72" orientation="landscape" r:id="rId1"/>

--- a/resources/templates/Template Laporan RTM FST.xlsx
+++ b/resources/templates/Template Laporan RTM FST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SiGKM\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588819E8-9920-4D68-B9BA-E02FB947B624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185F6F1B-46AC-4BE1-BF4F-A4C04129F226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8E063A3F-0C28-4533-A45D-5ECC25265349}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>KEMENTERIAN PENDIDIKAN TINGGI, SAINS, DAN TEKNOLOGI</t>
   </si>
@@ -110,13 +110,34 @@
   </si>
   <si>
     <t>Kupang, ……..................................2026</t>
+  </si>
+  <si>
+    <t>Mengetahui</t>
+  </si>
+  <si>
+    <t>Koordinator Prodi</t>
+  </si>
+  <si>
+    <t>Ketua GKM</t>
+  </si>
+  <si>
+    <t>Anggota GKM</t>
+  </si>
+  <si>
+    <t>(Dr. YULIANTO TRIWAHYUADI POLLY, S.Kom., M.Cs)</t>
+  </si>
+  <si>
+    <t>(CLARISSA ELFIRA AMOS PAH, M.T.I)</t>
+  </si>
+  <si>
+    <t>(NELCI DESSY RUMLAKLAK, S.KOM, M.KOM)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +200,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -369,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -413,90 +448,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,490 +599,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1584960" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B98CD57-3506-4A00-8467-8C83DA007905}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17471390" y="4732020"/>
-          <a:ext cx="1584960" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3932767</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>176953</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1397000</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>143086</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B67FDBE-151C-48FD-AFD3-D4E9B777B6E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12556067" y="4380653"/>
-          <a:ext cx="1394883" cy="1255183"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Ketua GKM</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1336887</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>922866</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>113454</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B7C1090-099A-4B86-B7C5-3D455908A5A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15789487" y="4381501"/>
-          <a:ext cx="1167129" cy="1224703"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Anggota GKM</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1394459</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1236133</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A52C1B31-E7BA-4FED-862B-4C6C2A6BF096}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8322309" y="4410710"/>
-          <a:ext cx="3753274" cy="1257300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Mengetahui</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Koord. Prodi</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1332,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4AE117-EDE6-421F-A879-14F0E7AF6AB3}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.54296875" style="3" customWidth="1"/>
@@ -1356,212 +915,212 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="34"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="36"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="38"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="40"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="24"/>
     </row>
     <row r="5" spans="1:14" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="42"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="16"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="26"/>
     </row>
     <row r="8" spans="1:14" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
     </row>
     <row r="10" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="29" t="s">
+      <c r="D10" s="33"/>
+      <c r="E10" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
     </row>
     <row r="11" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="20" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="15" t="s">
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="N11" s="15" t="s">
+      <c r="N11" s="42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="22"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="7" t="s">
         <v>20</v>
       </c>
@@ -1571,12 +1130,12 @@
       <c r="H12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
@@ -1622,18 +1181,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
-      <c r="J17" t="s">
+      <c r="J17" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="K17"/>
-    </row>
-    <row r="18" spans="5:11" x14ac:dyDescent="0.35">
+      <c r="K17" s="46"/>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1642,7 +1201,7 @@
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="5:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19" s="14"/>
@@ -1651,77 +1210,94 @@
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
+    <row r="20" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D20" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="44"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
+    <row r="21" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D21" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="G21" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45" t="s">
+        <v>27</v>
+      </c>
       <c r="K21"/>
     </row>
-    <row r="22" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
+    <row r="22" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D22" s="43"/>
+      <c r="E22" s="44"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
+    <row r="23" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D23" s="43"/>
+      <c r="E23" s="44"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
+    <row r="24" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D24" s="43"/>
+      <c r="E24" s="44"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
+    <row r="25" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
       <c r="K25"/>
     </row>
-    <row r="26" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
+    <row r="26" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D26" s="43"/>
+      <c r="E26" s="44"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
       <c r="K26"/>
+    </row>
+    <row r="27" spans="4:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D27" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="44"/>
+      <c r="G27" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D6:N6"/>
-    <mergeCell ref="D1:N1"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="D5:N5"/>
     <mergeCell ref="D7:N7"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B9:N9"/>
@@ -1737,6 +1313,12 @@
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="N11:N12"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="D1:N1"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="D5:N5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="122" scale="72" orientation="landscape" r:id="rId1"/>
